--- a/VARdata.xlsx
+++ b/VARdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/drk9452_ads_northwestern_edu/Documents/Uni/LBS PhD/Research/Projects/Oil supply shocks/Repositories/OilSupplyNewsUpdate/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{E4666CA9-3A26-40FF-83AF-CBD9E073F10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{408C2D0E-613A-43F9-9D9E-CA34D6D354E9}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{E4666CA9-3A26-40FF-83AF-CBD9E073F10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{383DACD1-2472-465F-BF77-91C183A4CCEF}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-13905" windowWidth="38640" windowHeight="21240" xr2:uid="{E64FA3D6-CEF8-4D84-93AC-D7CE42D05F79}"/>
+    <workbookView xWindow="86280" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E64FA3D6-CEF8-4D84-93AC-D7CE42D05F79}"/>
   </bookViews>
   <sheets>
     <sheet name="Monthly" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="625">
   <si>
     <t>POIL</t>
   </si>
@@ -1908,6 +1908,9 @@
   </si>
   <si>
     <t>2025M06</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
 </sst>
 </file>
@@ -1960,10 +1963,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2284,14 +2283,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12E1CFC8-D9C0-4308-945A-68684190B2E6}">
   <dimension ref="A1:G619"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2309,7 +2308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2332,7 +2331,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -2355,7 +2354,7 @@
         <v>47.3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2378,7 +2377,7 @@
         <v>47.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2401,7 +2400,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2424,7 +2423,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2447,7 +2446,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2470,7 +2469,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -2493,7 +2492,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -2516,7 +2515,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -2539,7 +2538,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -2562,7 +2561,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -2585,7 +2584,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -2608,7 +2607,7 @@
         <v>52.3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -2631,7 +2630,7 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -2654,7 +2653,7 @@
         <v>52.8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2677,7 +2676,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -2700,7 +2699,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -2723,7 +2722,7 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -2746,7 +2745,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2769,7 +2768,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -2792,7 +2791,7 @@
         <v>54.6</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -2815,7 +2814,7 @@
         <v>54.9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -2838,7 +2837,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -2861,7 +2860,7 @@
         <v>55.6</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -2884,7 +2883,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -2907,7 +2906,7 @@
         <v>55.9</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -2930,7 +2929,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -2953,7 +2952,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -2976,7 +2975,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -2999,7 +2998,7 @@
         <v>56.7</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -3022,7 +3021,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -3045,7 +3044,7 @@
         <v>57.3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -3068,7 +3067,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -3091,7 +3090,7 @@
         <v>57.9</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -3114,7 +3113,7 @@
         <v>58.1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -3137,7 +3136,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -3160,7 +3159,7 @@
         <v>58.7</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -3183,7 +3182,7 @@
         <v>59.3</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -3206,7 +3205,7 @@
         <v>59.6</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -3229,7 +3228,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -3252,7 +3251,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -3275,7 +3274,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -3298,7 +3297,7 @@
         <v>60.8</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -3321,7 +3320,7 @@
         <v>61.1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -3344,7 +3343,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -3367,7 +3366,7 @@
         <v>61.6</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -3390,7 +3389,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -3413,7 +3412,7 @@
         <v>62.3</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -3436,7 +3435,7 @@
         <v>62.7</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -3459,7 +3458,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>63.4</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -3505,7 +3504,7 @@
         <v>63.9</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -3528,7 +3527,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -3551,7 +3550,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -3574,7 +3573,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -3597,7 +3596,7 @@
         <v>65.900000000000006</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -3620,7 +3619,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -3643,7 +3642,7 @@
         <v>67.099999999999994</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -3666,7 +3665,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -3689,7 +3688,7 @@
         <v>67.900000000000006</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -3712,7 +3711,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -3735,7 +3734,7 @@
         <v>69.2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -3758,7 +3757,7 @@
         <v>69.900000000000006</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -3781,7 +3780,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -3804,7 +3803,7 @@
         <v>71.400000000000006</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -3827,7 +3826,7 @@
         <v>72.2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>72</v>
       </c>
@@ -3850,7 +3849,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -3873,7 +3872,7 @@
         <v>73.7</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -3896,7 +3895,7 @@
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -3919,7 +3918,7 @@
         <v>75.2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>76</v>
       </c>
@@ -3942,7 +3941,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>77</v>
       </c>
@@ -3965,7 +3964,7 @@
         <v>76.900000000000006</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -3988,7 +3987,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>79</v>
       </c>
@@ -4011,7 +4010,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>80</v>
       </c>
@@ -4034,7 +4033,7 @@
         <v>80.099999999999994</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -4057,7 +4056,7 @@
         <v>80.900000000000006</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>82</v>
       </c>
@@ -4080,7 +4079,7 @@
         <v>81.7</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -4103,7 +4102,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -4126,7 +4125,7 @@
         <v>82.6</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>85</v>
       </c>
@@ -4149,7 +4148,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>86</v>
       </c>
@@ -4172,7 +4171,7 @@
         <v>83.9</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>87</v>
       </c>
@@ -4195,7 +4194,7 @@
         <v>84.7</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>88</v>
       </c>
@@ -4218,7 +4217,7 @@
         <v>85.6</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -4241,7 +4240,7 @@
         <v>86.4</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>90</v>
       </c>
@@ -4264,7 +4263,7 @@
         <v>87.2</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -4287,7 +4286,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>92</v>
       </c>
@@ -4310,7 +4309,7 @@
         <v>88.6</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>93</v>
       </c>
@@ -4333,7 +4332,7 @@
         <v>89.1</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -4356,7 +4355,7 @@
         <v>89.7</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>95</v>
       </c>
@@ -4379,7 +4378,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -4402,7 +4401,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -4425,7 +4424,7 @@
         <v>92.2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>98</v>
       </c>
@@ -4448,7 +4447,7 @@
         <v>93.1</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>99</v>
       </c>
@@ -4471,7 +4470,7 @@
         <v>93.4</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>100</v>
       </c>
@@ -4494,7 +4493,7 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>101</v>
       </c>
@@ -4517,7 +4516,7 @@
         <v>94.1</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>102</v>
       </c>
@@ -4540,7 +4539,7 @@
         <v>94.4</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>103</v>
       </c>
@@ -4563,7 +4562,7 @@
         <v>94.7</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>104</v>
       </c>
@@ -4586,7 +4585,7 @@
         <v>94.7</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>105</v>
       </c>
@@ -4609,7 +4608,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>106</v>
       </c>
@@ -4632,7 +4631,7 @@
         <v>95.9</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -4655,7 +4654,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>108</v>
       </c>
@@ -4678,7 +4677,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>109</v>
       </c>
@@ -4701,7 +4700,7 @@
         <v>97.7</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>110</v>
       </c>
@@ -4724,7 +4723,7 @@
         <v>97.7</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>111</v>
       </c>
@@ -4747,7 +4746,7 @@
         <v>98.1</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>112</v>
       </c>
@@ -4770,7 +4769,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>113</v>
       </c>
@@ -4793,7 +4792,7 @@
         <v>97.7</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -4816,7 +4815,7 @@
         <v>97.9</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -4839,7 +4838,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>116</v>
       </c>
@@ -4862,7 +4861,7 @@
         <v>98.1</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>117</v>
       </c>
@@ -4885,7 +4884,7 @@
         <v>98.8</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>118</v>
       </c>
@@ -4908,7 +4907,7 @@
         <v>99.2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>119</v>
       </c>
@@ -4931,7 +4930,7 @@
         <v>99.4</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>120</v>
       </c>
@@ -4954,7 +4953,7 @@
         <v>99.8</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>121</v>
       </c>
@@ -4977,7 +4976,7 @@
         <v>100.1</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>122</v>
       </c>
@@ -5000,7 +4999,7 @@
         <v>100.4</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>123</v>
       </c>
@@ -5023,7 +5022,7 @@
         <v>100.8</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>124</v>
       </c>
@@ -5046,7 +5045,7 @@
         <v>101.1</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>125</v>
       </c>
@@ -5069,7 +5068,7 @@
         <v>101.4</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>126</v>
       </c>
@@ -5092,7 +5091,7 @@
         <v>102.1</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>127</v>
       </c>
@@ -5115,7 +5114,7 @@
         <v>102.6</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>128</v>
       </c>
@@ -5138,7 +5137,7 @@
         <v>102.9</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>129</v>
       </c>
@@ -5161,7 +5160,7 @@
         <v>103.3</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>130</v>
       </c>
@@ -5184,7 +5183,7 @@
         <v>103.5</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>131</v>
       </c>
@@ -5207,7 +5206,7 @@
         <v>103.7</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
         <v>132</v>
       </c>
@@ -5230,7 +5229,7 @@
         <v>104.1</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>133</v>
       </c>
@@ -5253,7 +5252,7 @@
         <v>104.4</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>134</v>
       </c>
@@ -5276,7 +5275,7 @@
         <v>104.7</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>135</v>
       </c>
@@ -5299,7 +5298,7 @@
         <v>105.1</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>136</v>
       </c>
@@ -5322,7 +5321,7 @@
         <v>105.3</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>137</v>
       </c>
@@ -5345,7 +5344,7 @@
         <v>105.5</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>138</v>
       </c>
@@ -5368,7 +5367,7 @@
         <v>105.7</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>139</v>
       </c>
@@ -5391,7 +5390,7 @@
         <v>106.3</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>140</v>
       </c>
@@ -5414,7 +5413,7 @@
         <v>106.8</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>141</v>
       </c>
@@ -5437,7 +5436,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>142</v>
       </c>
@@ -5460,7 +5459,7 @@
         <v>107.2</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>143</v>
       </c>
@@ -5483,7 +5482,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>144</v>
       </c>
@@ -5506,7 +5505,7 @@
         <v>107.7</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>145</v>
       </c>
@@ -5529,7 +5528,7 @@
         <v>107.9</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>146</v>
       </c>
@@ -5552,7 +5551,7 @@
         <v>108.1</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>147</v>
       </c>
@@ -5575,7 +5574,7 @@
         <v>108.5</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>148</v>
       </c>
@@ -5598,7 +5597,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>149</v>
       </c>
@@ -5621,7 +5620,7 @@
         <v>109.5</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>150</v>
       </c>
@@ -5644,7 +5643,7 @@
         <v>109.9</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
         <v>151</v>
       </c>
@@ -5667,7 +5666,7 @@
         <v>109.7</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
         <v>152</v>
       </c>
@@ -5690,7 +5689,7 @@
         <v>109.1</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
         <v>153</v>
       </c>
@@ -5713,7 +5712,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
         <v>154</v>
       </c>
@@ -5736,7 +5735,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
         <v>155</v>
       </c>
@@ -5759,7 +5758,7 @@
         <v>109.4</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
         <v>156</v>
       </c>
@@ -5782,7 +5781,7 @@
         <v>109.5</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
         <v>157</v>
       </c>
@@ -5805,7 +5804,7 @@
         <v>109.6</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
         <v>158</v>
       </c>
@@ -5828,7 +5827,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
         <v>159</v>
       </c>
@@ -5851,7 +5850,7 @@
         <v>110.2</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
         <v>160</v>
       </c>
@@ -5874,7 +5873,7 @@
         <v>110.4</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" t="s">
         <v>161</v>
       </c>
@@ -5897,7 +5896,7 @@
         <v>110.8</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" t="s">
         <v>162</v>
       </c>
@@ -5920,7 +5919,7 @@
         <v>111.4</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
         <v>163</v>
       </c>
@@ -5943,7 +5942,7 @@
         <v>111.8</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" t="s">
         <v>164</v>
       </c>
@@ -5966,7 +5965,7 @@
         <v>112.2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" t="s">
         <v>165</v>
       </c>
@@ -5989,7 +5988,7 @@
         <v>112.7</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
         <v>166</v>
       </c>
@@ -6012,7 +6011,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" t="s">
         <v>167</v>
       </c>
@@ -6035,7 +6034,7 @@
         <v>113.5</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" t="s">
         <v>168</v>
       </c>
@@ -6058,7 +6057,7 @@
         <v>113.8</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" t="s">
         <v>169</v>
       </c>
@@ -6081,7 +6080,7 @@
         <v>114.3</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" t="s">
         <v>170</v>
       </c>
@@ -6104,7 +6103,7 @@
         <v>114.7</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" t="s">
         <v>171</v>
       </c>
@@ -6127,7 +6126,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" t="s">
         <v>172</v>
       </c>
@@ -6150,7 +6149,7 @@
         <v>115.4</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" t="s">
         <v>173</v>
       </c>
@@ -6173,7 +6172,7 @@
         <v>115.6</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" t="s">
         <v>174</v>
       </c>
@@ -6196,7 +6195,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" t="s">
         <v>175</v>
       </c>
@@ -6219,7 +6218,7 @@
         <v>116.2</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" t="s">
         <v>176</v>
       </c>
@@ -6242,7 +6241,7 @@
         <v>116.5</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" t="s">
         <v>177</v>
       </c>
@@ -6265,7 +6264,7 @@
         <v>117.2</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" t="s">
         <v>178</v>
       </c>
@@ -6288,7 +6287,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" t="s">
         <v>179</v>
       </c>
@@ -6311,7 +6310,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" t="s">
         <v>180</v>
       </c>
@@ -6334,7 +6333,7 @@
         <v>118.5</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" t="s">
         <v>181</v>
       </c>
@@ -6357,7 +6356,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" t="s">
         <v>182</v>
       </c>
@@ -6380,7 +6379,7 @@
         <v>119.5</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" t="s">
         <v>183</v>
       </c>
@@ -6403,7 +6402,7 @@
         <v>119.9</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" t="s">
         <v>184</v>
       </c>
@@ -6426,7 +6425,7 @@
         <v>120.3</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" t="s">
         <v>185</v>
       </c>
@@ -6449,7 +6448,7 @@
         <v>120.7</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" t="s">
         <v>186</v>
       </c>
@@ -6472,7 +6471,7 @@
         <v>121.2</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" t="s">
         <v>187</v>
       </c>
@@ -6495,7 +6494,7 @@
         <v>121.6</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" t="s">
         <v>188</v>
       </c>
@@ -6518,7 +6517,7 @@
         <v>122.2</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" t="s">
         <v>189</v>
       </c>
@@ -6541,7 +6540,7 @@
         <v>123.1</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" t="s">
         <v>190</v>
       </c>
@@ -6564,7 +6563,7 @@
         <v>123.7</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" t="s">
         <v>191</v>
       </c>
@@ -6587,7 +6586,7 @@
         <v>124.1</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" t="s">
         <v>192</v>
       </c>
@@ -6610,7 +6609,7 @@
         <v>124.5</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" t="s">
         <v>193</v>
       </c>
@@ -6633,7 +6632,7 @@
         <v>124.5</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" t="s">
         <v>194</v>
       </c>
@@ -6656,7 +6655,7 @@
         <v>124.8</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" t="s">
         <v>195</v>
       </c>
@@ -6679,7 +6678,7 @@
         <v>125.4</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" t="s">
         <v>196</v>
       </c>
@@ -6702,7 +6701,7 @@
         <v>125.9</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" t="s">
         <v>197</v>
       </c>
@@ -6725,7 +6724,7 @@
         <v>126.3</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" t="s">
         <v>198</v>
       </c>
@@ -6748,7 +6747,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" t="s">
         <v>199</v>
       </c>
@@ -6771,7 +6770,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" t="s">
         <v>200</v>
       </c>
@@ -6794,7 +6793,7 @@
         <v>128.6</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" t="s">
         <v>201</v>
       </c>
@@ -6817,7 +6816,7 @@
         <v>128.9</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" t="s">
         <v>202</v>
       </c>
@@ -6840,7 +6839,7 @@
         <v>129.1</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" t="s">
         <v>203</v>
       </c>
@@ -6863,7 +6862,7 @@
         <v>129.9</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" t="s">
         <v>204</v>
       </c>
@@ -6886,7 +6885,7 @@
         <v>130.5</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" t="s">
         <v>205</v>
       </c>
@@ -6909,7 +6908,7 @@
         <v>131.6</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" t="s">
         <v>206</v>
       </c>
@@ -6932,7 +6931,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" t="s">
         <v>207</v>
       </c>
@@ -6955,7 +6954,7 @@
         <v>133.4</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" t="s">
         <v>208</v>
       </c>
@@ -6978,7 +6977,7 @@
         <v>133.69999999999999</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" t="s">
         <v>209</v>
       </c>
@@ -7001,7 +7000,7 @@
         <v>134.19999999999999</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" t="s">
         <v>210</v>
       </c>
@@ -7024,7 +7023,7 @@
         <v>134.69999999999999</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" t="s">
         <v>211</v>
       </c>
@@ -7047,7 +7046,7 @@
         <v>134.80000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" t="s">
         <v>212</v>
       </c>
@@ -7070,7 +7069,7 @@
         <v>134.80000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" t="s">
         <v>213</v>
       </c>
@@ -7093,7 +7092,7 @@
         <v>135.1</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" t="s">
         <v>214</v>
       </c>
@@ -7116,7 +7115,7 @@
         <v>135.6</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" t="s">
         <v>215</v>
       </c>
@@ -7139,7 +7138,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" t="s">
         <v>216</v>
       </c>
@@ -7162,7 +7161,7 @@
         <v>136.19999999999999</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" t="s">
         <v>217</v>
       </c>
@@ -7185,7 +7184,7 @@
         <v>136.6</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" t="s">
         <v>218</v>
       </c>
@@ -7208,7 +7207,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" t="s">
         <v>219</v>
       </c>
@@ -7231,7 +7230,7 @@
         <v>137.19999999999999</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" t="s">
         <v>220</v>
       </c>
@@ -7254,7 +7253,7 @@
         <v>137.80000000000001</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" t="s">
         <v>221</v>
       </c>
@@ -7277,7 +7276,7 @@
         <v>138.19999999999999</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" t="s">
         <v>222</v>
       </c>
@@ -7300,7 +7299,7 @@
         <v>138.30000000000001</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" t="s">
         <v>223</v>
       </c>
@@ -7323,7 +7322,7 @@
         <v>138.6</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" t="s">
         <v>224</v>
       </c>
@@ -7346,7 +7345,7 @@
         <v>139.1</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" t="s">
         <v>225</v>
       </c>
@@ -7369,7 +7368,7 @@
         <v>139.4</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" t="s">
         <v>226</v>
       </c>
@@ -7392,7 +7391,7 @@
         <v>139.69999999999999</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" t="s">
         <v>227</v>
       </c>
@@ -7415,7 +7414,7 @@
         <v>140.1</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" t="s">
         <v>228</v>
       </c>
@@ -7438,7 +7437,7 @@
         <v>140.5</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" t="s">
         <v>229</v>
       </c>
@@ -7461,7 +7460,7 @@
         <v>140.80000000000001</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" t="s">
         <v>230</v>
       </c>
@@ -7484,7 +7483,7 @@
         <v>141.1</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" t="s">
         <v>231</v>
       </c>
@@ -7507,7 +7506,7 @@
         <v>141.69999999999999</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" t="s">
         <v>232</v>
       </c>
@@ -7530,7 +7529,7 @@
         <v>142.1</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" t="s">
         <v>233</v>
       </c>
@@ -7553,7 +7552,7 @@
         <v>142.30000000000001</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" t="s">
         <v>234</v>
       </c>
@@ -7576,7 +7575,7 @@
         <v>142.80000000000001</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" t="s">
         <v>235</v>
       </c>
@@ -7599,7 +7598,7 @@
         <v>143.1</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" t="s">
         <v>236</v>
       </c>
@@ -7622,7 +7621,7 @@
         <v>143.30000000000001</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" t="s">
         <v>237</v>
       </c>
@@ -7645,7 +7644,7 @@
         <v>143.80000000000001</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" t="s">
         <v>238</v>
       </c>
@@ -7668,7 +7667,7 @@
         <v>144.19999999999999</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" t="s">
         <v>239</v>
       </c>
@@ -7691,7 +7690,7 @@
         <v>144.30000000000001</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" t="s">
         <v>240</v>
       </c>
@@ -7714,7 +7713,7 @@
         <v>144.5</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" t="s">
         <v>241</v>
       </c>
@@ -7737,7 +7736,7 @@
         <v>144.80000000000001</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" t="s">
         <v>242</v>
       </c>
@@ -7760,7 +7759,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" t="s">
         <v>243</v>
       </c>
@@ -7783,7 +7782,7 @@
         <v>145.6</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" t="s">
         <v>244</v>
       </c>
@@ -7806,7 +7805,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" t="s">
         <v>245</v>
       </c>
@@ -7829,7 +7828,7 @@
         <v>146.30000000000001</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" t="s">
         <v>246</v>
       </c>
@@ -7852,7 +7851,7 @@
         <v>146.30000000000001</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" t="s">
         <v>247</v>
       </c>
@@ -7875,7 +7874,7 @@
         <v>146.69999999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" t="s">
         <v>248</v>
       </c>
@@ -7898,7 +7897,7 @@
         <v>147.1</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" t="s">
         <v>249</v>
       </c>
@@ -7921,7 +7920,7 @@
         <v>147.19999999999999</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" t="s">
         <v>250</v>
       </c>
@@ -7944,7 +7943,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" t="s">
         <v>251</v>
       </c>
@@ -7967,7 +7966,7 @@
         <v>147.9</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" t="s">
         <v>252</v>
       </c>
@@ -7990,7 +7989,7 @@
         <v>148.4</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" t="s">
         <v>253</v>
       </c>
@@ -8013,7 +8012,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" t="s">
         <v>254</v>
       </c>
@@ -8036,7 +8035,7 @@
         <v>149.30000000000001</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" t="s">
         <v>255</v>
       </c>
@@ -8059,7 +8058,7 @@
         <v>149.4</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" t="s">
         <v>256</v>
       </c>
@@ -8082,7 +8081,7 @@
         <v>149.80000000000001</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" t="s">
         <v>257</v>
       </c>
@@ -8105,7 +8104,7 @@
         <v>150.1</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" t="s">
         <v>258</v>
       </c>
@@ -8128,7 +8127,7 @@
         <v>150.5</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" t="s">
         <v>259</v>
       </c>
@@ -8151,7 +8150,7 @@
         <v>150.9</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" t="s">
         <v>260</v>
       </c>
@@ -8174,7 +8173,7 @@
         <v>151.19999999999999</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" t="s">
         <v>261</v>
       </c>
@@ -8197,7 +8196,7 @@
         <v>151.80000000000001</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" t="s">
         <v>262</v>
       </c>
@@ -8220,7 +8219,7 @@
         <v>152.1</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" t="s">
         <v>263</v>
       </c>
@@ -8243,7 +8242,7 @@
         <v>152.4</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" t="s">
         <v>264</v>
       </c>
@@ -8266,7 +8265,7 @@
         <v>152.6</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" t="s">
         <v>265</v>
       </c>
@@ -8289,7 +8288,7 @@
         <v>152.9</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" t="s">
         <v>266</v>
       </c>
@@ -8312,7 +8311,7 @@
         <v>153.1</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" t="s">
         <v>267</v>
       </c>
@@ -8335,7 +8334,7 @@
         <v>153.5</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" t="s">
         <v>268</v>
       </c>
@@ -8358,7 +8357,7 @@
         <v>153.69999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" t="s">
         <v>269</v>
       </c>
@@ -8381,7 +8380,7 @@
         <v>153.9</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" t="s">
         <v>270</v>
       </c>
@@ -8404,7 +8403,7 @@
         <v>154.69999999999999</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" t="s">
         <v>271</v>
       </c>
@@ -8427,7 +8426,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" t="s">
         <v>272</v>
       </c>
@@ -8450,7 +8449,7 @@
         <v>155.5</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" t="s">
         <v>273</v>
       </c>
@@ -8473,7 +8472,7 @@
         <v>156.1</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" t="s">
         <v>274</v>
       </c>
@@ -8496,7 +8495,7 @@
         <v>156.4</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" t="s">
         <v>275</v>
       </c>
@@ -8519,7 +8518,7 @@
         <v>156.69999999999999</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" t="s">
         <v>276</v>
       </c>
@@ -8542,7 +8541,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" t="s">
         <v>277</v>
       </c>
@@ -8565,7 +8564,7 @@
         <v>157.19999999999999</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" t="s">
         <v>278</v>
       </c>
@@ -8588,7 +8587,7 @@
         <v>157.69999999999999</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" t="s">
         <v>279</v>
       </c>
@@ -8611,7 +8610,7 @@
         <v>158.19999999999999</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" t="s">
         <v>280</v>
       </c>
@@ -8634,7 +8633,7 @@
         <v>158.69999999999999</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" t="s">
         <v>281</v>
       </c>
@@ -8657,7 +8656,7 @@
         <v>159.1</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" t="s">
         <v>282</v>
       </c>
@@ -8680,7 +8679,7 @@
         <v>159.4</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" t="s">
         <v>283</v>
       </c>
@@ -8703,7 +8702,7 @@
         <v>159.69999999999999</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" t="s">
         <v>284</v>
       </c>
@@ -8726,7 +8725,7 @@
         <v>159.80000000000001</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" t="s">
         <v>285</v>
       </c>
@@ -8749,7 +8748,7 @@
         <v>159.9</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" t="s">
         <v>286</v>
       </c>
@@ -8772,7 +8771,7 @@
         <v>159.9</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" t="s">
         <v>287</v>
       </c>
@@ -8795,7 +8794,7 @@
         <v>160.19999999999999</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" t="s">
         <v>288</v>
       </c>
@@ -8818,7 +8817,7 @@
         <v>160.4</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" t="s">
         <v>289</v>
       </c>
@@ -8841,7 +8840,7 @@
         <v>160.80000000000001</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" t="s">
         <v>290</v>
       </c>
@@ -8864,7 +8863,7 @@
         <v>161.19999999999999</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" t="s">
         <v>291</v>
       </c>
@@ -8887,7 +8886,7 @@
         <v>161.5</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" t="s">
         <v>292</v>
       </c>
@@ -8910,7 +8909,7 @@
         <v>161.69999999999999</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" t="s">
         <v>293</v>
       </c>
@@ -8933,7 +8932,7 @@
         <v>161.80000000000001</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" t="s">
         <v>294</v>
       </c>
@@ -8956,7 +8955,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" t="s">
         <v>295</v>
       </c>
@@ -8979,7 +8978,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" t="s">
         <v>296</v>
       </c>
@@ -9002,7 +9001,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" t="s">
         <v>297</v>
       </c>
@@ -9025,7 +9024,7 @@
         <v>162.19999999999999</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" t="s">
         <v>298</v>
       </c>
@@ -9048,7 +9047,7 @@
         <v>162.6</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" t="s">
         <v>299</v>
       </c>
@@ -9071,7 +9070,7 @@
         <v>162.80000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" t="s">
         <v>300</v>
       </c>
@@ -9094,7 +9093,7 @@
         <v>163.19999999999999</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" t="s">
         <v>301</v>
       </c>
@@ -9117,7 +9116,7 @@
         <v>163.4</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" t="s">
         <v>302</v>
       </c>
@@ -9140,7 +9139,7 @@
         <v>163.5</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" t="s">
         <v>303</v>
       </c>
@@ -9163,7 +9162,7 @@
         <v>163.9</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" t="s">
         <v>304</v>
       </c>
@@ -9186,7 +9185,7 @@
         <v>164.1</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" t="s">
         <v>305</v>
       </c>
@@ -9209,7 +9208,7 @@
         <v>164.4</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" t="s">
         <v>306</v>
       </c>
@@ -9232,7 +9231,7 @@
         <v>164.7</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" t="s">
         <v>307</v>
       </c>
@@ -9255,7 +9254,7 @@
         <v>164.7</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" t="s">
         <v>308</v>
       </c>
@@ -9278,7 +9277,7 @@
         <v>164.8</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" t="s">
         <v>309</v>
       </c>
@@ -9301,7 +9300,7 @@
         <v>165.9</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" t="s">
         <v>310</v>
       </c>
@@ -9324,7 +9323,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" t="s">
         <v>311</v>
       </c>
@@ -9347,7 +9346,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" t="s">
         <v>312</v>
       </c>
@@ -9370,7 +9369,7 @@
         <v>166.7</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" t="s">
         <v>313</v>
       </c>
@@ -9393,7 +9392,7 @@
         <v>167.1</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" t="s">
         <v>314</v>
       </c>
@@ -9416,7 +9415,7 @@
         <v>167.8</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" t="s">
         <v>315</v>
       </c>
@@ -9439,7 +9438,7 @@
         <v>168.1</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" t="s">
         <v>316</v>
       </c>
@@ -9462,7 +9461,7 @@
         <v>168.4</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" t="s">
         <v>317</v>
       </c>
@@ -9485,7 +9484,7 @@
         <v>168.8</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" t="s">
         <v>318</v>
       </c>
@@ -9508,7 +9507,7 @@
         <v>169.3</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" t="s">
         <v>319</v>
       </c>
@@ -9531,7 +9530,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" t="s">
         <v>320</v>
       </c>
@@ -9554,7 +9553,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" t="s">
         <v>321</v>
       </c>
@@ -9577,7 +9576,7 @@
         <v>170.9</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" t="s">
         <v>322</v>
       </c>
@@ -9600,7 +9599,7 @@
         <v>171.2</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" t="s">
         <v>323</v>
       </c>
@@ -9623,7 +9622,7 @@
         <v>172.2</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" t="s">
         <v>324</v>
       </c>
@@ -9646,7 +9645,7 @@
         <v>172.7</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" t="s">
         <v>325</v>
       </c>
@@ -9669,7 +9668,7 @@
         <v>172.7</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" t="s">
         <v>326</v>
       </c>
@@ -9692,7 +9691,7 @@
         <v>173.6</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" t="s">
         <v>327</v>
       </c>
@@ -9715,7 +9714,7 @@
         <v>173.9</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" t="s">
         <v>328</v>
       </c>
@@ -9738,7 +9737,7 @@
         <v>174.2</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" t="s">
         <v>329</v>
       </c>
@@ -9761,7 +9760,7 @@
         <v>174.6</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" t="s">
         <v>330</v>
       </c>
@@ -9784,7 +9783,7 @@
         <v>175.6</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" t="s">
         <v>331</v>
       </c>
@@ -9807,7 +9806,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" t="s">
         <v>332</v>
       </c>
@@ -9830,7 +9829,7 @@
         <v>176.1</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" t="s">
         <v>333</v>
       </c>
@@ -9853,7 +9852,7 @@
         <v>176.4</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" t="s">
         <v>334</v>
       </c>
@@ -9876,7 +9875,7 @@
         <v>177.3</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" t="s">
         <v>335</v>
       </c>
@@ -9899,7 +9898,7 @@
         <v>177.7</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" t="s">
         <v>336</v>
       </c>
@@ -9922,7 +9921,7 @@
         <v>177.4</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" t="s">
         <v>337</v>
       </c>
@@ -9945,7 +9944,7 @@
         <v>177.4</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" t="s">
         <v>338</v>
       </c>
@@ -9968,7 +9967,7 @@
         <v>178.1</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" t="s">
         <v>339</v>
       </c>
@@ -9991,7 +9990,7 @@
         <v>177.6</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" t="s">
         <v>340</v>
       </c>
@@ -10014,7 +10013,7 @@
         <v>177.5</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" t="s">
         <v>341</v>
       </c>
@@ -10037,7 +10036,7 @@
         <v>177.4</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" t="s">
         <v>342</v>
       </c>
@@ -10060,7 +10059,7 @@
         <v>177.7</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" t="s">
         <v>343</v>
       </c>
@@ -10083,7 +10082,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" t="s">
         <v>344</v>
       </c>
@@ -10106,7 +10105,7 @@
         <v>178.5</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" t="s">
         <v>345</v>
       </c>
@@ -10129,7 +10128,7 @@
         <v>179.3</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" t="s">
         <v>346</v>
       </c>
@@ -10152,7 +10151,7 @@
         <v>179.5</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" t="s">
         <v>347</v>
       </c>
@@ -10175,7 +10174,7 @@
         <v>179.6</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" t="s">
         <v>348</v>
       </c>
@@ -10198,7 +10197,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" t="s">
         <v>349</v>
       </c>
@@ -10221,7 +10220,7 @@
         <v>180.5</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" t="s">
         <v>350</v>
       </c>
@@ -10244,7 +10243,7 @@
         <v>180.8</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" t="s">
         <v>351</v>
       </c>
@@ -10267,7 +10266,7 @@
         <v>181.2</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" t="s">
         <v>352</v>
       </c>
@@ -10290,7 +10289,7 @@
         <v>181.5</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" t="s">
         <v>353</v>
       </c>
@@ -10313,7 +10312,7 @@
         <v>181.8</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" t="s">
         <v>354</v>
       </c>
@@ -10336,7 +10335,7 @@
         <v>182.6</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" t="s">
         <v>355</v>
       </c>
@@ -10359,7 +10358,7 @@
         <v>183.6</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" t="s">
         <v>356</v>
       </c>
@@ -10382,7 +10381,7 @@
         <v>183.9</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" t="s">
         <v>357</v>
       </c>
@@ -10405,7 +10404,7 @@
         <v>183.2</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" t="s">
         <v>358</v>
       </c>
@@ -10428,7 +10427,7 @@
         <v>182.9</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" t="s">
         <v>359</v>
       </c>
@@ -10451,7 +10450,7 @@
         <v>183.1</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" t="s">
         <v>360</v>
       </c>
@@ -10474,7 +10473,7 @@
         <v>183.7</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" t="s">
         <v>361</v>
       </c>
@@ -10497,7 +10496,7 @@
         <v>184.5</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" t="s">
         <v>362</v>
       </c>
@@ -10520,7 +10519,7 @@
         <v>185.1</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" t="s">
         <v>363</v>
       </c>
@@ -10543,7 +10542,7 @@
         <v>184.9</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" t="s">
         <v>364</v>
       </c>
@@ -10566,7 +10565,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" t="s">
         <v>365</v>
       </c>
@@ -10589,7 +10588,7 @@
         <v>185.5</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" t="s">
         <v>366</v>
       </c>
@@ -10612,7 +10611,7 @@
         <v>186.3</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" t="s">
         <v>367</v>
       </c>
@@ -10635,7 +10634,7 @@
         <v>186.7</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" t="s">
         <v>368</v>
       </c>
@@ -10658,7 +10657,7 @@
         <v>187.1</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" t="s">
         <v>369</v>
       </c>
@@ -10681,7 +10680,7 @@
         <v>187.4</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" t="s">
         <v>370</v>
       </c>
@@ -10704,7 +10703,7 @@
         <v>188.2</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" t="s">
         <v>371</v>
       </c>
@@ -10727,7 +10726,7 @@
         <v>188.9</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" t="s">
         <v>372</v>
       </c>
@@ -10750,7 +10749,7 @@
         <v>189.1</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" t="s">
         <v>373</v>
       </c>
@@ -10773,7 +10772,7 @@
         <v>189.2</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" t="s">
         <v>374</v>
       </c>
@@ -10796,7 +10795,7 @@
         <v>189.8</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" t="s">
         <v>375</v>
       </c>
@@ -10819,7 +10818,7 @@
         <v>190.8</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" t="s">
         <v>376</v>
       </c>
@@ -10842,7 +10841,7 @@
         <v>191.7</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" t="s">
         <v>377</v>
       </c>
@@ -10865,7 +10864,7 @@
         <v>191.7</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" t="s">
         <v>378</v>
       </c>
@@ -10888,7 +10887,7 @@
         <v>191.6</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" t="s">
         <v>379</v>
       </c>
@@ -10911,7 +10910,7 @@
         <v>192.4</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" t="s">
         <v>380</v>
       </c>
@@ -10934,7 +10933,7 @@
         <v>193.1</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" t="s">
         <v>381</v>
       </c>
@@ -10957,7 +10956,7 @@
         <v>193.7</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" t="s">
         <v>382</v>
       </c>
@@ -10980,7 +10979,7 @@
         <v>193.6</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" t="s">
         <v>383</v>
       </c>
@@ -11003,7 +11002,7 @@
         <v>193.7</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" t="s">
         <v>384</v>
       </c>
@@ -11026,7 +11025,7 @@
         <v>194.9</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" t="s">
         <v>385</v>
       </c>
@@ -11049,7 +11048,7 @@
         <v>196.1</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" t="s">
         <v>386</v>
       </c>
@@ -11072,7 +11071,7 @@
         <v>198.8</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" t="s">
         <v>387</v>
       </c>
@@ -11095,7 +11094,7 @@
         <v>199.1</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" t="s">
         <v>388</v>
       </c>
@@ -11118,7 +11117,7 @@
         <v>198.1</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" t="s">
         <v>389</v>
       </c>
@@ -11141,7 +11140,7 @@
         <v>198.1</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" t="s">
         <v>390</v>
       </c>
@@ -11164,7 +11163,7 @@
         <v>199.3</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" t="s">
         <v>391</v>
       </c>
@@ -11187,7 +11186,7 @@
         <v>199.4</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" t="s">
         <v>392</v>
       </c>
@@ -11210,7 +11209,7 @@
         <v>199.7</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" t="s">
         <v>393</v>
       </c>
@@ -11233,7 +11232,7 @@
         <v>200.7</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" t="s">
         <v>394</v>
       </c>
@@ -11256,7 +11255,7 @@
         <v>201.3</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" t="s">
         <v>395</v>
       </c>
@@ -11279,7 +11278,7 @@
         <v>201.8</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" t="s">
         <v>396</v>
       </c>
@@ -11302,7 +11301,7 @@
         <v>202.9</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" t="s">
         <v>397</v>
       </c>
@@ -11325,7 +11324,7 @@
         <v>203.8</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" t="s">
         <v>398</v>
       </c>
@@ -11348,7 +11347,7 @@
         <v>202.8</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" t="s">
         <v>399</v>
       </c>
@@ -11371,7 +11370,7 @@
         <v>201.9</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" t="s">
         <v>400</v>
       </c>
@@ -11394,7 +11393,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" t="s">
         <v>401</v>
       </c>
@@ -11417,7 +11416,7 @@
         <v>203.1</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" t="s">
         <v>402</v>
       </c>
@@ -11440,7 +11439,7 @@
         <v>203.43700000000001</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" t="s">
         <v>403</v>
       </c>
@@ -11463,7 +11462,7 @@
         <v>204.226</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" t="s">
         <v>404</v>
       </c>
@@ -11486,7 +11485,7 @@
         <v>205.28800000000001</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" t="s">
         <v>405</v>
       </c>
@@ -11509,7 +11508,7 @@
         <v>205.904</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" t="s">
         <v>406</v>
       </c>
@@ -11532,7 +11531,7 @@
         <v>206.755</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" t="s">
         <v>407</v>
       </c>
@@ -11555,7 +11554,7 @@
         <v>207.23400000000001</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" t="s">
         <v>408</v>
       </c>
@@ -11578,7 +11577,7 @@
         <v>207.60300000000001</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" t="s">
         <v>409</v>
       </c>
@@ -11601,7 +11600,7 @@
         <v>207.667</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" t="s">
         <v>410</v>
       </c>
@@ -11624,7 +11623,7 @@
         <v>208.547</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" t="s">
         <v>411</v>
       </c>
@@ -11647,7 +11646,7 @@
         <v>209.19</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" t="s">
         <v>412</v>
       </c>
@@ -11670,7 +11669,7 @@
         <v>210.834</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" t="s">
         <v>413</v>
       </c>
@@ -11693,7 +11692,7 @@
         <v>211.44499999999999</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" t="s">
         <v>414</v>
       </c>
@@ -11716,7 +11715,7 @@
         <v>212.17400000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A411" t="s">
         <v>415</v>
       </c>
@@ -11739,7 +11738,7 @@
         <v>212.68700000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A412" t="s">
         <v>416</v>
       </c>
@@ -11762,7 +11761,7 @@
         <v>213.44800000000001</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A413" t="s">
         <v>417</v>
       </c>
@@ -11785,7 +11784,7 @@
         <v>213.94200000000001</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A414" t="s">
         <v>418</v>
       </c>
@@ -11808,7 +11807,7 @@
         <v>215.208</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A415" t="s">
         <v>419</v>
       </c>
@@ -11831,7 +11830,7 @@
         <v>217.46299999999999</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A416" t="s">
         <v>420</v>
       </c>
@@ -11854,7 +11853,7 @@
         <v>219.01599999999999</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A417" t="s">
         <v>421</v>
       </c>
@@ -11877,7 +11876,7 @@
         <v>218.69</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A418" t="s">
         <v>422</v>
       </c>
@@ -11900,7 +11899,7 @@
         <v>218.87700000000001</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A419" t="s">
         <v>423</v>
       </c>
@@ -11923,7 +11922,7 @@
         <v>216.995</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A420" t="s">
         <v>424</v>
       </c>
@@ -11946,7 +11945,7 @@
         <v>213.15299999999999</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A421" t="s">
         <v>425</v>
       </c>
@@ -11969,7 +11968,7 @@
         <v>211.398</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A422" t="s">
         <v>426</v>
       </c>
@@ -11992,7 +11991,7 @@
         <v>211.93299999999999</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A423" t="s">
         <v>427</v>
       </c>
@@ -12015,7 +12014,7 @@
         <v>212.70500000000001</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A424" t="s">
         <v>428</v>
       </c>
@@ -12038,7 +12037,7 @@
         <v>212.495</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A425" t="s">
         <v>429</v>
       </c>
@@ -12061,7 +12060,7 @@
         <v>212.709</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A426" t="s">
         <v>430</v>
       </c>
@@ -12084,7 +12083,7 @@
         <v>213.02199999999999</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A427" t="s">
         <v>431</v>
       </c>
@@ -12107,7 +12106,7 @@
         <v>214.79</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A428" t="s">
         <v>432</v>
       </c>
@@ -12130,7 +12129,7 @@
         <v>214.726</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A429" t="s">
         <v>433</v>
       </c>
@@ -12153,7 +12152,7 @@
         <v>215.44499999999999</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A430" t="s">
         <v>434</v>
       </c>
@@ -12176,7 +12175,7 @@
         <v>215.86099999999999</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A431" t="s">
         <v>435</v>
       </c>
@@ -12199,7 +12198,7 @@
         <v>216.50899999999999</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A432" t="s">
         <v>436</v>
       </c>
@@ -12222,7 +12221,7 @@
         <v>217.23400000000001</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A433" t="s">
         <v>437</v>
       </c>
@@ -12245,7 +12244,7 @@
         <v>217.34700000000001</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A434" t="s">
         <v>438</v>
       </c>
@@ -12268,7 +12267,7 @@
         <v>217.488</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A435" t="s">
         <v>439</v>
       </c>
@@ -12291,7 +12290,7 @@
         <v>217.28100000000001</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A436" t="s">
         <v>440</v>
       </c>
@@ -12314,7 +12313,7 @@
         <v>217.35300000000001</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A437" t="s">
         <v>441</v>
       </c>
@@ -12337,7 +12336,7 @@
         <v>217.40299999999999</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A438" t="s">
         <v>442</v>
       </c>
@@ -12360,7 +12359,7 @@
         <v>217.29</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A439" t="s">
         <v>443</v>
       </c>
@@ -12383,7 +12382,7 @@
         <v>217.19900000000001</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A440" t="s">
         <v>444</v>
       </c>
@@ -12406,7 +12405,7 @@
         <v>217.60499999999999</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A441" t="s">
         <v>445</v>
       </c>
@@ -12429,7 +12428,7 @@
         <v>217.923</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A442" t="s">
         <v>446</v>
       </c>
@@ -12452,7 +12451,7 @@
         <v>218.27500000000001</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A443" t="s">
         <v>447</v>
       </c>
@@ -12475,7 +12474,7 @@
         <v>219.035</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A444" t="s">
         <v>448</v>
       </c>
@@ -12498,7 +12497,7 @@
         <v>219.59</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A445" t="s">
         <v>449</v>
       </c>
@@ -12521,7 +12520,7 @@
         <v>220.47200000000001</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A446" t="s">
         <v>450</v>
       </c>
@@ -12544,7 +12543,7 @@
         <v>221.18700000000001</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A447" t="s">
         <v>451</v>
       </c>
@@ -12567,7 +12566,7 @@
         <v>221.898</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A448" t="s">
         <v>452</v>
       </c>
@@ -12590,7 +12589,7 @@
         <v>223.04599999999999</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A449" t="s">
         <v>453</v>
       </c>
@@ -12613,7 +12612,7 @@
         <v>224.09299999999999</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A450" t="s">
         <v>454</v>
       </c>
@@ -12636,7 +12635,7 @@
         <v>224.80600000000001</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A451" t="s">
         <v>455</v>
       </c>
@@ -12659,7 +12658,7 @@
         <v>224.80600000000001</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A452" t="s">
         <v>456</v>
       </c>
@@ -12682,7 +12681,7 @@
         <v>225.39500000000001</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A453" t="s">
         <v>457</v>
       </c>
@@ -12705,7 +12704,7 @@
         <v>226.10599999999999</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A454" t="s">
         <v>458</v>
       </c>
@@ -12728,7 +12727,7 @@
         <v>226.59700000000001</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A455" t="s">
         <v>459</v>
       </c>
@@ -12751,7 +12750,7 @@
         <v>226.75</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A456" t="s">
         <v>460</v>
       </c>
@@ -12774,7 +12773,7 @@
         <v>227.16900000000001</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A457" t="s">
         <v>461</v>
       </c>
@@ -12797,7 +12796,7 @@
         <v>227.22300000000001</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A458" t="s">
         <v>462</v>
       </c>
@@ -12820,7 +12819,7 @@
         <v>227.84200000000001</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A459" t="s">
         <v>463</v>
       </c>
@@ -12843,7 +12842,7 @@
         <v>228.32900000000001</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A460" t="s">
         <v>464</v>
       </c>
@@ -12866,7 +12865,7 @@
         <v>228.80699999999999</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A461" t="s">
         <v>465</v>
       </c>
@@ -12889,7 +12888,7 @@
         <v>229.18700000000001</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A462" t="s">
         <v>466</v>
       </c>
@@ -12912,7 +12911,7 @@
         <v>228.71299999999999</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A463" t="s">
         <v>467</v>
       </c>
@@ -12935,7 +12934,7 @@
         <v>228.524</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A464" t="s">
         <v>468</v>
       </c>
@@ -12958,7 +12957,7 @@
         <v>228.59</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A465" t="s">
         <v>469</v>
       </c>
@@ -12981,7 +12980,7 @@
         <v>229.91800000000001</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A466" t="s">
         <v>470</v>
       </c>
@@ -13004,7 +13003,7 @@
         <v>231.01499999999999</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A467" t="s">
         <v>471</v>
       </c>
@@ -13027,7 +13026,7 @@
         <v>231.63800000000001</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A468" t="s">
         <v>472</v>
       </c>
@@ -13050,7 +13049,7 @@
         <v>231.249</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A469" t="s">
         <v>473</v>
       </c>
@@ -13073,7 +13072,7 @@
         <v>231.221</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A470" t="s">
         <v>474</v>
       </c>
@@ -13096,7 +13095,7 @@
         <v>231.679</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A471" t="s">
         <v>475</v>
       </c>
@@ -13119,7 +13118,7 @@
         <v>232.93700000000001</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A472" t="s">
         <v>476</v>
       </c>
@@ -13142,7 +13141,7 @@
         <v>232.28200000000001</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A473" t="s">
         <v>477</v>
       </c>
@@ -13165,7 +13164,7 @@
         <v>231.797</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A474" t="s">
         <v>478</v>
       </c>
@@ -13188,7 +13187,7 @@
         <v>231.893</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A475" t="s">
         <v>479</v>
       </c>
@@ -13211,7 +13210,7 @@
         <v>232.44499999999999</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A476" t="s">
         <v>480</v>
       </c>
@@ -13234,7 +13233,7 @@
         <v>232.9</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A477" t="s">
         <v>481</v>
       </c>
@@ -13257,7 +13256,7 @@
         <v>233.45599999999999</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A478" t="s">
         <v>482</v>
       </c>
@@ -13280,7 +13279,7 @@
         <v>233.54400000000001</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A479" t="s">
         <v>483</v>
       </c>
@@ -13303,7 +13302,7 @@
         <v>233.66900000000001</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A480" t="s">
         <v>484</v>
       </c>
@@ -13326,7 +13325,7 @@
         <v>234.1</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A481" t="s">
         <v>485</v>
       </c>
@@ -13349,7 +13348,7 @@
         <v>234.71899999999999</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A482" t="s">
         <v>486</v>
       </c>
@@ -13372,7 +13371,7 @@
         <v>235.28800000000001</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A483" t="s">
         <v>487</v>
       </c>
@@ -13395,7 +13394,7 @@
         <v>235.547</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A484" t="s">
         <v>488</v>
       </c>
@@ -13418,7 +13417,7 @@
         <v>236.02799999999999</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A485" t="s">
         <v>489</v>
       </c>
@@ -13441,7 +13440,7 @@
         <v>236.46799999999999</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A486" t="s">
         <v>490</v>
       </c>
@@ -13464,7 +13463,7 @@
         <v>236.91800000000001</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A487" t="s">
         <v>491</v>
       </c>
@@ -13487,7 +13486,7 @@
         <v>237.23099999999999</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A488" t="s">
         <v>492</v>
       </c>
@@ -13510,7 +13509,7 @@
         <v>237.49799999999999</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A489" t="s">
         <v>493</v>
       </c>
@@ -13533,7 +13532,7 @@
         <v>237.46</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A490" t="s">
         <v>494</v>
       </c>
@@ -13556,7 +13555,7 @@
         <v>237.477</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A491" t="s">
         <v>495</v>
       </c>
@@ -13579,7 +13578,7 @@
         <v>237.43</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A492" t="s">
         <v>496</v>
       </c>
@@ -13602,7 +13601,7 @@
         <v>236.983</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A493" t="s">
         <v>497</v>
       </c>
@@ -13625,7 +13624,7 @@
         <v>236.25200000000001</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A494" t="s">
         <v>498</v>
       </c>
@@ -13648,7 +13647,7 @@
         <v>234.74700000000001</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A495" t="s">
         <v>499</v>
       </c>
@@ -13671,7 +13670,7 @@
         <v>235.34200000000001</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A496" t="s">
         <v>500</v>
       </c>
@@ -13694,7 +13693,7 @@
         <v>235.976</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A497" t="s">
         <v>501</v>
       </c>
@@ -13717,7 +13716,7 @@
         <v>236.22200000000001</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A498" t="s">
         <v>502</v>
       </c>
@@ -13740,7 +13739,7 @@
         <v>237.001</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A499" t="s">
         <v>503</v>
       </c>
@@ -13763,7 +13762,7 @@
         <v>237.65700000000001</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A500" t="s">
         <v>504</v>
       </c>
@@ -13786,7 +13785,7 @@
         <v>238.03399999999999</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A501" t="s">
         <v>505</v>
       </c>
@@ -13809,7 +13808,7 @@
         <v>238.03299999999999</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A502" t="s">
         <v>506</v>
       </c>
@@ -13832,7 +13831,7 @@
         <v>237.49799999999999</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A503" t="s">
         <v>507</v>
       </c>
@@ -13855,7 +13854,7 @@
         <v>237.733</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A504" t="s">
         <v>508</v>
       </c>
@@ -13878,7 +13877,7 @@
         <v>238.017</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A505" t="s">
         <v>509</v>
       </c>
@@ -13901,7 +13900,7 @@
         <v>237.761</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A506" t="s">
         <v>510</v>
       </c>
@@ -13924,7 +13923,7 @@
         <v>237.65199999999999</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A507" t="s">
         <v>511</v>
       </c>
@@ -13947,7 +13946,7 @@
         <v>237.33600000000001</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A508" t="s">
         <v>512</v>
       </c>
@@ -13970,7 +13969,7 @@
         <v>238.08</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A509" t="s">
         <v>513</v>
       </c>
@@ -13993,7 +13992,7 @@
         <v>238.99199999999999</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A510" t="s">
         <v>514</v>
       </c>
@@ -14016,7 +14015,7 @@
         <v>239.55699999999999</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A511" t="s">
         <v>515</v>
       </c>
@@ -14039,7 +14038,7 @@
         <v>240.22200000000001</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A512" t="s">
         <v>516</v>
       </c>
@@ -14062,7 +14061,7 @@
         <v>240.101</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A513" t="s">
         <v>517</v>
       </c>
@@ -14085,7 +14084,7 @@
         <v>240.54499999999999</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A514" t="s">
         <v>518</v>
       </c>
@@ -14108,7 +14107,7 @@
         <v>241.17599999999999</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A515" t="s">
         <v>519</v>
       </c>
@@ -14131,7 +14130,7 @@
         <v>241.74100000000001</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A516" t="s">
         <v>520</v>
       </c>
@@ -14154,7 +14153,7 @@
         <v>242.02600000000001</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A517" t="s">
         <v>521</v>
       </c>
@@ -14177,7 +14176,7 @@
         <v>242.637</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A518" t="s">
         <v>522</v>
       </c>
@@ -14200,7 +14199,7 @@
         <v>243.61799999999999</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A519" t="s">
         <v>523</v>
       </c>
@@ -14223,7 +14222,7 @@
         <v>244.006</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A520" t="s">
         <v>524</v>
       </c>
@@ -14246,7 +14245,7 @@
         <v>243.892</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A521" t="s">
         <v>525</v>
       </c>
@@ -14269,7 +14268,7 @@
         <v>244.19300000000001</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A522" t="s">
         <v>526</v>
       </c>
@@ -14292,7 +14291,7 @@
         <v>244.00399999999999</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A523" t="s">
         <v>527</v>
       </c>
@@ -14315,7 +14314,7 @@
         <v>244.16300000000001</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A524" t="s">
         <v>528</v>
       </c>
@@ -14338,7 +14337,7 @@
         <v>244.24299999999999</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A525" t="s">
         <v>529</v>
       </c>
@@ -14361,7 +14360,7 @@
         <v>245.18299999999999</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A526" t="s">
         <v>530</v>
       </c>
@@ -14384,7 +14383,7 @@
         <v>246.435</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A527" t="s">
         <v>531</v>
       </c>
@@ -14407,7 +14406,7 @@
         <v>246.626</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A528" t="s">
         <v>532</v>
       </c>
@@ -14430,7 +14429,7 @@
         <v>247.28399999999999</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A529" t="s">
         <v>533</v>
       </c>
@@ -14453,7 +14452,7 @@
         <v>247.80500000000001</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A530" t="s">
         <v>534</v>
       </c>
@@ -14476,7 +14475,7 @@
         <v>248.85900000000001</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A531" t="s">
         <v>535</v>
       </c>
@@ -14499,7 +14498,7 @@
         <v>249.529</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A532" t="s">
         <v>536</v>
       </c>
@@ -14522,7 +14521,7 @@
         <v>249.577</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A533" t="s">
         <v>537</v>
       </c>
@@ -14545,7 +14544,7 @@
         <v>250.227</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A534" t="s">
         <v>538</v>
       </c>
@@ -14568,7 +14567,7 @@
         <v>250.792</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A535" t="s">
         <v>539</v>
       </c>
@@ -14591,7 +14590,7 @@
         <v>251.018</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A536" t="s">
         <v>540</v>
       </c>
@@ -14614,7 +14613,7 @@
         <v>251.214</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A537" t="s">
         <v>541</v>
       </c>
@@ -14637,7 +14636,7 @@
         <v>251.66300000000001</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A538" t="s">
         <v>542</v>
       </c>
@@ -14660,7 +14659,7 @@
         <v>252.18199999999999</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A539" t="s">
         <v>543</v>
       </c>
@@ -14683,7 +14682,7 @@
         <v>252.77199999999999</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A540" t="s">
         <v>544</v>
       </c>
@@ -14706,7 +14705,7 @@
         <v>252.59399999999999</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A541" t="s">
         <v>545</v>
       </c>
@@ -14729,7 +14728,7 @@
         <v>252.767</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A542" t="s">
         <v>546</v>
       </c>
@@ -14752,7 +14751,7 @@
         <v>252.56100000000001</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A543" t="s">
         <v>547</v>
       </c>
@@ -14775,7 +14774,7 @@
         <v>253.31899999999999</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A544" t="s">
         <v>548</v>
       </c>
@@ -14798,7 +14797,7 @@
         <v>254.27699999999999</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A545" t="s">
         <v>549</v>
       </c>
@@ -14821,7 +14820,7 @@
         <v>255.233</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A546" t="s">
         <v>550</v>
       </c>
@@ -14844,7 +14843,7 @@
         <v>255.29599999999999</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A547" t="s">
         <v>551</v>
       </c>
@@ -14867,7 +14866,7 @@
         <v>255.21299999999999</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A548" t="s">
         <v>552</v>
       </c>
@@ -14890,7 +14889,7 @@
         <v>255.80199999999999</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A549" t="s">
         <v>553</v>
       </c>
@@ -14913,7 +14912,7 @@
         <v>256.036</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A550" t="s">
         <v>554</v>
       </c>
@@ -14936,7 +14935,7 @@
         <v>256.43</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A551" t="s">
         <v>555</v>
       </c>
@@ -14959,7 +14958,7 @@
         <v>257.15499999999997</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A552" t="s">
         <v>556</v>
       </c>
@@ -14982,7 +14981,7 @@
         <v>257.87900000000002</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A553" t="s">
         <v>557</v>
       </c>
@@ -15005,7 +15004,7 @@
         <v>258.63</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A554" t="s">
         <v>558</v>
       </c>
@@ -15028,7 +15027,7 @@
         <v>259.12700000000001</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A555" t="s">
         <v>559</v>
       </c>
@@ -15051,7 +15050,7 @@
         <v>259.25</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A556" t="s">
         <v>560</v>
       </c>
@@ -15074,7 +15073,7 @@
         <v>258.07600000000002</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A557" t="s">
         <v>561</v>
       </c>
@@ -15097,7 +15096,7 @@
         <v>256.03199999999998</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A558" t="s">
         <v>562</v>
       </c>
@@ -15120,7 +15119,7 @@
         <v>255.80199999999999</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A559" t="s">
         <v>563</v>
       </c>
@@ -15143,7 +15142,7 @@
         <v>257.04199999999997</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A560" t="s">
         <v>564</v>
       </c>
@@ -15166,7 +15165,7 @@
         <v>258.35199999999998</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A561" t="s">
         <v>565</v>
       </c>
@@ -15189,7 +15188,7 @@
         <v>259.31599999999997</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A562" t="s">
         <v>566</v>
       </c>
@@ -15212,7 +15211,7 @@
         <v>259.99700000000001</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A563" t="s">
         <v>567</v>
       </c>
@@ -15235,7 +15234,7 @@
         <v>260.31900000000002</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A564" t="s">
         <v>568</v>
       </c>
@@ -15258,7 +15257,7 @@
         <v>260.911</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A565" t="s">
         <v>569</v>
       </c>
@@ -15281,7 +15280,7 @@
         <v>262.04500000000002</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A566" t="s">
         <v>570</v>
       </c>
@@ -15304,7 +15303,7 @@
         <v>262.63900000000001</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A567" t="s">
         <v>571</v>
       </c>
@@ -15327,7 +15326,7 @@
         <v>263.57299999999998</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A568" t="s">
         <v>572</v>
       </c>
@@ -15350,7 +15349,7 @@
         <v>264.84699999999998</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A569" t="s">
         <v>573</v>
       </c>
@@ -15373,7 +15372,7 @@
         <v>266.625</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A570" t="s">
         <v>574</v>
       </c>
@@ -15396,7 +15395,7 @@
         <v>268.404</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A571" t="s">
         <v>575</v>
       </c>
@@ -15419,7 +15418,7 @@
         <v>270.70999999999998</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A572" t="s">
         <v>576</v>
       </c>
@@ -15442,7 +15441,7 @@
         <v>271.96499999999997</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A573" t="s">
         <v>577</v>
       </c>
@@ -15465,7 +15464,7 @@
         <v>272.75200000000001</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A574" t="s">
         <v>578</v>
       </c>
@@ -15488,7 +15487,7 @@
         <v>273.94200000000001</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A575" t="s">
         <v>579</v>
       </c>
@@ -15511,7 +15510,7 @@
         <v>276.52800000000002</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A576" t="s">
         <v>580</v>
       </c>
@@ -15534,7 +15533,7 @@
         <v>278.82400000000001</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A577" t="s">
         <v>581</v>
       </c>
@@ -15557,7 +15556,7 @@
         <v>280.80599999999998</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A578" t="s">
         <v>582</v>
       </c>
@@ -15580,7 +15579,7 @@
         <v>282.54199999999997</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A579" t="s">
         <v>583</v>
       </c>
@@ -15603,7 +15602,7 @@
         <v>284.52499999999998</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A580" t="s">
         <v>584</v>
       </c>
@@ -15626,7 +15625,7 @@
         <v>287.46699999999998</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A581" t="s">
         <v>585</v>
       </c>
@@ -15649,7 +15648,7 @@
         <v>288.58199999999999</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A582" t="s">
         <v>586</v>
       </c>
@@ -15672,7 +15671,7 @@
         <v>291.29899999999998</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A583" t="s">
         <v>587</v>
       </c>
@@ -15695,7 +15694,7 @@
         <v>295.072</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A584" t="s">
         <v>588</v>
       </c>
@@ -15718,7 +15717,7 @@
         <v>294.94</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A585" t="s">
         <v>589</v>
       </c>
@@ -15741,7 +15740,7 @@
         <v>295.16199999999998</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A586" t="s">
         <v>590</v>
       </c>
@@ -15764,7 +15763,7 @@
         <v>296.42099999999999</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A587" t="s">
         <v>591</v>
       </c>
@@ -15787,7 +15786,7 @@
         <v>297.97899999999998</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A588" t="s">
         <v>592</v>
       </c>
@@ -15810,7 +15809,7 @@
         <v>298.70800000000003</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A589" t="s">
         <v>593</v>
       </c>
@@ -15833,7 +15832,7 @@
         <v>298.80799999999999</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A590" t="s">
         <v>594</v>
       </c>
@@ -15856,7 +15855,7 @@
         <v>300.45600000000002</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A591" t="s">
         <v>595</v>
       </c>
@@ -15879,7 +15878,7 @@
         <v>301.476</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A592" t="s">
         <v>596</v>
       </c>
@@ -15902,7 +15901,7 @@
         <v>301.64299999999997</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A593" t="s">
         <v>597</v>
       </c>
@@ -15925,7 +15924,7 @@
         <v>302.858</v>
       </c>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A594" t="s">
         <v>598</v>
       </c>
@@ -15948,7 +15947,7 @@
         <v>303.31599999999997</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A595" t="s">
         <v>599</v>
       </c>
@@ -15971,7 +15970,7 @@
         <v>304.09899999999999</v>
       </c>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A596" t="s">
         <v>600</v>
       </c>
@@ -15994,7 +15993,7 @@
         <v>304.61500000000001</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A597" t="s">
         <v>601</v>
       </c>
@@ -16017,7 +16016,7 @@
         <v>306.13799999999998</v>
       </c>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A598" t="s">
         <v>602</v>
       </c>
@@ -16040,7 +16039,7 @@
         <v>307.37400000000002</v>
       </c>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A599" t="s">
         <v>603</v>
       </c>
@@ -16063,7 +16062,7 @@
         <v>307.65300000000002</v>
       </c>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A600" t="s">
         <v>604</v>
       </c>
@@ -16086,7 +16085,7 @@
         <v>308.08699999999999</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A601" t="s">
         <v>605</v>
       </c>
@@ -16109,7 +16108,7 @@
         <v>308.73500000000001</v>
       </c>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A602" t="s">
         <v>606</v>
       </c>
@@ -16132,7 +16131,7 @@
         <v>309.79399999999998</v>
       </c>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A603" t="s">
         <v>607</v>
       </c>
@@ -16155,7 +16154,7 @@
         <v>311.02199999999999</v>
       </c>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A604" t="s">
         <v>608</v>
       </c>
@@ -16178,7 +16177,7 @@
         <v>312.10700000000003</v>
       </c>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A605" t="s">
         <v>609</v>
       </c>
@@ -16201,7 +16200,7 @@
         <v>313.01600000000002</v>
       </c>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A606" t="s">
         <v>610</v>
       </c>
@@ -16224,7 +16223,7 @@
         <v>313.14</v>
       </c>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A607" t="s">
         <v>611</v>
       </c>
@@ -16247,7 +16246,7 @@
         <v>313.13099999999997</v>
       </c>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A608" t="s">
         <v>612</v>
       </c>
@@ -16270,7 +16269,7 @@
         <v>313.56599999999997</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A609" t="s">
         <v>613</v>
       </c>
@@ -16293,7 +16292,7 @@
         <v>314.13099999999997</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A610" t="s">
         <v>614</v>
       </c>
@@ -16316,7 +16315,7 @@
         <v>314.851</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A611" t="s">
         <v>615</v>
       </c>
@@ -16339,7 +16338,7 @@
         <v>315.56400000000002</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A612" t="s">
         <v>616</v>
       </c>
@@ -16362,7 +16361,7 @@
         <v>316.44900000000001</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A613" t="s">
         <v>617</v>
       </c>
@@ -16385,7 +16384,7 @@
         <v>317.60300000000001</v>
       </c>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A614" t="s">
         <v>618</v>
       </c>
@@ -16408,7 +16407,7 @@
         <v>319.08600000000001</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A615" t="s">
         <v>619</v>
       </c>
@@ -16431,7 +16430,7 @@
         <v>319.77499999999998</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A616" t="s">
         <v>620</v>
       </c>
@@ -16454,7 +16453,7 @@
         <v>319.61500000000001</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A617" t="s">
         <v>621</v>
       </c>
@@ -16477,7 +16476,7 @@
         <v>320.32100000000003</v>
       </c>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A618" t="s">
         <v>622</v>
       </c>
@@ -16500,7 +16499,7 @@
         <v>320.58</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A619" t="s">
         <v>623</v>
       </c>

--- a/VARdata.xlsx
+++ b/VARdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/drk9452_ads_northwestern_edu/Documents/Uni/LBS PhD/Research/Projects/Oil supply shocks/Repositories/OilSupplyNewsUpdate/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{E4666CA9-3A26-40FF-83AF-CBD9E073F10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{383DACD1-2472-465F-BF77-91C183A4CCEF}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{E4666CA9-3A26-40FF-83AF-CBD9E073F10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A21402BA-0A7F-436B-8A9E-0757ED017392}"/>
   <bookViews>
-    <workbookView xWindow="86280" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E64FA3D6-CEF8-4D84-93AC-D7CE42D05F79}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E64FA3D6-CEF8-4D84-93AC-D7CE42D05F79}"/>
   </bookViews>
   <sheets>
     <sheet name="Monthly" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="631">
   <si>
     <t>POIL</t>
   </si>
@@ -1911,6 +1911,24 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>2025M07</t>
+  </si>
+  <si>
+    <t>2025M08</t>
+  </si>
+  <si>
+    <t>2025M09</t>
+  </si>
+  <si>
+    <t>2025M10</t>
+  </si>
+  <si>
+    <t>2025M11</t>
+  </si>
+  <si>
+    <t>2025M12</t>
   </si>
 </sst>
 </file>
@@ -2282,7 +2300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12E1CFC8-D9C0-4308-945A-68684190B2E6}">
-  <dimension ref="A1:G619"/>
+  <dimension ref="A1:G625"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -9288,7 +9306,7 @@
         <v>65495.8</v>
       </c>
       <c r="D305">
-        <v>2211.29806813604</v>
+        <v>2211.29806813605</v>
       </c>
       <c r="E305">
         <v>81.197329999999994</v>
@@ -9380,7 +9398,7 @@
         <v>65664.25</v>
       </c>
       <c r="D309">
-        <v>2217.3170949144601</v>
+        <v>2217.3170949144501</v>
       </c>
       <c r="E309">
         <v>82.928759999999997</v>
@@ -9403,7 +9421,7 @@
         <v>65708.44</v>
       </c>
       <c r="D310">
-        <v>2203.5689150129101</v>
+        <v>2203.5689150128801</v>
       </c>
       <c r="E310">
         <v>83.467060000000004</v>
@@ -9426,7 +9444,7 @@
         <v>66214.94</v>
       </c>
       <c r="D311">
-        <v>2195.96091821457</v>
+        <v>2195.9609182145</v>
       </c>
       <c r="E311">
         <v>83.950220000000002</v>
@@ -9449,7 +9467,7 @@
         <v>66194.06</v>
       </c>
       <c r="D312">
-        <v>2183.2736513333898</v>
+        <v>2183.2736513332902</v>
       </c>
       <c r="E312">
         <v>84.743189999999998</v>
@@ -9472,7 +9490,7 @@
         <v>65383.96</v>
       </c>
       <c r="D313">
-        <v>2178.7993225515502</v>
+        <v>2178.7993225514501</v>
       </c>
       <c r="E313">
         <v>85.532560000000004</v>
@@ -9495,7 +9513,7 @@
         <v>66449.88</v>
       </c>
       <c r="D314">
-        <v>2170.8562407787599</v>
+        <v>2170.8562407787399</v>
       </c>
       <c r="E314">
         <v>85.323189999999997</v>
@@ -9518,7 +9536,7 @@
         <v>67041.63</v>
       </c>
       <c r="D315">
-        <v>2175.6147332297501</v>
+        <v>2175.6147332298801</v>
       </c>
       <c r="E315">
         <v>85.634529999999998</v>
@@ -9541,7 +9559,7 @@
         <v>67073.56</v>
       </c>
       <c r="D316">
-        <v>2156.6293973929501</v>
+        <v>2156.6293973933698</v>
       </c>
       <c r="E316">
         <v>86.065070000000006</v>
@@ -9564,7 +9582,7 @@
         <v>67735.19</v>
       </c>
       <c r="D317">
-        <v>2154.8446319209802</v>
+        <v>2154.8446319217401</v>
       </c>
       <c r="E317">
         <v>86.918080000000003</v>
@@ -9587,7 +9605,7 @@
         <v>68247.25</v>
       </c>
       <c r="D318">
-        <v>2142.4075485993599</v>
+        <v>2142.4075486001502</v>
       </c>
       <c r="E318">
         <v>87.355999999999995</v>
@@ -9610,7 +9628,7 @@
         <v>68040.13</v>
       </c>
       <c r="D319">
-        <v>2153.0586370183901</v>
+        <v>2153.0586370187002</v>
       </c>
       <c r="E319">
         <v>87.443349999999995</v>
@@ -9633,7 +9651,7 @@
         <v>68665.06</v>
       </c>
       <c r="D320">
-        <v>2157.1370711309</v>
+        <v>2157.1370711303398</v>
       </c>
       <c r="E320">
         <v>87.759680000000003</v>
@@ -9656,7 +9674,7 @@
         <v>69491.88</v>
       </c>
       <c r="D321">
-        <v>2163.1070358065099</v>
+        <v>2163.1070358050401</v>
       </c>
       <c r="E321">
         <v>88.185360000000003</v>
@@ -9679,7 +9697,7 @@
         <v>69501.440000000002</v>
       </c>
       <c r="D322">
-        <v>2165.6827358302198</v>
+        <v>2165.6827358274199</v>
       </c>
       <c r="E322">
         <v>87.989270000000005</v>
@@ -9702,7 +9720,7 @@
         <v>69945.88</v>
       </c>
       <c r="D323">
-        <v>2152.3461267586699</v>
+        <v>2152.34612675574</v>
       </c>
       <c r="E323">
         <v>88.280940000000001</v>
@@ -9725,7 +9743,7 @@
         <v>70501.31</v>
       </c>
       <c r="D324">
-        <v>2159.4386929259699</v>
+        <v>2159.4386929238399</v>
       </c>
       <c r="E324">
         <v>88.602180000000004</v>
@@ -9748,7 +9766,7 @@
         <v>69239.88</v>
       </c>
       <c r="D325">
-        <v>2180.6370177027002</v>
+        <v>2180.6370177005301</v>
       </c>
       <c r="E325">
         <v>88.918909999999997</v>
@@ -9771,7 +9789,7 @@
         <v>69158.38</v>
       </c>
       <c r="D326">
-        <v>2149.3658438428502</v>
+        <v>2149.3658438392499</v>
       </c>
       <c r="E326">
         <v>87.723500000000001</v>
@@ -9794,7 +9812,7 @@
         <v>68689.75</v>
       </c>
       <c r="D327">
-        <v>2113.80788041184</v>
+        <v>2113.8078804081301</v>
       </c>
       <c r="E327">
         <v>88.453180000000003</v>
@@ -9817,7 +9835,7 @@
         <v>69352.19</v>
       </c>
       <c r="D328">
-        <v>2154.6656920908799</v>
+        <v>2154.6656920932301</v>
       </c>
       <c r="E328">
         <v>87.630679999999998</v>
@@ -9840,7 +9858,7 @@
         <v>68419.19</v>
       </c>
       <c r="D329">
-        <v>2178.87413201249</v>
+        <v>2178.8741320292102</v>
       </c>
       <c r="E329">
         <v>87.244709999999998</v>
@@ -9863,7 +9881,7 @@
         <v>67731.94</v>
       </c>
       <c r="D330">
-        <v>2162.8974506377199</v>
+        <v>2162.8974506794598</v>
       </c>
       <c r="E330">
         <v>87.226910000000004</v>
@@ -9886,7 +9904,7 @@
         <v>66173.25</v>
       </c>
       <c r="D331">
-        <v>2117.34371879018</v>
+        <v>2117.3437188552598</v>
       </c>
       <c r="E331">
         <v>87.014679999999998</v>
@@ -9909,7 +9927,7 @@
         <v>68112.56</v>
       </c>
       <c r="D332">
-        <v>2139.7228613776601</v>
+        <v>2139.7228614330602</v>
       </c>
       <c r="E332">
         <v>86.409419999999997</v>
@@ -9932,7 +9950,7 @@
         <v>68286.63</v>
       </c>
       <c r="D333">
-        <v>2152.4458184754799</v>
+        <v>2152.4458184642799</v>
       </c>
       <c r="E333">
         <v>86.883610000000004</v>
@@ -9955,7 +9973,7 @@
         <v>67814.69</v>
       </c>
       <c r="D334">
-        <v>2158.6244139106798</v>
+        <v>2158.6244137918802</v>
       </c>
       <c r="E334">
         <v>86.290890000000005</v>
@@ -9978,7 +9996,7 @@
         <v>67716.5</v>
       </c>
       <c r="D335">
-        <v>2161.0858806292099</v>
+        <v>2161.0858804304999</v>
       </c>
       <c r="E335">
         <v>86.007919999999999</v>
@@ -10001,7 +10019,7 @@
         <v>68069.63</v>
       </c>
       <c r="D336">
-        <v>2160.5675624978799</v>
+        <v>2160.5675622494</v>
       </c>
       <c r="E336">
         <v>85.776430000000005</v>
@@ -10024,7 +10042,7 @@
         <v>67653.31</v>
       </c>
       <c r="D337">
-        <v>2172.6545008112698</v>
+        <v>2172.6545006773299</v>
       </c>
       <c r="E337">
         <v>85.842770000000002</v>
@@ -10047,7 +10065,7 @@
         <v>66803.63</v>
       </c>
       <c r="D338">
-        <v>2186.7422871202798</v>
+        <v>2186.7422872437501</v>
       </c>
       <c r="E338">
         <v>86.752880000000005</v>
@@ -10070,7 +10088,7 @@
         <v>66897.13</v>
       </c>
       <c r="D339">
-        <v>2214.7571550347002</v>
+        <v>2214.7571554569599</v>
       </c>
       <c r="E339">
         <v>86.518349999999998</v>
@@ -10093,7 +10111,7 @@
         <v>66698.44</v>
       </c>
       <c r="D340">
-        <v>2200.4284291144099</v>
+        <v>2200.4284296148699</v>
       </c>
       <c r="E340">
         <v>87.361170000000001</v>
@@ -10116,7 +10134,7 @@
         <v>66176.75</v>
       </c>
       <c r="D341">
-        <v>2170.54246124579</v>
+        <v>2170.5424615449201</v>
       </c>
       <c r="E341">
         <v>87.974559999999997</v>
@@ -10139,7 +10157,7 @@
         <v>66750.559999999998</v>
       </c>
       <c r="D342">
-        <v>2193.6417587330702</v>
+        <v>2193.6417587266101</v>
       </c>
       <c r="E342">
         <v>88.308300000000003</v>
@@ -10162,7 +10180,7 @@
         <v>66606.81</v>
       </c>
       <c r="D343">
-        <v>2203.3106104992999</v>
+        <v>2203.3106102951201</v>
       </c>
       <c r="E343">
         <v>88.481049999999996</v>
@@ -10185,7 +10203,7 @@
         <v>67068.31</v>
       </c>
       <c r="D344">
-        <v>2189.79308935176</v>
+        <v>2189.7930890934399</v>
       </c>
       <c r="E344">
         <v>88.838800000000006</v>
@@ -10208,7 +10226,7 @@
         <v>66793.75</v>
       </c>
       <c r="D345">
-        <v>2195.27730817259</v>
+        <v>2195.2773078457299</v>
       </c>
       <c r="E345">
         <v>89.144130000000004</v>
@@ -10231,7 +10249,7 @@
         <v>67330.38</v>
       </c>
       <c r="D346">
-        <v>2157.2863197848201</v>
+        <v>2157.28631922155</v>
       </c>
       <c r="E346">
         <v>89.408810000000003</v>
@@ -10254,7 +10272,7 @@
         <v>68739.25</v>
       </c>
       <c r="D347">
-        <v>2203.7725490923899</v>
+        <v>2203.7725483568202</v>
       </c>
       <c r="E347">
         <v>89.506450000000001</v>
@@ -10277,7 +10295,7 @@
         <v>68837.19</v>
       </c>
       <c r="D348">
-        <v>2207.63788907655</v>
+        <v>2207.63788825552</v>
       </c>
       <c r="E348">
         <v>89.820520000000002</v>
@@ -10300,7 +10318,7 @@
         <v>67179.81</v>
       </c>
       <c r="D349">
-        <v>2207.4986781754601</v>
+        <v>2207.4986779843898</v>
       </c>
       <c r="E349">
         <v>89.514849999999996</v>
@@ -10323,7 +10341,7 @@
         <v>67722.06</v>
       </c>
       <c r="D350">
-        <v>2220.5258495669</v>
+        <v>2220.5258507312701</v>
       </c>
       <c r="E350">
         <v>90.516170000000002</v>
@@ -10346,7 +10364,7 @@
         <v>69312.38</v>
       </c>
       <c r="D351">
-        <v>2216.0744689901799</v>
+        <v>2216.0744713572299</v>
       </c>
       <c r="E351">
         <v>90.493579999999994</v>
@@ -10369,7 +10387,7 @@
         <v>69844.63</v>
       </c>
       <c r="D352">
-        <v>2240.9053067314899</v>
+        <v>2240.9053091176202</v>
       </c>
       <c r="E352">
         <v>90.541089999999997</v>
@@ -10392,7 +10410,7 @@
         <v>68764.63</v>
       </c>
       <c r="D353">
-        <v>2242.2133335499998</v>
+        <v>2242.2133344307499</v>
       </c>
       <c r="E353">
         <v>90.274919999999995</v>
@@ -10415,7 +10433,7 @@
         <v>68761.75</v>
       </c>
       <c r="D354">
-        <v>2229.7249011119202</v>
+        <v>2229.72490001297</v>
       </c>
       <c r="E354">
         <v>90.132419999999996</v>
@@ -10438,7 +10456,7 @@
         <v>67951.81</v>
       </c>
       <c r="D355">
-        <v>2247.8630552927202</v>
+        <v>2247.8630530001201</v>
       </c>
       <c r="E355">
         <v>90.549040000000005</v>
@@ -10461,7 +10479,7 @@
         <v>68570.63</v>
       </c>
       <c r="D356">
-        <v>2273.6396889907901</v>
+        <v>2273.6396867681001</v>
       </c>
       <c r="E356">
         <v>91.219329999999999</v>
@@ -10484,7 +10502,7 @@
         <v>69025.69</v>
       </c>
       <c r="D357">
-        <v>2281.5909970559101</v>
+        <v>2281.5909954422</v>
       </c>
       <c r="E357">
         <v>91.101550000000003</v>
@@ -10507,7 +10525,7 @@
         <v>69694.31</v>
       </c>
       <c r="D358">
-        <v>2303.9354567782402</v>
+        <v>2303.9354548092001</v>
       </c>
       <c r="E358">
         <v>91.965869999999995</v>
@@ -10530,7 +10548,7 @@
         <v>70598.75</v>
       </c>
       <c r="D359">
-        <v>2302.45398373328</v>
+        <v>2302.4539815002599</v>
       </c>
       <c r="E359">
         <v>92.80256</v>
@@ -10553,7 +10571,7 @@
         <v>70831.13</v>
       </c>
       <c r="D360">
-        <v>2308.39309416572</v>
+        <v>2308.3930929426901</v>
       </c>
       <c r="E360">
         <v>93.109260000000006</v>
@@ -10576,7 +10594,7 @@
         <v>72088.19</v>
       </c>
       <c r="D361">
-        <v>2315.3839728810399</v>
+        <v>2315.3839751594101</v>
       </c>
       <c r="E361">
         <v>93.794749999999993</v>
@@ -10599,7 +10617,7 @@
         <v>71775.75</v>
       </c>
       <c r="D362">
-        <v>2319.32593780241</v>
+        <v>2319.32594417682</v>
       </c>
       <c r="E362">
         <v>93.643230000000003</v>
@@ -10622,7 +10640,7 @@
         <v>71755.13</v>
       </c>
       <c r="D363">
-        <v>2334.8587221369798</v>
+        <v>2334.85873076599</v>
       </c>
       <c r="E363">
         <v>94.864930000000001</v>
@@ -10645,7 +10663,7 @@
         <v>71699.81</v>
       </c>
       <c r="D364">
-        <v>2326.5790674855998</v>
+        <v>2326.57908435737</v>
       </c>
       <c r="E364">
         <v>94.842579999999998</v>
@@ -10668,7 +10686,7 @@
         <v>71665.88</v>
       </c>
       <c r="D365">
-        <v>2343.8832286816801</v>
+        <v>2343.8832265390602</v>
       </c>
       <c r="E365">
         <v>95.461780000000005</v>
@@ -10691,7 +10709,7 @@
         <v>71341.94</v>
       </c>
       <c r="D366">
-        <v>2353.5361234817101</v>
+        <v>2353.5361131027198</v>
       </c>
       <c r="E366">
         <v>95.780320000000003</v>
@@ -10714,7 +10732,7 @@
         <v>72940.31</v>
       </c>
       <c r="D367">
-        <v>2359.3582600847299</v>
+        <v>2359.3582335709302</v>
       </c>
       <c r="E367">
         <v>95.707149999999999</v>
@@ -10737,7 +10755,7 @@
         <v>73397.06</v>
       </c>
       <c r="D368">
-        <v>2349.97526918228</v>
+        <v>2349.9752558068099</v>
       </c>
       <c r="E368">
         <v>96.365390000000005</v>
@@ -10760,7 +10778,7 @@
         <v>72367.31</v>
       </c>
       <c r="D369">
-        <v>2322.1672968418702</v>
+        <v>2322.16729310646</v>
       </c>
       <c r="E369">
         <v>96.41619</v>
@@ -10783,7 +10801,7 @@
         <v>72987.88</v>
       </c>
       <c r="D370">
-        <v>2338.96984911754</v>
+        <v>2338.9698542686201</v>
       </c>
       <c r="E370">
         <v>96.805130000000005</v>
@@ -10806,7 +10824,7 @@
         <v>73603.19</v>
       </c>
       <c r="D371">
-        <v>2359.4495404715599</v>
+        <v>2359.4495494002499</v>
       </c>
       <c r="E371">
         <v>97.240899999999996</v>
@@ -10829,7 +10847,7 @@
         <v>73264.88</v>
       </c>
       <c r="D372">
-        <v>2395.6512507815801</v>
+        <v>2395.6512599327798</v>
       </c>
       <c r="E372">
         <v>97.384119999999996</v>
@@ -10852,7 +10870,7 @@
         <v>72898.13</v>
       </c>
       <c r="D373">
-        <v>2377.5271222522101</v>
+        <v>2377.5271348431102</v>
       </c>
       <c r="E373">
         <v>97.728980000000007</v>
@@ -10875,7 +10893,7 @@
         <v>73182.5</v>
       </c>
       <c r="D374">
-        <v>2374.0060930692698</v>
+        <v>2374.0061100610201</v>
       </c>
       <c r="E374">
         <v>98.488140000000001</v>
@@ -10898,7 +10916,7 @@
         <v>73460.88</v>
       </c>
       <c r="D375">
-        <v>2367.6335515046999</v>
+        <v>2367.6335719599401</v>
       </c>
       <c r="E375">
         <v>98.547129999999996</v>
@@ -10921,7 +10939,7 @@
         <v>73775.38</v>
       </c>
       <c r="D376">
-        <v>2398.8338402193099</v>
+        <v>2398.83387603551</v>
       </c>
       <c r="E376">
         <v>98.779730000000001</v>
@@ -10944,7 +10962,7 @@
         <v>74067.88</v>
       </c>
       <c r="D377">
-        <v>2405.0889401989498</v>
+        <v>2405.0889320256701</v>
       </c>
       <c r="E377">
         <v>99.500789999999995</v>
@@ -10967,7 +10985,7 @@
         <v>74224.69</v>
       </c>
       <c r="D378">
-        <v>2430.9918301473099</v>
+        <v>2430.9917871614798</v>
       </c>
       <c r="E378">
         <v>99.127110000000002</v>
@@ -10990,7 +11008,7 @@
         <v>73843.19</v>
       </c>
       <c r="D379">
-        <v>2412.3788473234399</v>
+        <v>2412.3787455378201</v>
       </c>
       <c r="E379">
         <v>99.791139999999999</v>
@@ -11013,7 +11031,7 @@
         <v>73684.69</v>
       </c>
       <c r="D380">
-        <v>2429.4726274015702</v>
+        <v>2429.4725827791599</v>
       </c>
       <c r="E380">
         <v>99.880129999999994</v>
@@ -11036,7 +11054,7 @@
         <v>73727.19</v>
       </c>
       <c r="D381">
-        <v>2439.5060457683098</v>
+        <v>2439.5060412606299</v>
       </c>
       <c r="E381">
         <v>100.1999</v>
@@ -11059,7 +11077,7 @@
         <v>73286</v>
       </c>
       <c r="D382">
-        <v>2448.1865950348101</v>
+        <v>2448.18663474287</v>
       </c>
       <c r="E382">
         <v>100.28400000000001</v>
@@ -11082,7 +11100,7 @@
         <v>73381.56</v>
       </c>
       <c r="D383">
-        <v>2452.5904026411499</v>
+        <v>2452.59046426536</v>
       </c>
       <c r="E383">
         <v>100.8638</v>
@@ -11105,7 +11123,7 @@
         <v>73846.38</v>
       </c>
       <c r="D384">
-        <v>2446.6011751229598</v>
+        <v>2446.6012322953502</v>
       </c>
       <c r="E384">
         <v>101.93819999999999</v>
@@ -11128,7 +11146,7 @@
         <v>74132.56</v>
       </c>
       <c r="D385">
-        <v>2455.2765654711902</v>
+        <v>2455.2766162655698</v>
       </c>
       <c r="E385">
         <v>102.6133</v>
@@ -11151,7 +11169,7 @@
         <v>73647.38</v>
       </c>
       <c r="D386">
-        <v>2429.6622394886499</v>
+        <v>2429.6622814482698</v>
       </c>
       <c r="E386">
         <v>102.4846</v>
@@ -11174,7 +11192,7 @@
         <v>73561.88</v>
       </c>
       <c r="D387">
-        <v>2451.5034188377199</v>
+        <v>2451.50344605694</v>
       </c>
       <c r="E387">
         <v>103.3763</v>
@@ -11197,7 +11215,7 @@
         <v>73414.880000000005</v>
       </c>
       <c r="D388">
-        <v>2450.9998953806398</v>
+        <v>2450.9999360153602</v>
       </c>
       <c r="E388">
         <v>103.7015</v>
@@ -11220,7 +11238,7 @@
         <v>73481</v>
       </c>
       <c r="D389">
-        <v>2456.2342751354099</v>
+        <v>2456.2342274091202</v>
       </c>
       <c r="E389">
         <v>104.1263</v>
@@ -11243,7 +11261,7 @@
         <v>73035.69</v>
       </c>
       <c r="D390">
-        <v>2450.4828189177101</v>
+        <v>2450.4826880318901</v>
       </c>
       <c r="E390">
         <v>104.83110000000001</v>
@@ -11266,7 +11284,7 @@
         <v>72932.19</v>
       </c>
       <c r="D391">
-        <v>2449.5543007298902</v>
+        <v>2449.5539408999298</v>
       </c>
       <c r="E391">
         <v>105.1742</v>
@@ -11289,7 +11307,7 @@
         <v>73961.38</v>
       </c>
       <c r="D392">
-        <v>2460.0101003126401</v>
+        <v>2460.0100358405598</v>
       </c>
       <c r="E392">
         <v>105.5162</v>
@@ -11312,7 +11330,7 @@
         <v>73654.25</v>
       </c>
       <c r="D393">
-        <v>2461.94373831248</v>
+        <v>2461.9437661604402</v>
       </c>
       <c r="E393">
         <v>105.93040000000001</v>
@@ -11335,7 +11353,7 @@
         <v>73365.13</v>
       </c>
       <c r="D394">
-        <v>2464.47431761493</v>
+        <v>2464.4744165145498</v>
       </c>
       <c r="E394">
         <v>106.3349</v>
@@ -11358,7 +11376,7 @@
         <v>73705.81</v>
       </c>
       <c r="D395">
-        <v>2478.5094648264799</v>
+        <v>2478.5099645486098</v>
       </c>
       <c r="E395">
         <v>106.608</v>
@@ -11381,7 +11399,7 @@
         <v>73337.25</v>
       </c>
       <c r="D396">
-        <v>2496.5263264015098</v>
+        <v>2496.5263997421298</v>
       </c>
       <c r="E396">
         <v>107.87860000000001</v>
@@ -11404,7 +11422,7 @@
         <v>73117.440000000002</v>
       </c>
       <c r="D397">
-        <v>2461.2337552366198</v>
+        <v>2461.23379547594</v>
       </c>
       <c r="E397">
         <v>108.57129999999999</v>
@@ -11427,7 +11445,7 @@
         <v>72767.31</v>
       </c>
       <c r="D398">
-        <v>2462.0737234665098</v>
+        <v>2462.0737481338901</v>
       </c>
       <c r="E398">
         <v>109.2043</v>
@@ -11450,7 +11468,7 @@
         <v>73023.44</v>
       </c>
       <c r="D399">
-        <v>2475.1729666184701</v>
+        <v>2475.1729695165</v>
       </c>
       <c r="E399">
         <v>109.4357</v>
@@ -11473,7 +11491,7 @@
         <v>72945.94</v>
       </c>
       <c r="D400">
-        <v>2458.1419895650201</v>
+        <v>2458.1419686204499</v>
       </c>
       <c r="E400">
         <v>110.15179999999999</v>
@@ -11496,7 +11514,7 @@
         <v>73183.56</v>
       </c>
       <c r="D401">
-        <v>2465.3751845942602</v>
+        <v>2465.3750181661699</v>
       </c>
       <c r="E401">
         <v>110.30110000000001</v>
@@ -11519,7 +11537,7 @@
         <v>72711</v>
       </c>
       <c r="D402">
-        <v>2493.4787165461698</v>
+        <v>2493.47837597436</v>
       </c>
       <c r="E402">
         <v>111.31270000000001</v>
@@ -11542,7 +11560,7 @@
         <v>72322.44</v>
       </c>
       <c r="D403">
-        <v>2499.8049159755501</v>
+        <v>2499.8042190176702</v>
       </c>
       <c r="E403">
         <v>111.4787</v>
@@ -11565,7 +11583,7 @@
         <v>72832.13</v>
       </c>
       <c r="D404">
-        <v>2484.8247252612</v>
+        <v>2484.8246372942399</v>
       </c>
       <c r="E404">
         <v>111.97799999999999</v>
@@ -11588,7 +11606,7 @@
         <v>72184.5</v>
       </c>
       <c r="D405">
-        <v>2467.458818906</v>
+        <v>2467.4589474690601</v>
       </c>
       <c r="E405">
         <v>112.4597</v>
@@ -11611,7 +11629,7 @@
         <v>72961.38</v>
       </c>
       <c r="D406">
-        <v>2461.8476261963801</v>
+        <v>2461.8478611237601</v>
       </c>
       <c r="E406">
         <v>112.5314</v>
@@ -11634,7 +11652,7 @@
         <v>73638.5</v>
       </c>
       <c r="D407">
-        <v>2439.0794098128599</v>
+        <v>2439.0808406302199</v>
       </c>
       <c r="E407">
         <v>113.2724</v>
@@ -11657,7 +11675,7 @@
         <v>73345.81</v>
       </c>
       <c r="D408">
-        <v>2430.27080307292</v>
+        <v>2430.2708286769398</v>
       </c>
       <c r="E408">
         <v>113.74290000000001</v>
@@ -11680,7 +11698,7 @@
         <v>73789.81</v>
       </c>
       <c r="D409">
-        <v>2446.9522529075798</v>
+        <v>2446.9521726503499</v>
       </c>
       <c r="E409">
         <v>113.9851</v>
@@ -11703,7 +11721,7 @@
         <v>73874.13</v>
       </c>
       <c r="D410">
-        <v>2449.68766315117</v>
+        <v>2449.6875876582699</v>
       </c>
       <c r="E410">
         <v>115.6785</v>
@@ -11726,7 +11744,7 @@
         <v>74057.88</v>
       </c>
       <c r="D411">
-        <v>2433.8796717013402</v>
+        <v>2433.8796380693898</v>
       </c>
       <c r="E411">
         <v>115.05029999999999</v>
@@ -11749,7 +11767,7 @@
         <v>74237.88</v>
       </c>
       <c r="D412">
-        <v>2471.8949937062098</v>
+        <v>2471.8948166566402</v>
       </c>
       <c r="E412">
         <v>114.6896</v>
@@ -11772,7 +11790,7 @@
         <v>73646.13</v>
       </c>
       <c r="D413">
-        <v>2450.0978689233302</v>
+        <v>2450.0974405260399</v>
       </c>
       <c r="E413">
         <v>115.1825</v>
@@ -11795,7 +11813,7 @@
         <v>73963.44</v>
       </c>
       <c r="D414">
-        <v>2435.4748812840398</v>
+        <v>2435.4743408917702</v>
       </c>
       <c r="E414">
         <v>114.1686</v>
@@ -11818,7 +11836,7 @@
         <v>73982.94</v>
       </c>
       <c r="D415">
-        <v>2432.2548861127202</v>
+        <v>2432.2538318546999</v>
       </c>
       <c r="E415">
         <v>114.4692</v>
@@ -11841,7 +11859,7 @@
         <v>74729</v>
       </c>
       <c r="D416">
-        <v>2464.8933272348299</v>
+        <v>2464.8929037032499</v>
       </c>
       <c r="E416">
         <v>113.70659999999999</v>
@@ -11864,7 +11882,7 @@
         <v>73531.75</v>
       </c>
       <c r="D417">
-        <v>2479.36522697086</v>
+        <v>2479.3648170033898</v>
       </c>
       <c r="E417">
         <v>112.6833</v>
@@ -11887,7 +11905,7 @@
         <v>72525.5</v>
       </c>
       <c r="D418">
-        <v>2489.9600701417298</v>
+        <v>2489.9626028247799</v>
       </c>
       <c r="E418">
         <v>111.54130000000001</v>
@@ -11910,7 +11928,7 @@
         <v>73586.75</v>
       </c>
       <c r="D419">
-        <v>2498.4188147638301</v>
+        <v>2498.4204337624501</v>
       </c>
       <c r="E419">
         <v>109.8184</v>
@@ -11933,7 +11951,7 @@
         <v>73427.56</v>
       </c>
       <c r="D420">
-        <v>2505.1188271963201</v>
+        <v>2505.1183624312798</v>
       </c>
       <c r="E420">
         <v>106.8489</v>
@@ -11956,7 +11974,7 @@
         <v>72631.63</v>
       </c>
       <c r="D421">
-        <v>2523.6461133292701</v>
+        <v>2523.6458284939899</v>
       </c>
       <c r="E421">
         <v>103.4164</v>
@@ -11979,7 +11997,7 @@
         <v>71529.25</v>
       </c>
       <c r="D422">
-        <v>2535.4603557296</v>
+        <v>2535.4603304556099</v>
       </c>
       <c r="E422">
         <v>100.49039999999999</v>
@@ -12002,7 +12020,7 @@
         <v>72050.559999999998</v>
       </c>
       <c r="D423">
-        <v>2531.9336463773402</v>
+        <v>2531.9339284892999</v>
       </c>
       <c r="E423">
         <v>101.3404</v>
@@ -12025,7 +12043,7 @@
         <v>71852</v>
       </c>
       <c r="D424">
-        <v>2525.6764421552002</v>
+        <v>2525.6764987443298</v>
       </c>
       <c r="E424">
         <v>100.8404</v>
@@ -12048,7 +12066,7 @@
         <v>72003.81</v>
       </c>
       <c r="D425">
-        <v>2518.4951797403201</v>
+        <v>2518.4947360469901</v>
       </c>
       <c r="E425">
         <v>101.0283</v>
@@ -12071,7 +12089,7 @@
         <v>71594.06</v>
       </c>
       <c r="D426">
-        <v>2503.9495204465902</v>
+        <v>2503.9483545476101</v>
       </c>
       <c r="E426">
         <v>101.6028</v>
@@ -12094,7 +12112,7 @@
         <v>71796.75</v>
       </c>
       <c r="D427">
-        <v>2488.77573357437</v>
+        <v>2488.77330359706</v>
       </c>
       <c r="E427">
         <v>102.5956</v>
@@ -12117,7 +12135,7 @@
         <v>72644.38</v>
       </c>
       <c r="D428">
-        <v>2504.1734226526601</v>
+        <v>2504.1713645762402</v>
       </c>
       <c r="E428">
         <v>103.5034</v>
@@ -12140,7 +12158,7 @@
         <v>72132</v>
       </c>
       <c r="D429">
-        <v>2513.5743995657799</v>
+        <v>2513.5729187462098</v>
       </c>
       <c r="E429">
         <v>104.3562</v>
@@ -12163,7 +12181,7 @@
         <v>72612.63</v>
       </c>
       <c r="D430">
-        <v>2516.1033496835798</v>
+        <v>2516.1088831289899</v>
       </c>
       <c r="E430">
         <v>105.5352</v>
@@ -12186,7 +12204,7 @@
         <v>73068.25</v>
       </c>
       <c r="D431">
-        <v>2505.8755132610199</v>
+        <v>2505.8786106646698</v>
       </c>
       <c r="E431">
         <v>106.04770000000001</v>
@@ -12209,7 +12227,7 @@
         <v>73045.19</v>
       </c>
       <c r="D432">
-        <v>2535.6818909603899</v>
+        <v>2535.6831487220802</v>
       </c>
       <c r="E432">
         <v>107.0355</v>
@@ -12232,7 +12250,7 @@
         <v>72743.63</v>
       </c>
       <c r="D433">
-        <v>2530.3447052455799</v>
+        <v>2530.3457239131699</v>
       </c>
       <c r="E433">
         <v>107.667</v>
@@ -12255,7 +12273,7 @@
         <v>72907.25</v>
       </c>
       <c r="D434">
-        <v>2538.1596475179399</v>
+        <v>2538.1596676716799</v>
       </c>
       <c r="E434">
         <v>109.66849999999999</v>
@@ -12278,7 +12296,7 @@
         <v>73473.19</v>
       </c>
       <c r="D435">
-        <v>2528.4597957322499</v>
+        <v>2528.4589114055002</v>
       </c>
       <c r="E435">
         <v>109.52509999999999</v>
@@ -12301,7 +12319,7 @@
         <v>73774.5</v>
       </c>
       <c r="D436">
-        <v>2531.5195833521202</v>
+        <v>2531.5178021340998</v>
       </c>
       <c r="E436">
         <v>111.12949999999999</v>
@@ -12324,7 +12342,7 @@
         <v>73761.06</v>
       </c>
       <c r="D437">
-        <v>2520.94147184146</v>
+        <v>2520.9392746233002</v>
       </c>
       <c r="E437">
         <v>111.63500000000001</v>
@@ -12347,7 +12365,7 @@
         <v>73823.69</v>
       </c>
       <c r="D438">
-        <v>2526.9770167015699</v>
+        <v>2526.9743982549098</v>
       </c>
       <c r="E438">
         <v>112.58069999999999</v>
@@ -12370,7 +12388,7 @@
         <v>73935.13</v>
       </c>
       <c r="D439">
-        <v>2539.97366445132</v>
+        <v>2539.9696014074698</v>
       </c>
       <c r="E439">
         <v>112.3613</v>
@@ -12393,7 +12411,7 @@
         <v>74200</v>
       </c>
       <c r="D440">
-        <v>2531.54833113521</v>
+        <v>2531.54459989616</v>
       </c>
       <c r="E440">
         <v>112.8854</v>
@@ -12416,7 +12434,7 @@
         <v>74133.63</v>
       </c>
       <c r="D441">
-        <v>2547.6350036870699</v>
+        <v>2547.6328391881302</v>
       </c>
       <c r="E441">
         <v>113.30880000000001</v>
@@ -12439,7 +12457,7 @@
         <v>74439.88</v>
       </c>
       <c r="D442">
-        <v>2538.96693531249</v>
+        <v>2538.97705644092</v>
       </c>
       <c r="E442">
         <v>113.5702</v>
@@ -12462,7 +12480,7 @@
         <v>74332.44</v>
       </c>
       <c r="D443">
-        <v>2570.6301536669898</v>
+        <v>2570.63679950193</v>
       </c>
       <c r="E443">
         <v>114.1142</v>
@@ -12485,7 +12503,7 @@
         <v>74940</v>
       </c>
       <c r="D444">
-        <v>2543.5380050510198</v>
+        <v>2543.54426834573</v>
       </c>
       <c r="E444">
         <v>114.7718</v>
@@ -12508,7 +12526,7 @@
         <v>74893.56</v>
       </c>
       <c r="D445">
-        <v>2532.1484390110099</v>
+        <v>2532.1526665532801</v>
       </c>
       <c r="E445">
         <v>116.1199</v>
@@ -12531,7 +12549,7 @@
         <v>75386.5</v>
       </c>
       <c r="D446">
-        <v>2535.1336269816402</v>
+        <v>2535.1333467141899</v>
       </c>
       <c r="E446">
         <v>117.7303</v>
@@ -12554,7 +12572,7 @@
         <v>75141.63</v>
       </c>
       <c r="D447">
-        <v>2527.8035046104701</v>
+        <v>2527.7989571551898</v>
       </c>
       <c r="E447">
         <v>117.5355</v>
@@ -12577,7 +12595,7 @@
         <v>74122.19</v>
       </c>
       <c r="D448">
-        <v>2527.1157873912498</v>
+        <v>2527.1075486259101</v>
       </c>
       <c r="E448">
         <v>117.1961</v>
@@ -12600,7 +12618,7 @@
         <v>74059.56</v>
       </c>
       <c r="D449">
-        <v>2534.81411656609</v>
+        <v>2534.80656517236</v>
       </c>
       <c r="E449">
         <v>116.61060000000001</v>
@@ -12623,7 +12641,7 @@
         <v>73314.44</v>
       </c>
       <c r="D450">
-        <v>2531.09981822174</v>
+        <v>2531.0966973529498</v>
       </c>
       <c r="E450">
         <v>117.684</v>
@@ -12646,7 +12664,7 @@
         <v>74098.5</v>
       </c>
       <c r="D451">
-        <v>2516.7807771584398</v>
+        <v>2516.7819850849</v>
       </c>
       <c r="E451">
         <v>117.9905</v>
@@ -12669,7 +12687,7 @@
         <v>74385.88</v>
       </c>
       <c r="D452">
-        <v>2493.8360857185398</v>
+        <v>2493.8152045883298</v>
       </c>
       <c r="E452">
         <v>118.34990000000001</v>
@@ -12692,7 +12710,7 @@
         <v>74908.75</v>
       </c>
       <c r="D453">
-        <v>2465.0720776647299</v>
+        <v>2465.0733650439802</v>
       </c>
       <c r="E453">
         <v>118.6061</v>
@@ -12715,7 +12733,7 @@
         <v>74257.13</v>
       </c>
       <c r="D454">
-        <v>2439.0274498973299</v>
+        <v>2439.04148411811</v>
       </c>
       <c r="E454">
         <v>118.533</v>
@@ -12738,7 +12756,7 @@
         <v>74798.5</v>
       </c>
       <c r="D455">
-        <v>2443.6540575303902</v>
+        <v>2443.6808366294599</v>
       </c>
       <c r="E455">
         <v>118.5491</v>
@@ -12761,7 +12779,7 @@
         <v>75782.19</v>
       </c>
       <c r="D456">
-        <v>2448.9626706930298</v>
+        <v>2448.9736733670302</v>
       </c>
       <c r="E456">
         <v>118.14075730506754</v>
@@ -12784,7 +12802,7 @@
         <v>76191.81</v>
       </c>
       <c r="D457">
-        <v>2455.5739880793399</v>
+        <v>2455.58485076335</v>
       </c>
       <c r="E457">
         <v>118.41470415791355</v>
@@ -12807,7 +12825,7 @@
         <v>76337.5</v>
       </c>
       <c r="D458">
-        <v>2440.8445670226802</v>
+        <v>2440.85189403817</v>
       </c>
       <c r="E458">
         <v>119.33437715532203</v>
@@ -12830,7 +12848,7 @@
         <v>76656.06</v>
       </c>
       <c r="D459">
-        <v>2430.38548322112</v>
+        <v>2430.3894433054202</v>
       </c>
       <c r="E459">
         <v>119.58573725959694</v>
@@ -12853,7 +12871,7 @@
         <v>76340.25</v>
       </c>
       <c r="D460">
-        <v>2452.1782432939599</v>
+        <v>2452.1061064332998</v>
       </c>
       <c r="E460">
         <v>118.99054109179259</v>
@@ -12876,7 +12894,7 @@
         <v>76644.5</v>
       </c>
       <c r="D461">
-        <v>2477.4568970402502</v>
+        <v>2477.4557643661501</v>
       </c>
       <c r="E461">
         <v>118.15970701999298</v>
@@ -12899,7 +12917,7 @@
         <v>75932.94</v>
       </c>
       <c r="D462">
-        <v>2494.3610849023598</v>
+        <v>2494.3588957591701</v>
       </c>
       <c r="E462">
         <v>118.86664944643007</v>
@@ -12922,7 +12940,7 @@
         <v>75746.94</v>
       </c>
       <c r="D463">
-        <v>2504.8666116040399</v>
+        <v>2504.86511587519</v>
       </c>
       <c r="E463">
         <v>118.3926607642689</v>
@@ -12945,7 +12963,7 @@
         <v>75942.19</v>
       </c>
       <c r="D464">
-        <v>2511.6258458327802</v>
+        <v>2511.61533246917</v>
       </c>
       <c r="E464">
         <v>118.52036283139523</v>
@@ -12968,7 +12986,7 @@
         <v>75993.38</v>
       </c>
       <c r="D465">
-        <v>2515.5176308221899</v>
+        <v>2515.5184086997301</v>
       </c>
       <c r="E465">
         <v>118.16673072549602</v>
@@ -12991,7 +13009,7 @@
         <v>75481.56</v>
       </c>
       <c r="D466">
-        <v>2522.1869030602302</v>
+        <v>2522.20498781059</v>
       </c>
       <c r="E466">
         <v>117.75755242288895</v>
@@ -13014,7 +13032,7 @@
         <v>75985.31</v>
       </c>
       <c r="D467">
-        <v>2509.5553056929102</v>
+        <v>2509.60468244096</v>
       </c>
       <c r="E467">
         <v>118.35596815169392</v>
@@ -13037,7 +13055,7 @@
         <v>76528.56</v>
       </c>
       <c r="D468">
-        <v>2517.39438043057</v>
+        <v>2517.41459779977</v>
       </c>
       <c r="E468">
         <v>118.19566799799401</v>
@@ -13060,7 +13078,7 @@
         <v>76566.63</v>
       </c>
       <c r="D469">
-        <v>2500.5242694070098</v>
+        <v>2500.5429887425898</v>
       </c>
       <c r="E469">
         <v>118.57286011270736</v>
@@ -13083,7 +13101,7 @@
         <v>75888</v>
       </c>
       <c r="D470">
-        <v>2504.1677697730702</v>
+        <v>2504.1810923264602</v>
       </c>
       <c r="E470">
         <v>119.04896745594699</v>
@@ -13106,7 +13124,7 @@
         <v>75679.63</v>
       </c>
       <c r="D471">
-        <v>2507.2584525689299</v>
+        <v>2507.26629865823</v>
       </c>
       <c r="E471">
         <v>119.02866143345256</v>
@@ -13129,7 +13147,7 @@
         <v>75817.440000000002</v>
       </c>
       <c r="D472">
-        <v>2511.23787077425</v>
+        <v>2511.0954690497301</v>
       </c>
       <c r="E472">
         <v>119.35038495946846</v>
@@ -13152,7 +13170,7 @@
         <v>76247.63</v>
       </c>
       <c r="D473">
-        <v>2497.1058934092598</v>
+        <v>2497.1062753995502</v>
       </c>
       <c r="E473">
         <v>119.80717869674264</v>
@@ -13175,7 +13193,7 @@
         <v>76199.13</v>
       </c>
       <c r="D474">
-        <v>2475.7839050167199</v>
+        <v>2475.7788022517002</v>
       </c>
       <c r="E474">
         <v>119.89250139482283</v>
@@ -13198,7 +13216,7 @@
         <v>76174.25</v>
       </c>
       <c r="D475">
-        <v>2473.4341966915299</v>
+        <v>2473.4296399662599</v>
       </c>
       <c r="E475">
         <v>119.38053640623478</v>
@@ -13221,7 +13239,7 @@
         <v>76665.5</v>
       </c>
       <c r="D476">
-        <v>2487.0444901757701</v>
+        <v>2487.0511198716299</v>
       </c>
       <c r="E476">
         <v>120.06179493641287</v>
@@ -13244,7 +13262,7 @@
         <v>76426.94</v>
       </c>
       <c r="D477">
-        <v>2487.1451878002699</v>
+        <v>2487.1518459654199</v>
       </c>
       <c r="E477">
         <v>120.62158187704878</v>
@@ -13267,7 +13285,7 @@
         <v>75902.25</v>
       </c>
       <c r="D478">
-        <v>2515.5806474353599</v>
+        <v>2515.5975488243098</v>
       </c>
       <c r="E478">
         <v>120.99892306608187</v>
@@ -13290,7 +13308,7 @@
         <v>76260.88</v>
       </c>
       <c r="D479">
-        <v>2521.4655656445898</v>
+        <v>2521.5234977718501</v>
       </c>
       <c r="E479">
         <v>120.81653939296628</v>
@@ -13313,7 +13331,7 @@
         <v>76543.38</v>
       </c>
       <c r="D480">
-        <v>2516.6772533199101</v>
+        <v>2516.7565046681798</v>
       </c>
       <c r="E480">
         <v>121.39299775045774</v>
@@ -13336,7 +13354,7 @@
         <v>76886.63</v>
       </c>
       <c r="D481">
-        <v>2513.1467104118401</v>
+        <v>2513.1548951551599</v>
       </c>
       <c r="E481">
         <v>121.2350712992764</v>
@@ -13359,7 +13377,7 @@
         <v>77257.88</v>
       </c>
       <c r="D482">
-        <v>2515.6840748285099</v>
+        <v>2515.6948508032001</v>
       </c>
       <c r="E482">
         <v>122.29477842314841</v>
@@ -13382,7 +13400,7 @@
         <v>77761.56</v>
       </c>
       <c r="D483">
-        <v>2505.3316546557799</v>
+        <v>2505.3410138282502</v>
       </c>
       <c r="E483">
         <v>122.99393056930916</v>
@@ -13405,7 +13423,7 @@
         <v>77179.94</v>
       </c>
       <c r="D484">
-        <v>2502.2757895590498</v>
+        <v>2502.0569118840499</v>
       </c>
       <c r="E484">
         <v>122.80862122821897</v>
@@ -13428,7 +13446,7 @@
         <v>77247</v>
       </c>
       <c r="D485">
-        <v>2483.5576453284002</v>
+        <v>2483.5565282910402</v>
       </c>
       <c r="E485">
         <v>123.28358667038096</v>
@@ -13451,7 +13469,7 @@
         <v>76948.25</v>
       </c>
       <c r="D486">
-        <v>2490.9397997357601</v>
+        <v>2490.9273788485998</v>
       </c>
       <c r="E486">
         <v>122.99587285905162</v>
@@ -13474,7 +13492,7 @@
         <v>77353.5</v>
       </c>
       <c r="D487">
-        <v>2486.4227194835198</v>
+        <v>2486.4018912576398</v>
       </c>
       <c r="E487">
         <v>123.2257264918003</v>
@@ -13497,7 +13515,7 @@
         <v>77616.63</v>
       </c>
       <c r="D488">
-        <v>2477.1719944199599</v>
+        <v>2477.19528640931</v>
       </c>
       <c r="E488">
         <v>123.45360970387436</v>
@@ -13520,7 +13538,7 @@
         <v>77782.75</v>
       </c>
       <c r="D489">
-        <v>2493.1775937126199</v>
+        <v>2493.2375696792401</v>
       </c>
       <c r="E489">
         <v>122.25831169856602</v>
@@ -13543,7 +13561,7 @@
         <v>78668</v>
       </c>
       <c r="D490">
-        <v>2493.03028496771</v>
+        <v>2493.0531848116698</v>
       </c>
       <c r="E490">
         <v>123.48572963177847</v>
@@ -13566,7 +13584,7 @@
         <v>79410.69</v>
       </c>
       <c r="D491">
-        <v>2505.8890126103101</v>
+        <v>2505.9305361810498</v>
       </c>
       <c r="E491">
         <v>122.65342657538569</v>
@@ -13589,7 +13607,7 @@
         <v>79498.94</v>
       </c>
       <c r="D492">
-        <v>2491.9582883191001</v>
+        <v>2492.0968079374002</v>
       </c>
       <c r="E492">
         <v>123.5449340741413</v>
@@ -13612,7 +13630,7 @@
         <v>80310.25</v>
       </c>
       <c r="D493">
-        <v>2502.8254314787</v>
+        <v>2502.8193622475001</v>
       </c>
       <c r="E493">
         <v>123.82562279424961</v>
@@ -13635,7 +13653,7 @@
         <v>79728.56</v>
       </c>
       <c r="D494">
-        <v>2510.1863625527499</v>
+        <v>2510.17930661941</v>
       </c>
       <c r="E494">
         <v>124.51339629768127</v>
@@ -13658,7 +13676,7 @@
         <v>79522.880000000005</v>
       </c>
       <c r="D495">
-        <v>2534.3901514475901</v>
+        <v>2534.3801913165698</v>
       </c>
       <c r="E495">
         <v>124.17704048680501</v>
@@ -13681,7 +13699,7 @@
         <v>80422.31</v>
       </c>
       <c r="D496">
-        <v>2572.1255448685502</v>
+        <v>2571.8828599016301</v>
       </c>
       <c r="E496">
         <v>124.13239125563145</v>
@@ -13704,7 +13722,7 @@
         <v>80016.81</v>
       </c>
       <c r="D497">
-        <v>2572.32153799042</v>
+        <v>2572.3045627950901</v>
       </c>
       <c r="E497">
         <v>124.06245844535665</v>
@@ -13727,7 +13745,7 @@
         <v>79975.75</v>
       </c>
       <c r="D498">
-        <v>2586.7654751374798</v>
+        <v>2586.7429430899101</v>
       </c>
       <c r="E498">
         <v>123.74836754574204</v>
@@ -13750,7 +13768,7 @@
         <v>80397.81</v>
       </c>
       <c r="D499">
-        <v>2586.5946184457498</v>
+        <v>2586.5667089093399</v>
       </c>
       <c r="E499">
         <v>124.33509119711461</v>
@@ -13773,7 +13791,7 @@
         <v>80923.75</v>
       </c>
       <c r="D500">
-        <v>2582.9298077240401</v>
+        <v>2582.9460709750001</v>
       </c>
       <c r="E500">
         <v>124.07425868463432</v>
@@ -13796,7 +13814,7 @@
         <v>80772</v>
       </c>
       <c r="D501">
-        <v>2610.4336934888902</v>
+        <v>2610.5583441157901</v>
       </c>
       <c r="E501">
         <v>124.49109553380849</v>
@@ -13819,7 +13837,7 @@
         <v>80558.94</v>
       </c>
       <c r="D502">
-        <v>2622.9495049642301</v>
+        <v>2622.9852929798299</v>
       </c>
       <c r="E502">
         <v>124.37144851537983</v>
@@ -13842,7 +13860,7 @@
         <v>80698.75</v>
       </c>
       <c r="D503">
-        <v>2642.3287087280601</v>
+        <v>2642.3586915317001</v>
       </c>
       <c r="E503">
         <v>124.77885124480906</v>
@@ -13865,7 +13883,7 @@
         <v>81290.69</v>
       </c>
       <c r="D504">
-        <v>2650.0556516100701</v>
+        <v>2650.2511718617002</v>
       </c>
       <c r="E504">
         <v>124.31098861255964</v>
@@ -13888,7 +13906,7 @@
         <v>81446.44</v>
       </c>
       <c r="D505">
-        <v>2675.5896931602801</v>
+        <v>2675.5639957119201</v>
       </c>
       <c r="E505">
         <v>124.01275898947097</v>
@@ -13911,7 +13929,7 @@
         <v>81466.63</v>
       </c>
       <c r="D506">
-        <v>2677.0151465428498</v>
+        <v>2676.9830076767498</v>
       </c>
       <c r="E506">
         <v>125.35768452359675</v>
@@ -13934,7 +13952,7 @@
         <v>80705.06</v>
       </c>
       <c r="D507">
-        <v>2685.93895243115</v>
+        <v>2685.9051147370501</v>
       </c>
       <c r="E507">
         <v>125.02797942597637</v>
@@ -13957,7 +13975,7 @@
         <v>80676.75</v>
       </c>
       <c r="D508">
-        <v>2686.8599997421402</v>
+        <v>2686.59492505559</v>
       </c>
       <c r="E508">
         <v>125.28072428385592</v>
@@ -13980,7 +13998,7 @@
         <v>79778.25</v>
       </c>
       <c r="D509">
-        <v>2680.7035277290902</v>
+        <v>2680.6727594434401</v>
       </c>
       <c r="E509">
         <v>125.51082522869189</v>
@@ -14003,7 +14021,7 @@
         <v>78990.94</v>
       </c>
       <c r="D510">
-        <v>2693.6162826080599</v>
+        <v>2693.5809952422901</v>
       </c>
       <c r="E510">
         <v>125.44819974466931</v>
@@ -14026,7 +14044,7 @@
         <v>79889.38</v>
       </c>
       <c r="D511">
-        <v>2705.5910546789901</v>
+        <v>2705.5449003898502</v>
       </c>
       <c r="E511">
         <v>126.31682558927686</v>
@@ -14049,7 +14067,7 @@
         <v>80607.5</v>
       </c>
       <c r="D512">
-        <v>2715.7049214552599</v>
+        <v>2715.7194472967199</v>
       </c>
       <c r="E512">
         <v>125.70197635861378</v>
@@ -14072,7 +14090,7 @@
         <v>80064</v>
       </c>
       <c r="D513">
-        <v>2709.4002467238702</v>
+        <v>2709.59508099614</v>
       </c>
       <c r="E513">
         <v>126.07324989916349</v>
@@ -14095,7 +14113,7 @@
         <v>80392.06</v>
       </c>
       <c r="D514">
-        <v>2697.2775157945598</v>
+        <v>2697.3614612359802</v>
       </c>
       <c r="E514">
         <v>125.96148503155078</v>
@@ -14118,7 +14136,7 @@
         <v>81571.56</v>
       </c>
       <c r="D515">
-        <v>2698.5899174340602</v>
+        <v>2698.6320847182101</v>
       </c>
       <c r="E515">
         <v>126.83403785871297</v>
@@ -14141,7 +14159,7 @@
         <v>82631.94</v>
       </c>
       <c r="D516">
-        <v>2695.4770284206602</v>
+        <v>2695.6992901113399</v>
       </c>
       <c r="E516">
         <v>126.92318194808253</v>
@@ -14164,7 +14182,7 @@
         <v>82090.5</v>
       </c>
       <c r="D517">
-        <v>2707.02510630291</v>
+        <v>2707.0125298018102</v>
       </c>
       <c r="E517">
         <v>126.88902479694869</v>
@@ -14187,7 +14205,7 @@
         <v>81167.63</v>
       </c>
       <c r="D518">
-        <v>2730.3461344755001</v>
+        <v>2730.3526369413298</v>
       </c>
       <c r="E518">
         <v>127.85577746216126</v>
@@ -14210,7 +14228,7 @@
         <v>81183.13</v>
       </c>
       <c r="D519">
-        <v>2736.0811327758802</v>
+        <v>2735.7342897383801</v>
       </c>
       <c r="E519">
         <v>128.33369493686936</v>
@@ -14233,7 +14251,7 @@
         <v>80376.44</v>
       </c>
       <c r="D520">
-        <v>2749.6418742440901</v>
+        <v>2749.4876489220001</v>
       </c>
       <c r="E520">
         <v>129.01558161615276</v>
@@ -14256,7 +14274,7 @@
         <v>79942</v>
       </c>
       <c r="D521">
-        <v>2713.62296077887</v>
+        <v>2713.5888757610101</v>
       </c>
       <c r="E521">
         <v>129.27656943628483</v>
@@ -14279,7 +14297,7 @@
         <v>80525.19</v>
       </c>
       <c r="D522">
-        <v>2691.3278553141599</v>
+        <v>2691.3025363196898</v>
       </c>
       <c r="E522">
         <v>129.50706446858402</v>
@@ -14302,7 +14320,7 @@
         <v>81074.69</v>
       </c>
       <c r="D523">
-        <v>2687.4714631935499</v>
+        <v>2687.3763876419998</v>
       </c>
       <c r="E523">
         <v>129.47927127320767</v>
@@ -14325,7 +14343,7 @@
         <v>81591.38</v>
       </c>
       <c r="D524">
-        <v>2678.3431857834698</v>
+        <v>2678.3840965890499</v>
       </c>
       <c r="E524">
         <v>129.33671267722045</v>
@@ -14348,7 +14366,7 @@
         <v>80980.19</v>
       </c>
       <c r="D525">
-        <v>2645.32939607242</v>
+        <v>2645.5822588013498</v>
       </c>
       <c r="E525">
         <v>130.17848438081424</v>
@@ -14371,7 +14389,7 @@
         <v>81190.75</v>
       </c>
       <c r="D526">
-        <v>2666.56478480739</v>
+        <v>2666.7195882997999</v>
       </c>
       <c r="E526">
         <v>130.46378519162477</v>
@@ -14394,7 +14412,7 @@
         <v>81339.19</v>
       </c>
       <c r="D527">
-        <v>2620.5765563426598</v>
+        <v>2620.6928805780399</v>
       </c>
       <c r="E527">
         <v>130.55413121856733</v>
@@ -14417,7 +14435,7 @@
         <v>82008.69</v>
       </c>
       <c r="D528">
-        <v>2599.40268389531</v>
+        <v>2599.6951869702598</v>
       </c>
       <c r="E528">
         <v>131.77102810417074</v>
@@ -14440,7 +14458,7 @@
         <v>81730.81</v>
       </c>
       <c r="D529">
-        <v>2563.6928072875698</v>
+        <v>2563.6879177312098</v>
       </c>
       <c r="E529">
         <v>131.96378721102226</v>
@@ -14463,7 +14481,7 @@
         <v>82221.88</v>
       </c>
       <c r="D530">
-        <v>2560.4117340228199</v>
+        <v>2560.4027568052602</v>
       </c>
       <c r="E530">
         <v>132.47125094422424</v>
@@ -14486,7 +14504,7 @@
         <v>82346.94</v>
       </c>
       <c r="D531">
-        <v>2527.88825001234</v>
+        <v>2527.15409101266</v>
       </c>
       <c r="E531">
         <v>132.93298644421094</v>
@@ -14509,7 +14527,7 @@
         <v>82167</v>
       </c>
       <c r="D532">
-        <v>2513.2154258932601</v>
+        <v>2513.1125381390598</v>
       </c>
       <c r="E532">
         <v>132.44750488403352</v>
@@ -14532,7 +14550,7 @@
         <v>81802.94</v>
       </c>
       <c r="D533">
-        <v>2518.9817477821198</v>
+        <v>2518.9301776244401</v>
       </c>
       <c r="E533">
         <v>133.15785976208238</v>
@@ -14555,7 +14573,7 @@
         <v>81545.69</v>
       </c>
       <c r="D534">
-        <v>2511.4106567240801</v>
+        <v>2511.4218101169899</v>
       </c>
       <c r="E534">
         <v>132.90321082650064</v>
@@ -14578,7 +14596,7 @@
         <v>82230</v>
       </c>
       <c r="D535">
-        <v>2500.44271864957</v>
+        <v>2500.3222517612999</v>
       </c>
       <c r="E535">
         <v>132.70481133397854</v>
@@ -14601,7 +14619,7 @@
         <v>82667.88</v>
       </c>
       <c r="D536">
-        <v>2510.97528983858</v>
+        <v>2511.0237465700402</v>
       </c>
       <c r="E536">
         <v>133.07972091568664</v>
@@ -14624,10 +14642,10 @@
         <v>83433.63</v>
       </c>
       <c r="D537">
-        <v>2514.0158547825499</v>
+        <v>2514.3538294405698</v>
       </c>
       <c r="E537">
-        <v>133.65810791536416</v>
+        <v>133.65067677033733</v>
       </c>
       <c r="F537">
         <v>104.03270000000001</v>
@@ -14647,10 +14665,10 @@
         <v>83363.75</v>
       </c>
       <c r="D538">
-        <v>2509.3779916499998</v>
+        <v>2509.6973736965001</v>
       </c>
       <c r="E538">
-        <v>133.16905584985594</v>
+        <v>133.159422977715</v>
       </c>
       <c r="F538">
         <v>104.10039999999999</v>
@@ -14670,10 +14688,10 @@
         <v>84478.31</v>
       </c>
       <c r="D539">
-        <v>2520.7949003519702</v>
+        <v>2520.9949441613398</v>
       </c>
       <c r="E539">
-        <v>134.09423413483421</v>
+        <v>134.08243461507712</v>
       </c>
       <c r="F539">
         <v>103.98560000000001</v>
@@ -14693,10 +14711,10 @@
         <v>84611.5</v>
       </c>
       <c r="D540">
-        <v>2545.0477435939301</v>
+        <v>2545.40152890031</v>
       </c>
       <c r="E540">
-        <v>133.49283236360796</v>
+        <v>133.49864356080025</v>
       </c>
       <c r="F540">
         <v>104.0681</v>
@@ -14716,10 +14734,10 @@
         <v>84371.69</v>
       </c>
       <c r="D541">
-        <v>2557.18207885534</v>
+        <v>2557.38410609017</v>
       </c>
       <c r="E541">
-        <v>133.61733628620041</v>
+        <v>133.6238541456282</v>
       </c>
       <c r="F541">
         <v>104.0936</v>
@@ -14739,10 +14757,10 @@
         <v>82888.69</v>
       </c>
       <c r="D542">
-        <v>2542.1292392359401</v>
+        <v>2542.4084704851798</v>
       </c>
       <c r="E542">
-        <v>133.55832118988386</v>
+        <v>133.56866403399539</v>
       </c>
       <c r="F542">
         <v>103.4021</v>
@@ -14762,10 +14780,10 @@
         <v>82603.75</v>
       </c>
       <c r="D543">
-        <v>2530.9564884326101</v>
+        <v>2528.7506035004499</v>
       </c>
       <c r="E543">
-        <v>133.46484840479354</v>
+        <v>133.4937783333651</v>
       </c>
       <c r="F543">
         <v>102.83710000000001</v>
@@ -14785,10 +14803,10 @@
         <v>82528.69</v>
       </c>
       <c r="D544">
-        <v>2534.6713185569602</v>
+        <v>2534.9435178513299</v>
       </c>
       <c r="E544">
-        <v>134.23810593869791</v>
+        <v>134.26612326684631</v>
       </c>
       <c r="F544">
         <v>102.87569999999999</v>
@@ -14808,10 +14826,10 @@
         <v>82299.13</v>
       </c>
       <c r="D545">
-        <v>2518.5565867188998</v>
+        <v>2518.6259217316201</v>
       </c>
       <c r="E545">
-        <v>134.14139134314763</v>
+        <v>134.17591478155919</v>
       </c>
       <c r="F545">
         <v>102.274</v>
@@ -14831,10 +14849,10 @@
         <v>81535.63</v>
       </c>
       <c r="D546">
-        <v>2519.9754944089</v>
+        <v>2520.0307032939299</v>
       </c>
       <c r="E546">
-        <v>134.23909457870354</v>
+        <v>134.25153176848161</v>
       </c>
       <c r="F546">
         <v>102.392</v>
@@ -14854,10 +14872,10 @@
         <v>81712.81</v>
       </c>
       <c r="D547">
-        <v>2523.85628289755</v>
+        <v>2523.7129935090402</v>
       </c>
       <c r="E547">
-        <v>133.42403785544923</v>
+        <v>133.45443223898036</v>
       </c>
       <c r="F547">
         <v>102.4375</v>
@@ -14877,10 +14895,10 @@
         <v>81218.559999999998</v>
       </c>
       <c r="D548">
-        <v>2493.7056923570799</v>
+        <v>2493.88303602616</v>
       </c>
       <c r="E548">
-        <v>133.59534762851786</v>
+        <v>133.61623976098895</v>
       </c>
       <c r="F548">
         <v>101.9408</v>
@@ -14900,10 +14918,10 @@
         <v>82287.25</v>
       </c>
       <c r="D549">
-        <v>2510.99227651398</v>
+        <v>2511.34629801149</v>
       </c>
       <c r="E549">
-        <v>133.63061603917691</v>
+        <v>133.64469860722178</v>
       </c>
       <c r="F549">
         <v>102.639</v>
@@ -14923,10 +14941,10 @@
         <v>80615.25</v>
       </c>
       <c r="D550">
-        <v>2505.3077532350599</v>
+        <v>2505.83602086171</v>
       </c>
       <c r="E550">
-        <v>133.46455882413565</v>
+        <v>133.46851801539395</v>
       </c>
       <c r="F550">
         <v>102.29170000000001</v>
@@ -14946,10 +14964,10 @@
         <v>82476.88</v>
       </c>
       <c r="D551">
-        <v>2504.3446118602801</v>
+        <v>2504.6372635123098</v>
       </c>
       <c r="E551">
-        <v>133.6563763137313</v>
+        <v>133.66177641528549</v>
       </c>
       <c r="F551">
         <v>101.4281</v>
@@ -14969,10 +14987,10 @@
         <v>83394.880000000005</v>
       </c>
       <c r="D552">
-        <v>2500.5983722259398</v>
+        <v>2501.18696193917</v>
       </c>
       <c r="E552">
-        <v>133.93192151455256</v>
+        <v>133.94468599478679</v>
       </c>
       <c r="F552">
         <v>101.9372</v>
@@ -14992,10 +15010,10 @@
         <v>83462.69</v>
       </c>
       <c r="D553">
-        <v>2488.28197073926</v>
+        <v>2488.5340843451399</v>
       </c>
       <c r="E553">
-        <v>134.14632322772044</v>
+        <v>134.16612882337895</v>
       </c>
       <c r="F553">
         <v>101.7003</v>
@@ -15015,10 +15033,10 @@
         <v>82933.75</v>
       </c>
       <c r="D554">
-        <v>2482.87622166138</v>
+        <v>2483.26605328403</v>
       </c>
       <c r="E554">
-        <v>127.60414647932635</v>
+        <v>127.66912971222796</v>
       </c>
       <c r="F554">
         <v>101.0338</v>
@@ -15038,10 +15056,10 @@
         <v>82111</v>
       </c>
       <c r="D555">
-        <v>2472.5431200305102</v>
+        <v>2469.0190190308199</v>
       </c>
       <c r="E555">
-        <v>127.98893556293922</v>
+        <v>128.06744133285179</v>
       </c>
       <c r="F555">
         <v>101.37350000000001</v>
@@ -15061,10 +15079,10 @@
         <v>82233.81</v>
       </c>
       <c r="D556">
-        <v>2520.0310189298202</v>
+        <v>2520.4470066464301</v>
       </c>
       <c r="E556">
-        <v>127.65031301808182</v>
+        <v>127.7271957964585</v>
       </c>
       <c r="F556">
         <v>97.407799999999995</v>
@@ -15084,10 +15102,10 @@
         <v>82550.31</v>
       </c>
       <c r="D557">
-        <v>2595.7455999941699</v>
+        <v>2595.9488178127799</v>
       </c>
       <c r="E557">
-        <v>116.82282451701882</v>
+        <v>116.9094593718261</v>
       </c>
       <c r="F557">
         <v>84.561899999999994</v>
@@ -15107,10 +15125,10 @@
         <v>71432.13</v>
       </c>
       <c r="D558">
-        <v>2622.37368983952</v>
+        <v>2622.5404202851901</v>
       </c>
       <c r="E558">
-        <v>117.7913654348033</v>
+        <v>117.85233344680985</v>
       </c>
       <c r="F558">
         <v>85.960400000000007</v>
@@ -15130,10 +15148,10 @@
         <v>70177</v>
       </c>
       <c r="D559">
-        <v>2666.1406314311998</v>
+        <v>2666.1271918146899</v>
       </c>
       <c r="E559">
-        <v>123.27672498417164</v>
+        <v>123.35193015827606</v>
       </c>
       <c r="F559">
         <v>91.593400000000003</v>
@@ -15153,10 +15171,10 @@
         <v>71649.25</v>
       </c>
       <c r="D560">
-        <v>2665.7960372859702</v>
+        <v>2666.1825716124999</v>
       </c>
       <c r="E560">
-        <v>127.25618743223089</v>
+        <v>127.33643926328182</v>
       </c>
       <c r="F560">
         <v>95.025599999999997</v>
@@ -15176,10 +15194,10 @@
         <v>72757.13</v>
       </c>
       <c r="D561">
-        <v>2652.7937395025501</v>
+        <v>2653.1726518291298</v>
       </c>
       <c r="E561">
-        <v>128.96395051005075</v>
+        <v>129.04118020316363</v>
       </c>
       <c r="F561">
         <v>95.954899999999995</v>
@@ -15199,10 +15217,10 @@
         <v>72606.63</v>
       </c>
       <c r="D562">
-        <v>2647.6799222201998</v>
+        <v>2648.3966001787999</v>
       </c>
       <c r="E562">
-        <v>131.07514474364487</v>
+        <v>131.12876809185218</v>
       </c>
       <c r="F562">
         <v>95.966899999999995</v>
@@ -15222,10 +15240,10 @@
         <v>73182.31</v>
       </c>
       <c r="D563">
-        <v>2626.23035593851</v>
+        <v>2626.5034539885701</v>
       </c>
       <c r="E563">
-        <v>132.54404179522592</v>
+        <v>132.6055269121259</v>
       </c>
       <c r="F563">
         <v>96.739400000000003</v>
@@ -15245,10 +15263,10 @@
         <v>74978.94</v>
       </c>
       <c r="D564">
-        <v>2616.75250057942</v>
+        <v>2617.8544875023799</v>
       </c>
       <c r="E564">
-        <v>133.9465542762523</v>
+        <v>134.03304133938576</v>
       </c>
       <c r="F564">
         <v>97.081599999999995</v>
@@ -15268,10 +15286,10 @@
         <v>75718.880000000005</v>
       </c>
       <c r="D565">
-        <v>2618.9388266805299</v>
+        <v>2619.0167782380699</v>
       </c>
       <c r="E565">
-        <v>135.10112058040573</v>
+        <v>135.18145979699403</v>
       </c>
       <c r="F565">
         <v>98.363</v>
@@ -15291,16 +15309,16 @@
         <v>75922.5</v>
       </c>
       <c r="D566">
-        <v>2593.24048612874</v>
+        <v>2593.5412622465801</v>
       </c>
       <c r="E566">
-        <v>135.91735289756102</v>
+        <v>135.98689105914522</v>
       </c>
       <c r="F566">
         <v>98.882199999999997</v>
       </c>
       <c r="G566">
-        <v>262.63900000000001</v>
+        <v>262.68700000000001</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15314,16 +15332,16 @@
         <v>74006.13</v>
       </c>
       <c r="D567">
-        <v>2593.11692636932</v>
+        <v>2588.1386918196999</v>
       </c>
       <c r="E567">
-        <v>135.06210900907197</v>
+        <v>135.1392194227671</v>
       </c>
       <c r="F567">
         <v>95.614900000000006</v>
       </c>
       <c r="G567">
-        <v>263.57299999999998</v>
+        <v>263.57900000000001</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15337,16 +15355,16 @@
         <v>75878.559999999998</v>
       </c>
       <c r="D568">
-        <v>2557.8511170945999</v>
+        <v>2558.3961019178</v>
       </c>
       <c r="E568">
-        <v>136.13352295983407</v>
+        <v>136.22571270832398</v>
       </c>
       <c r="F568">
         <v>98.385599999999997</v>
       </c>
       <c r="G568">
-        <v>264.84699999999998</v>
+        <v>264.96100000000001</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15360,16 +15378,16 @@
         <v>75382.69</v>
       </c>
       <c r="D569">
-        <v>2513.0224528966601</v>
+        <v>2513.4557498447102</v>
       </c>
       <c r="E569">
-        <v>137.5598545210195</v>
+        <v>137.64564942626836</v>
       </c>
       <c r="F569">
         <v>98.558700000000002</v>
       </c>
       <c r="G569">
-        <v>266.625</v>
+        <v>266.61399999999998</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15383,16 +15401,16 @@
         <v>75885.06</v>
       </c>
       <c r="D570">
-        <v>2498.6159370580199</v>
+        <v>2498.9985361147301</v>
       </c>
       <c r="E570">
-        <v>136.0139445173086</v>
+        <v>136.05389989753658</v>
       </c>
       <c r="F570">
         <v>99.433300000000003</v>
       </c>
       <c r="G570">
-        <v>268.404</v>
+        <v>268.38299999999998</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15406,16 +15424,16 @@
         <v>76361</v>
       </c>
       <c r="D571">
-        <v>2456.7012534003902</v>
+        <v>2457.1845742417599</v>
       </c>
       <c r="E571">
-        <v>137.15169070819513</v>
+        <v>137.16216009258682</v>
       </c>
       <c r="F571">
         <v>99.798699999999997</v>
       </c>
       <c r="G571">
-        <v>270.70999999999998</v>
+        <v>270.654</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15429,16 +15447,16 @@
         <v>77642.559999999998</v>
       </c>
       <c r="D572">
-        <v>2439.3026917992902</v>
+        <v>2439.8379281799398</v>
       </c>
       <c r="E572">
-        <v>137.5284603615107</v>
+        <v>137.53122656301971</v>
       </c>
       <c r="F572">
         <v>100.25190000000001</v>
       </c>
       <c r="G572">
-        <v>271.96499999999997</v>
+        <v>271.90300000000002</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15452,16 +15470,16 @@
         <v>77234.06</v>
       </c>
       <c r="D573">
-        <v>2435.3486567517498</v>
+        <v>2435.7672276643202</v>
       </c>
       <c r="E573">
-        <v>136.9899519997887</v>
+        <v>136.99512698838896</v>
       </c>
       <c r="F573">
         <v>100.0437</v>
       </c>
       <c r="G573">
-        <v>272.75200000000001</v>
+        <v>272.67599999999999</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15475,16 +15493,16 @@
         <v>77634.94</v>
       </c>
       <c r="D574">
-        <v>2415.3830402840899</v>
+        <v>2416.2762991456102</v>
       </c>
       <c r="E574">
-        <v>136.35935956471712</v>
+        <v>136.31922406989943</v>
       </c>
       <c r="F574">
         <v>98.857900000000001</v>
       </c>
       <c r="G574">
-        <v>273.94200000000001</v>
+        <v>273.91000000000003</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15498,16 +15516,16 @@
         <v>78969.5</v>
       </c>
       <c r="D575">
-        <v>2411.2208902821799</v>
+        <v>2412.5375182978701</v>
       </c>
       <c r="E575">
-        <v>137.77323425500239</v>
+        <v>137.74665055013264</v>
       </c>
       <c r="F575">
         <v>100.1861</v>
       </c>
       <c r="G575">
-        <v>276.52800000000002</v>
+        <v>276.55</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15518,19 +15536,19 @@
         <v>79.150000000000006</v>
       </c>
       <c r="C576">
-        <v>79861.81</v>
+        <v>79827.69</v>
       </c>
       <c r="D576">
-        <v>2389.1205300521001</v>
+        <v>2391.79900422729</v>
       </c>
       <c r="E576">
-        <v>139.42524880931316</v>
+        <v>139.44267258599598</v>
       </c>
       <c r="F576">
         <v>100.86539999999999</v>
       </c>
       <c r="G576">
-        <v>278.82400000000001</v>
+        <v>278.91899999999998</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15541,19 +15559,19 @@
         <v>71.709999999999994</v>
       </c>
       <c r="C577">
-        <v>79392.31</v>
+        <v>79366.75</v>
       </c>
       <c r="D577">
-        <v>2364.1623880024999</v>
+        <v>2364.5694835723202</v>
       </c>
       <c r="E577">
-        <v>140.74117448039982</v>
+        <v>140.81205214436932</v>
       </c>
       <c r="F577">
         <v>100.57259999999999</v>
       </c>
       <c r="G577">
-        <v>280.80599999999998</v>
+        <v>280.84500000000003</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15564,19 +15582,19 @@
         <v>83.22</v>
       </c>
       <c r="C578">
-        <v>79552.38</v>
+        <v>79544.94</v>
       </c>
       <c r="D578">
-        <v>2330.06561961237</v>
+        <v>2330.7938082947699</v>
       </c>
       <c r="E578">
-        <v>141.17217050539756</v>
+        <v>141.11520203055548</v>
       </c>
       <c r="F578">
         <v>100.18559999999999</v>
       </c>
       <c r="G578">
-        <v>282.54199999999997</v>
+        <v>282.54300000000001</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15587,19 +15605,19 @@
         <v>91.64</v>
       </c>
       <c r="C579">
-        <v>80814.63</v>
+        <v>80818.31</v>
       </c>
       <c r="D579">
-        <v>2268.1202736477999</v>
+        <v>2263.58552786072</v>
       </c>
       <c r="E579">
-        <v>142.01203042127673</v>
+        <v>141.89557206449706</v>
       </c>
       <c r="F579">
         <v>100.8064</v>
       </c>
       <c r="G579">
-        <v>284.52499999999998</v>
+        <v>284.5</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15610,19 +15628,19 @@
         <v>108.5</v>
       </c>
       <c r="C580">
-        <v>80745.56</v>
+        <v>80746.75</v>
       </c>
       <c r="D580">
-        <v>2251.2438027541998</v>
+        <v>2252.0828825763301</v>
       </c>
       <c r="E580">
-        <v>141.386590814941</v>
+        <v>141.29459428789141</v>
       </c>
       <c r="F580">
         <v>101.3907</v>
       </c>
       <c r="G580">
-        <v>287.46699999999998</v>
+        <v>287.67399999999998</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15633,19 +15651,19 @@
         <v>101.78</v>
       </c>
       <c r="C581">
-        <v>79967.94</v>
+        <v>80001.94</v>
       </c>
       <c r="D581">
-        <v>2233.8785894019302</v>
+        <v>2235.7275641401602</v>
       </c>
       <c r="E581">
-        <v>139.70329988461529</v>
+        <v>139.63250258409872</v>
       </c>
       <c r="F581">
         <v>101.44</v>
       </c>
       <c r="G581">
-        <v>288.58199999999999</v>
+        <v>288.56099999999998</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15656,19 +15674,19 @@
         <v>109.55</v>
       </c>
       <c r="C582">
-        <v>79466.559999999998</v>
+        <v>79472.19</v>
       </c>
       <c r="D582">
-        <v>2187.8861448171901</v>
+        <v>2190.35679238791</v>
       </c>
       <c r="E582">
-        <v>140.5008531966717</v>
+        <v>140.35543238866498</v>
       </c>
       <c r="F582">
         <v>101.3335</v>
       </c>
       <c r="G582">
-        <v>291.29899999999998</v>
+        <v>291.298</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15679,19 +15697,19 @@
         <v>114.84</v>
       </c>
       <c r="C583">
-        <v>79717.19</v>
+        <v>79715.94</v>
       </c>
       <c r="D583">
-        <v>2164.0419250841601</v>
+        <v>2167.5525395701802</v>
       </c>
       <c r="E583">
-        <v>141.74164782447244</v>
+        <v>141.60750151547671</v>
       </c>
       <c r="F583">
         <v>101.018</v>
       </c>
       <c r="G583">
-        <v>295.072</v>
+        <v>294.95699999999999</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15702,19 +15720,19 @@
         <v>101.62</v>
       </c>
       <c r="C584">
-        <v>80628.13</v>
+        <v>80622.13</v>
       </c>
       <c r="D584">
-        <v>2142.63448609537</v>
+        <v>2143.3778313460898</v>
       </c>
       <c r="E584">
-        <v>141.45042270361822</v>
+        <v>141.33029180276199</v>
       </c>
       <c r="F584">
         <v>101.223</v>
       </c>
       <c r="G584">
-        <v>294.94</v>
+        <v>294.91300000000001</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15725,19 +15743,19 @@
         <v>93.67</v>
       </c>
       <c r="C585">
-        <v>81602.38</v>
+        <v>81595.13</v>
       </c>
       <c r="D585">
-        <v>2116.2039177888801</v>
+        <v>2117.96608194485</v>
       </c>
       <c r="E585">
-        <v>142.12083313138905</v>
+        <v>141.96568860854504</v>
       </c>
       <c r="F585">
         <v>101.0963</v>
       </c>
       <c r="G585">
-        <v>295.16199999999998</v>
+        <v>295.09699999999998</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15748,19 +15766,19 @@
         <v>84.26</v>
       </c>
       <c r="C586">
-        <v>82145.38</v>
+        <v>82137.94</v>
       </c>
       <c r="D586">
-        <v>2109.4059777068101</v>
+        <v>2112.2785716127501</v>
       </c>
       <c r="E586">
-        <v>142.72015775242571</v>
+        <v>142.55112807576546</v>
       </c>
       <c r="F586">
         <v>101.29179999999999</v>
       </c>
       <c r="G586">
-        <v>296.42099999999999</v>
+        <v>296.34899999999999</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15771,19 +15789,19 @@
         <v>87.55</v>
       </c>
       <c r="C587">
-        <v>82232.94</v>
+        <v>82226.559999999998</v>
       </c>
       <c r="D587">
-        <v>2075.10605030643</v>
+        <v>2076.1785042356501</v>
       </c>
       <c r="E587">
-        <v>141.99145145593877</v>
+        <v>141.80588567412346</v>
       </c>
       <c r="F587">
         <v>101.2529</v>
       </c>
       <c r="G587">
-        <v>297.97899999999998</v>
+        <v>298.00700000000001</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15794,19 +15812,19 @@
         <v>84.37</v>
       </c>
       <c r="C588">
-        <v>82561.13</v>
+        <v>82544.63</v>
       </c>
       <c r="D588">
-        <v>2007.2802218470999</v>
+        <v>2010.9412406163201</v>
       </c>
       <c r="E588">
-        <v>141.7819758335674</v>
+        <v>141.61984042213524</v>
       </c>
       <c r="F588">
         <v>100.9552</v>
       </c>
       <c r="G588">
-        <v>298.70800000000003</v>
+        <v>298.786</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15817,19 +15835,19 @@
         <v>76.44</v>
       </c>
       <c r="C589">
-        <v>81944.38</v>
+        <v>81927.88</v>
       </c>
       <c r="D589">
-        <v>2033.5934004471801</v>
+        <v>2034.1256771262399</v>
       </c>
       <c r="E589">
-        <v>141.11956260026543</v>
+        <v>140.93961230073265</v>
       </c>
       <c r="F589">
         <v>99.766400000000004</v>
       </c>
       <c r="G589">
-        <v>298.80799999999999</v>
+        <v>298.83199999999999</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15840,19 +15858,19 @@
         <v>78.12</v>
       </c>
       <c r="C590">
-        <v>82124.56</v>
+        <v>82091.56</v>
       </c>
       <c r="D590">
-        <v>2068.0681740446998</v>
+        <v>2067.1462221632901</v>
       </c>
       <c r="E590">
-        <v>141.62529271196013</v>
+        <v>141.45516232434346</v>
       </c>
       <c r="F590">
         <v>100.505</v>
       </c>
       <c r="G590">
-        <v>300.45600000000002</v>
+        <v>300.42</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15863,19 +15881,19 @@
         <v>76.83</v>
       </c>
       <c r="C591">
-        <v>82773.94</v>
+        <v>82741.63</v>
       </c>
       <c r="D591">
-        <v>2027.42833162785</v>
+        <v>2021.8132338079399</v>
       </c>
       <c r="E591">
-        <v>142.42784692897087</v>
+        <v>142.24732815523618</v>
       </c>
       <c r="F591">
         <v>100.6416</v>
       </c>
       <c r="G591">
-        <v>301.476</v>
+        <v>301.45</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15886,19 +15904,19 @@
         <v>73.28</v>
       </c>
       <c r="C592">
-        <v>82731.56</v>
+        <v>82699.63</v>
       </c>
       <c r="D592">
-        <v>2016.4754738101201</v>
+        <v>2017.5955506360201</v>
       </c>
       <c r="E592">
-        <v>142.57275415587222</v>
+        <v>142.50489486501837</v>
       </c>
       <c r="F592">
         <v>101.0205</v>
       </c>
       <c r="G592">
-        <v>301.64299999999997</v>
+        <v>301.82100000000003</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15909,19 +15927,19 @@
         <v>79.45</v>
       </c>
       <c r="C593">
-        <v>82150.13</v>
+        <v>82114.81</v>
       </c>
       <c r="D593">
-        <v>1984.1730935616799</v>
+        <v>1985.97384727553</v>
       </c>
       <c r="E593">
-        <v>141.62547728660985</v>
+        <v>141.50964977288419</v>
       </c>
       <c r="F593">
         <v>101.253</v>
       </c>
       <c r="G593">
-        <v>302.858</v>
+        <v>302.84500000000003</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15932,19 +15950,19 @@
         <v>71.58</v>
       </c>
       <c r="C594">
-        <v>81381.88</v>
+        <v>81346.44</v>
       </c>
       <c r="D594">
-        <v>1976.5705529218999</v>
+        <v>1979.3665705262199</v>
       </c>
       <c r="E594">
-        <v>142.44571945194784</v>
+        <v>142.3039535870723</v>
       </c>
       <c r="F594">
         <v>100.9286</v>
       </c>
       <c r="G594">
-        <v>303.31599999999997</v>
+        <v>303.334</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15955,19 +15973,19 @@
         <v>70.25</v>
       </c>
       <c r="C595">
-        <v>81978.25</v>
+        <v>81940.5</v>
       </c>
       <c r="D595">
-        <v>1975.55461678082</v>
+        <v>1980.1193524471</v>
       </c>
       <c r="E595">
-        <v>143.01742636471837</v>
+        <v>142.90640034148012</v>
       </c>
       <c r="F595">
         <v>100.11960000000001</v>
       </c>
       <c r="G595">
-        <v>304.09899999999999</v>
+        <v>304.01400000000001</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -15978,19 +15996,19 @@
         <v>76.069999999999993</v>
       </c>
       <c r="C596">
-        <v>81250.94</v>
+        <v>81210.94</v>
       </c>
       <c r="D596">
-        <v>1964.0541987629799</v>
+        <v>1964.73899156887</v>
       </c>
       <c r="E596">
-        <v>142.56849455773181</v>
+        <v>142.40442573493118</v>
       </c>
       <c r="F596">
         <v>100.9067</v>
       </c>
       <c r="G596">
-        <v>304.61500000000001</v>
+        <v>304.60899999999998</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16001,19 +16019,19 @@
         <v>81.39</v>
       </c>
       <c r="C597">
-        <v>80783.94</v>
+        <v>80762.69</v>
       </c>
       <c r="D597">
-        <v>1953.05309645432</v>
+        <v>1953.83062718582</v>
       </c>
       <c r="E597">
-        <v>143.16084305625412</v>
+        <v>143.01127915189505</v>
       </c>
       <c r="F597">
         <v>100.83929999999999</v>
       </c>
       <c r="G597">
-        <v>306.13799999999998</v>
+        <v>306.08199999999999</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16024,19 +16042,19 @@
         <v>89.43</v>
       </c>
       <c r="C598">
-        <v>81745.56</v>
+        <v>81724.31</v>
       </c>
       <c r="D598">
-        <v>1942.60094014728</v>
+        <v>1946.02322556232</v>
       </c>
       <c r="E598">
-        <v>143.4198416198395</v>
+        <v>143.35150642794963</v>
       </c>
       <c r="F598">
         <v>101.0211</v>
       </c>
       <c r="G598">
-        <v>307.37400000000002</v>
+        <v>307.27600000000001</v>
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16047,19 +16065,19 @@
         <v>85.64</v>
       </c>
       <c r="C599">
-        <v>82099.5</v>
+        <v>82078.25</v>
       </c>
       <c r="D599">
-        <v>1944.4009091530399</v>
+        <v>1945.5176154021301</v>
       </c>
       <c r="E599">
-        <v>143.66440021969402</v>
+        <v>143.52873551435749</v>
       </c>
       <c r="F599">
         <v>100.4689</v>
       </c>
       <c r="G599">
-        <v>307.65300000000002</v>
+        <v>307.69600000000003</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16070,19 +16088,19 @@
         <v>77.69</v>
       </c>
       <c r="C600">
-        <v>82915.19</v>
+        <v>82893.69</v>
       </c>
       <c r="D600">
-        <v>1967.1396906284699</v>
+        <v>1970.9590953454499</v>
       </c>
       <c r="E600">
-        <v>144.11589703797998</v>
+        <v>144.01491438554649</v>
       </c>
       <c r="F600">
         <v>100.8639</v>
       </c>
       <c r="G600">
-        <v>308.08699999999999</v>
+        <v>308.14800000000002</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16093,19 +16111,19 @@
         <v>71.900000000000006</v>
       </c>
       <c r="C601">
-        <v>83215.75</v>
+        <v>83199.75</v>
       </c>
       <c r="D601">
-        <v>1962.2275395627501</v>
+        <v>1962.2337548333501</v>
       </c>
       <c r="E601">
-        <v>144.25923961837609</v>
+        <v>144.06551042465961</v>
       </c>
       <c r="F601">
         <v>100.6031</v>
       </c>
       <c r="G601">
-        <v>308.73500000000001</v>
+        <v>308.74099999999999</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16116,19 +16134,19 @@
         <v>74.150000000000006</v>
       </c>
       <c r="C602">
-        <v>81848.31</v>
+        <v>81780.69</v>
       </c>
       <c r="D602">
-        <v>1964.64964745515</v>
+        <v>1963.5157417365899</v>
       </c>
       <c r="E602">
-        <v>143.62968052067822</v>
+        <v>143.47766767134777</v>
       </c>
       <c r="F602">
         <v>99.222300000000004</v>
       </c>
       <c r="G602">
-        <v>309.79399999999998</v>
+        <v>309.69799999999998</v>
       </c>
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16139,19 +16157,19 @@
         <v>77.25</v>
       </c>
       <c r="C603">
-        <v>82540.88</v>
+        <v>82474.13</v>
       </c>
       <c r="D603">
-        <v>1982.83749666313</v>
+        <v>1978.3592108456901</v>
       </c>
       <c r="E603">
-        <v>144.35412774356155</v>
+        <v>144.22185649110688</v>
       </c>
       <c r="F603">
         <v>100.285</v>
       </c>
       <c r="G603">
-        <v>311.02199999999999</v>
+        <v>310.96699999999998</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16162,19 +16180,19 @@
         <v>81.28</v>
       </c>
       <c r="C604">
-        <v>82978.38</v>
+        <v>82884.88</v>
       </c>
       <c r="D604">
-        <v>1967.5023347103199</v>
+        <v>1967.7881871773</v>
       </c>
       <c r="E604">
-        <v>143.93086891497251</v>
+        <v>143.90923674577942</v>
       </c>
       <c r="F604">
         <v>100.4575</v>
       </c>
       <c r="G604">
-        <v>312.10700000000003</v>
+        <v>312.34500000000003</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16185,19 +16203,19 @@
         <v>85.35</v>
       </c>
       <c r="C605">
-        <v>82433.440000000002</v>
+        <v>82351</v>
       </c>
       <c r="D605">
-        <v>1994.29329509222</v>
+        <v>1995.1211427619201</v>
       </c>
       <c r="E605">
-        <v>144.53767445694857</v>
+        <v>144.50524604530958</v>
       </c>
       <c r="F605">
         <v>100.24339999999999</v>
       </c>
       <c r="G605">
-        <v>313.01600000000002</v>
+        <v>313.02300000000002</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16208,19 +16226,19 @@
         <v>80.02</v>
       </c>
       <c r="C606">
-        <v>81733.06</v>
+        <v>81640.38</v>
       </c>
       <c r="D606">
-        <v>1987.8741124256601</v>
+        <v>1991.10903594964</v>
       </c>
       <c r="E606">
-        <v>145.01253898824305</v>
+        <v>144.97598475286594</v>
       </c>
       <c r="F606">
         <v>100.863</v>
       </c>
       <c r="G606">
-        <v>313.14</v>
+        <v>313.17500000000001</v>
       </c>
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16231,19 +16249,19 @@
         <v>79.77</v>
       </c>
       <c r="C607">
-        <v>81435.19</v>
+        <v>81335.19</v>
       </c>
       <c r="D607">
-        <v>1989.8647843732999</v>
+        <v>1993.10966513932</v>
       </c>
       <c r="E607">
-        <v>145.13175820688275</v>
+        <v>144.98852611627615</v>
       </c>
       <c r="F607">
         <v>100.89400000000001</v>
       </c>
       <c r="G607">
-        <v>313.13099999999997</v>
+        <v>313.04399999999998</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16254,19 +16272,19 @@
         <v>81.8</v>
       </c>
       <c r="C608">
-        <v>81715.94</v>
+        <v>81635.81</v>
       </c>
       <c r="D608">
-        <v>1966.1400120822</v>
+        <v>1967.69407090138</v>
       </c>
       <c r="E608">
-        <v>145.48464989616389</v>
+        <v>145.34415303977144</v>
       </c>
       <c r="F608">
         <v>99.975700000000003</v>
       </c>
       <c r="G608">
-        <v>313.56599999999997</v>
+        <v>313.56900000000002</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16277,19 +16295,19 @@
         <v>76.680000000000007</v>
       </c>
       <c r="C609">
-        <v>81938.13</v>
+        <v>81854.94</v>
       </c>
       <c r="D609">
-        <v>1990.7882669386299</v>
+        <v>1991.63125800957</v>
       </c>
       <c r="E609">
-        <v>145.83398914726416</v>
+        <v>145.60409123922608</v>
       </c>
       <c r="F609">
         <v>100.43089999999999</v>
       </c>
       <c r="G609">
-        <v>314.13099999999997</v>
+        <v>314.06200000000001</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16300,19 +16318,19 @@
         <v>70.239999999999995</v>
       </c>
       <c r="C610">
-        <v>80860.38</v>
+        <v>80775.81</v>
       </c>
       <c r="D610">
-        <v>1996.5036865731199</v>
+        <v>2000.7953105434899</v>
       </c>
       <c r="E610">
-        <v>145.7453498293882</v>
+        <v>145.61711612476154</v>
       </c>
       <c r="F610">
         <v>99.808400000000006</v>
       </c>
       <c r="G610">
-        <v>314.851</v>
+        <v>314.73200000000003</v>
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16323,19 +16341,19 @@
         <v>71.989999999999995</v>
       </c>
       <c r="C611">
-        <v>82023.56</v>
+        <v>81926.13</v>
       </c>
       <c r="D611">
-        <v>2004.88290849129</v>
+        <v>2004.85323222442</v>
       </c>
       <c r="E611">
-        <v>146.55848767053618</v>
+        <v>146.38329320972682</v>
       </c>
       <c r="F611">
         <v>99.469499999999996</v>
       </c>
       <c r="G611">
-        <v>315.56400000000002</v>
+        <v>315.63099999999997</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16346,19 +16364,19 @@
         <v>69.95</v>
       </c>
       <c r="C612">
-        <v>82238.38</v>
+        <v>82133.88</v>
       </c>
       <c r="D612">
-        <v>1991.36901132097</v>
+        <v>1995.1591679421199</v>
       </c>
       <c r="E612">
-        <v>146.56452763467027</v>
+        <v>146.43996866414332</v>
       </c>
       <c r="F612">
         <v>99.292500000000004</v>
       </c>
       <c r="G612">
-        <v>316.44900000000001</v>
+        <v>316.52800000000002</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16369,19 +16387,19 @@
         <v>70.12</v>
       </c>
       <c r="C613">
-        <v>82646.5</v>
+        <v>82557.88</v>
       </c>
       <c r="D613">
-        <v>2005.6491404523999</v>
+        <v>2004.7099317212801</v>
       </c>
       <c r="E613">
-        <v>147.65935784377464</v>
+        <v>147.55848999353427</v>
       </c>
       <c r="F613">
         <v>100.32729999999999</v>
       </c>
       <c r="G613">
-        <v>317.60300000000001</v>
+        <v>317.60399999999998</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16392,19 +16410,19 @@
         <v>75.739999999999995</v>
       </c>
       <c r="C614">
-        <v>82376.75</v>
+        <v>82150.31</v>
       </c>
       <c r="D614">
-        <v>2019.5848073862101</v>
+        <v>2015.8714990759499</v>
       </c>
       <c r="E614">
-        <v>147.22694372372359</v>
+        <v>107.084680646179</v>
       </c>
       <c r="F614">
         <v>100.0647</v>
       </c>
       <c r="G614">
-        <v>319.08600000000001</v>
+        <v>318.96100000000001</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16415,19 +16433,19 @@
         <v>71.53</v>
       </c>
       <c r="C615">
-        <v>82666.44</v>
+        <v>82418.38</v>
       </c>
       <c r="D615">
-        <v>2003.4907284979699</v>
+        <v>1996.0877065123</v>
       </c>
       <c r="E615">
-        <v>148.47042263320535</v>
+        <v>107.966246701709</v>
       </c>
       <c r="F615">
         <v>101.0993</v>
       </c>
       <c r="G615">
-        <v>319.77499999999998</v>
+        <v>319.67899999999997</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16438,19 +16456,19 @@
         <v>68.239999999999995</v>
       </c>
       <c r="C616">
-        <v>83778.75</v>
+        <v>83540.94</v>
       </c>
       <c r="D616">
-        <v>2004.9992607783799</v>
+        <v>2001.65554631336</v>
       </c>
       <c r="E616">
-        <v>149.08727424840274</v>
+        <v>108.36047415102099</v>
       </c>
       <c r="F616">
         <v>101.04040000000001</v>
       </c>
       <c r="G616">
-        <v>319.61500000000001</v>
+        <v>319.78500000000003</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16461,19 +16479,19 @@
         <v>63.54</v>
       </c>
       <c r="C617">
-        <v>83227.94</v>
+        <v>82978.25</v>
       </c>
       <c r="D617">
-        <v>1986.8172638992801</v>
+        <v>1985.73278300633</v>
       </c>
       <c r="E617">
-        <v>148.94509250450278</v>
+        <v>108.23326716438</v>
       </c>
       <c r="F617">
         <v>101.1279</v>
       </c>
       <c r="G617">
-        <v>320.32100000000003</v>
+        <v>320.30200000000002</v>
       </c>
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16484,19 +16502,19 @@
         <v>62.17</v>
       </c>
       <c r="C618">
-        <v>83313.13</v>
+        <v>83068.13</v>
       </c>
       <c r="D618">
-        <v>1992.58894702619</v>
+        <v>1993.5968582944499</v>
       </c>
       <c r="E618">
-        <v>149.35412984112781</v>
+        <v>108.601629715882</v>
       </c>
       <c r="F618">
-        <v>100.9773</v>
+        <v>100.96550000000001</v>
       </c>
       <c r="G618">
-        <v>320.58</v>
+        <v>320.62</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -16507,19 +16525,157 @@
         <v>68.17</v>
       </c>
       <c r="C619">
-        <v>84405.13</v>
+        <v>84156.69</v>
       </c>
       <c r="D619">
-        <v>1984.17213663537</v>
+        <v>1988.6415974287499</v>
       </c>
       <c r="E619">
-        <v>149.72210402155815</v>
+        <v>108.959154727925</v>
       </c>
       <c r="F619">
-        <v>101.428</v>
+        <v>101.4785</v>
       </c>
       <c r="G619">
-        <v>321.5</v>
+        <v>321.435</v>
+      </c>
+    </row>
+    <row r="620" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A620" t="s">
+        <v>625</v>
+      </c>
+      <c r="B620">
+        <v>68.39</v>
+      </c>
+      <c r="C620">
+        <v>84562.44</v>
+      </c>
+      <c r="D620">
+        <v>2009.82017959069</v>
+      </c>
+      <c r="E620">
+        <v>109.165462336365</v>
+      </c>
+      <c r="F620">
+        <v>101.89400000000001</v>
+      </c>
+      <c r="G620">
+        <v>322.16899999999998</v>
+      </c>
+    </row>
+    <row r="621" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A621" t="s">
+        <v>626</v>
+      </c>
+      <c r="B621">
+        <v>64.86</v>
+      </c>
+      <c r="C621">
+        <v>85042.75</v>
+      </c>
+      <c r="D621">
+        <v>2026.4874779014499</v>
+      </c>
+      <c r="E621">
+        <v>108.886271701712</v>
+      </c>
+      <c r="F621">
+        <v>101.6247</v>
+      </c>
+      <c r="G621">
+        <v>323.291</v>
+      </c>
+    </row>
+    <row r="622" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A622" t="s">
+        <v>627</v>
+      </c>
+      <c r="B622">
+        <v>63.96</v>
+      </c>
+      <c r="C622">
+        <v>86164.75</v>
+      </c>
+      <c r="D622">
+        <v>2018.8592186267001</v>
+      </c>
+      <c r="E622">
+        <v>109.905439643118</v>
+      </c>
+      <c r="F622">
+        <v>101.66800000000001</v>
+      </c>
+      <c r="G622">
+        <v>324.245</v>
+      </c>
+    </row>
+    <row r="623" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A623" t="s">
+        <v>628</v>
+      </c>
+      <c r="B623">
+        <v>60.89</v>
+      </c>
+      <c r="C623">
+        <v>86110.25</v>
+      </c>
+      <c r="D623">
+        <v>2024.90263173023</v>
+      </c>
+      <c r="E623">
+        <v>109.605428443696</v>
+      </c>
+      <c r="F623">
+        <v>101.2075</v>
+      </c>
+      <c r="G623">
+        <v>324.654</v>
+      </c>
+    </row>
+    <row r="624" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A624" t="s">
+        <v>629</v>
+      </c>
+      <c r="B624">
+        <v>60.06</v>
+      </c>
+      <c r="C624">
+        <v>86079.88</v>
+      </c>
+      <c r="D624">
+        <v>2011.2843671400799</v>
+      </c>
+      <c r="E624">
+        <v>109.942326464494</v>
+      </c>
+      <c r="F624">
+        <v>101.3605</v>
+      </c>
+      <c r="G624">
+        <v>325.06299999999999</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A625" t="s">
+        <v>630</v>
+      </c>
+      <c r="B625">
+        <v>57.97</v>
+      </c>
+      <c r="C625">
+        <v>85891.5</v>
+      </c>
+      <c r="D625">
+        <v>2001.77582591138</v>
+      </c>
+      <c r="E625">
+        <v>110.66823508944</v>
+      </c>
+      <c r="F625">
+        <v>101.6781</v>
+      </c>
+      <c r="G625">
+        <v>326.03100000000001</v>
       </c>
     </row>
   </sheetData>

--- a/VARdata.xlsx
+++ b/VARdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/drk9452_ads_northwestern_edu/Documents/Uni/LBS PhD/Research/Projects/Oil supply shocks/Repositories/OilSupplyNewsUpdate/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{E4666CA9-3A26-40FF-83AF-CBD9E073F10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A21402BA-0A7F-436B-8A9E-0757ED017392}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{E4666CA9-3A26-40FF-83AF-CBD9E073F10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{971446E3-99CA-4E00-B8D5-E5943DD8C0E2}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E64FA3D6-CEF8-4D84-93AC-D7CE42D05F79}"/>
+    <workbookView xWindow="74520" yWindow="5400" windowWidth="6915" windowHeight="4080" xr2:uid="{E64FA3D6-CEF8-4D84-93AC-D7CE42D05F79}"/>
   </bookViews>
   <sheets>
     <sheet name="Monthly" sheetId="2" r:id="rId1"/>
@@ -2340,7 +2340,7 @@
         <v>484.83627615005503</v>
       </c>
       <c r="E2">
-        <v>44.125749999999996</v>
+        <v>32.292669542939812</v>
       </c>
       <c r="F2">
         <v>45.620399999999997</v>
@@ -2363,7 +2363,7 @@
         <v>498.72242650216901</v>
       </c>
       <c r="E3">
-        <v>43.927309999999999</v>
+        <v>32.147444649445632</v>
       </c>
       <c r="F3">
         <v>45.475900000000003</v>
@@ -2386,7 +2386,7 @@
         <v>499.928218427601</v>
       </c>
       <c r="E4">
-        <v>43.89911</v>
+        <v>32.126806965528395</v>
       </c>
       <c r="F4">
         <v>45.477699999999999</v>
@@ -2409,7 +2409,7 @@
         <v>517.34059571160299</v>
       </c>
       <c r="E5">
-        <v>43.91048</v>
+        <v>32.135127904043955</v>
       </c>
       <c r="F5">
         <v>45.345100000000002</v>
@@ -2432,7 +2432,7 @@
         <v>542.17119329404295</v>
       </c>
       <c r="E6">
-        <v>44.127929999999999</v>
+        <v>32.294264938363199</v>
       </c>
       <c r="F6">
         <v>45.7044</v>
@@ -2455,7 +2455,7 @@
         <v>549.29258193285295</v>
       </c>
       <c r="E7">
-        <v>43.998089999999998</v>
+        <v>32.199243772412359</v>
       </c>
       <c r="F7">
         <v>45.623800000000003</v>
@@ -2478,7 +2478,7 @@
         <v>559.23500288419996</v>
       </c>
       <c r="E8">
-        <v>43.593850000000003</v>
+        <v>31.903407696288149</v>
       </c>
       <c r="F8">
         <v>45.722099999999998</v>
@@ -2501,7 +2501,7 @@
         <v>563.48955436039103</v>
       </c>
       <c r="E9">
-        <v>43.529490000000003</v>
+        <v>31.856306939660019</v>
       </c>
       <c r="F9">
         <v>45.236600000000003</v>
@@ -2524,7 +2524,7 @@
         <v>564.19266286016295</v>
       </c>
       <c r="E10">
-        <v>43.026719999999997</v>
+        <v>31.488363381395196</v>
       </c>
       <c r="F10">
         <v>45.236499999999999</v>
@@ -2547,7 +2547,7 @@
         <v>555.19960214761602</v>
       </c>
       <c r="E11">
-        <v>42.58267</v>
+        <v>31.163393042975059</v>
       </c>
       <c r="F11">
         <v>45.113300000000002</v>
@@ -2570,7 +2570,7 @@
         <v>557.60881329119502</v>
       </c>
       <c r="E12">
-        <v>41.762619999999998</v>
+        <v>30.563253585658462</v>
       </c>
       <c r="F12">
         <v>43.627800000000001</v>
@@ -2593,7 +2593,7 @@
         <v>560.70021764103706</v>
       </c>
       <c r="E13">
-        <v>40.561959999999999</v>
+        <v>29.684571260407875</v>
       </c>
       <c r="F13">
         <v>42.0533</v>
@@ -2616,7 +2616,7 @@
         <v>562.20762087289597</v>
       </c>
       <c r="E14">
-        <v>40.073239999999998</v>
+        <v>29.326909952463524</v>
       </c>
       <c r="F14">
         <v>41.467599999999997</v>
@@ -2639,7 +2639,7 @@
         <v>574.77302062368904</v>
       </c>
       <c r="E15">
-        <v>39.660980000000002</v>
+        <v>29.025204577579871</v>
       </c>
       <c r="F15">
         <v>40.516500000000001</v>
@@ -2662,7 +2662,7 @@
         <v>572.51141153411197</v>
       </c>
       <c r="E16">
-        <v>39.349629999999998</v>
+        <v>28.797348446812816</v>
       </c>
       <c r="F16">
         <v>40.063800000000001</v>
@@ -2685,7 +2685,7 @@
         <v>570.28917269764702</v>
       </c>
       <c r="E17">
-        <v>39.36544</v>
+        <v>28.8089187227962</v>
       </c>
       <c r="F17">
         <v>40.157299999999999</v>
@@ -2708,7 +2708,7 @@
         <v>566.35676049622998</v>
       </c>
       <c r="E18">
-        <v>39.108080000000001</v>
+        <v>28.620574242904734</v>
       </c>
       <c r="F18">
         <v>40.025300000000001</v>
@@ -2731,7 +2731,7 @@
         <v>564.76832990079197</v>
       </c>
       <c r="E19">
-        <v>39.415390000000002</v>
+        <v>28.845473769309177</v>
       </c>
       <c r="F19">
         <v>40.277200000000001</v>
@@ -2754,7 +2754,7 @@
         <v>549.16806079458695</v>
       </c>
       <c r="E20">
-        <v>39.45966</v>
+        <v>28.877872005728182</v>
       </c>
       <c r="F20">
         <v>40.699399999999997</v>
@@ -2777,7 +2777,7 @@
         <v>546.09877376894599</v>
       </c>
       <c r="E21">
-        <v>39.632629999999999</v>
+        <v>29.004457118748181</v>
       </c>
       <c r="F21">
         <v>41.099800000000002</v>
@@ -2800,7 +2800,7 @@
         <v>548.64159188733697</v>
       </c>
       <c r="E22">
-        <v>40.017699999999998</v>
+        <v>29.286263960805254</v>
       </c>
       <c r="F22">
         <v>41.630400000000002</v>
@@ -2823,7 +2823,7 @@
         <v>555.32960536166695</v>
       </c>
       <c r="E23">
-        <v>40.422409999999999</v>
+        <v>29.582443998328088</v>
       </c>
       <c r="F23">
         <v>41.813499999999998</v>
@@ -2846,7 +2846,7 @@
         <v>556.86681550651997</v>
       </c>
       <c r="E24">
-        <v>40.619210000000002</v>
+        <v>29.726468686090914</v>
       </c>
       <c r="F24">
         <v>41.869700000000002</v>
@@ -2869,7 +2869,7 @@
         <v>573.44757925939598</v>
       </c>
       <c r="E25">
-        <v>40.929389999999998</v>
+        <v>29.953468572525228</v>
       </c>
       <c r="F25">
         <v>42.441400000000002</v>
@@ -2892,7 +2892,7 @@
         <v>601.38697050040003</v>
       </c>
       <c r="E26">
-        <v>41.389009999999999</v>
+        <v>30.28983354706563</v>
       </c>
       <c r="F26">
         <v>43.001199999999997</v>
@@ -2915,7 +2915,7 @@
         <v>579.15385761932896</v>
       </c>
       <c r="E27">
-        <v>41.840170000000001</v>
+        <v>30.62000721643086</v>
       </c>
       <c r="F27">
         <v>43.422899999999998</v>
@@ -2938,7 +2938,7 @@
         <v>577.57936614764799</v>
       </c>
       <c r="E28">
-        <v>41.971240000000002</v>
+        <v>30.715928536680217</v>
       </c>
       <c r="F28">
         <v>43.516800000000003</v>
@@ -2961,7 +2961,7 @@
         <v>579.85447994678202</v>
       </c>
       <c r="E29">
-        <v>42.454349999999998</v>
+        <v>31.069484262824012</v>
       </c>
       <c r="F29">
         <v>43.732700000000001</v>
@@ -2984,7 +2984,7 @@
         <v>573.76955597157905</v>
       </c>
       <c r="E30">
-        <v>42.869030000000002</v>
+        <v>31.372960672994182</v>
       </c>
       <c r="F30">
         <v>43.918599999999998</v>
@@ -3007,7 +3007,7 @@
         <v>576.19163993235099</v>
       </c>
       <c r="E31">
-        <v>42.861550000000001</v>
+        <v>31.367486563926775</v>
       </c>
       <c r="F31">
         <v>43.963700000000003</v>
@@ -3030,7 +3030,7 @@
         <v>586.85666408723796</v>
       </c>
       <c r="E32">
-        <v>43.07038</v>
+        <v>31.520315199828762</v>
       </c>
       <c r="F32">
         <v>44.214100000000002</v>
@@ -3053,7 +3053,7 @@
         <v>587.89553929038198</v>
       </c>
       <c r="E33">
-        <v>43.109610000000004</v>
+        <v>31.549024999122135</v>
       </c>
       <c r="F33">
         <v>44.5182</v>
@@ -3076,7 +3076,7 @@
         <v>600.19260512750498</v>
       </c>
       <c r="E34">
-        <v>43.54618</v>
+        <v>31.868521228474862</v>
       </c>
       <c r="F34">
         <v>44.6721</v>
@@ -3099,7 +3099,7 @@
         <v>612.37255021482702</v>
       </c>
       <c r="E35">
-        <v>43.592219999999998</v>
+        <v>31.902214808884416</v>
       </c>
       <c r="F35">
         <v>44.658499999999997</v>
@@ -3122,7 +3122,7 @@
         <v>614.25030018425696</v>
       </c>
       <c r="E36">
-        <v>44.03595</v>
+        <v>32.226950960820389</v>
       </c>
       <c r="F36">
         <v>45.339199999999998</v>
@@ -3145,7 +3145,7 @@
         <v>603.23059876331195</v>
       </c>
       <c r="E37">
-        <v>44.202730000000003</v>
+        <v>32.349006029037284</v>
       </c>
       <c r="F37">
         <v>45.8294</v>
@@ -3168,7 +3168,7 @@
         <v>611.38156994624296</v>
       </c>
       <c r="E38">
-        <v>44.399749999999997</v>
+        <v>32.493191720007971</v>
       </c>
       <c r="F38">
         <v>45.508699999999997</v>
@@ -3191,7 +3191,7 @@
         <v>610.41610180429302</v>
       </c>
       <c r="E39">
-        <v>44.431049999999999</v>
+        <v>32.516098085490576</v>
       </c>
       <c r="F39">
         <v>46.227699999999999</v>
@@ -3214,7 +3214,7 @@
         <v>611.04180013447694</v>
       </c>
       <c r="E40">
-        <v>44.688920000000003</v>
+        <v>32.70481580009119</v>
       </c>
       <c r="F40">
         <v>46.8185</v>
@@ -3237,7 +3237,7 @@
         <v>646.13181992873797</v>
       </c>
       <c r="E41">
-        <v>44.666130000000003</v>
+        <v>32.688137331421906</v>
       </c>
       <c r="F41">
         <v>47.2684</v>
@@ -3260,7 +3260,7 @@
         <v>667.34312351963604</v>
       </c>
       <c r="E42">
-        <v>44.818150000000003</v>
+        <v>32.799390548056586</v>
       </c>
       <c r="F42">
         <v>47.641100000000002</v>
@@ -3283,7 +3283,7 @@
         <v>684.12351630247804</v>
       </c>
       <c r="E43">
-        <v>44.836280000000002</v>
+        <v>32.812658676050184</v>
       </c>
       <c r="F43">
         <v>48.011600000000001</v>
@@ -3306,7 +3306,7 @@
         <v>695.564106847419</v>
       </c>
       <c r="E44">
-        <v>44.609050000000003</v>
+        <v>32.646364317308581</v>
       </c>
       <c r="F44">
         <v>48.073</v>
@@ -3329,7 +3329,7 @@
         <v>713.37593134740098</v>
       </c>
       <c r="E45">
-        <v>44.895209999999999</v>
+        <v>32.855785580775098</v>
       </c>
       <c r="F45">
         <v>48.1205</v>
@@ -3352,7 +3352,7 @@
         <v>703.21653261338895</v>
       </c>
       <c r="E46">
-        <v>45.028599999999997</v>
+        <v>32.953404753034668</v>
       </c>
       <c r="F46">
         <v>48.318899999999999</v>
@@ -3375,7 +3375,7 @@
         <v>705.62015513286804</v>
       </c>
       <c r="E47">
-        <v>44.999859999999998</v>
+        <v>32.932371879425403</v>
       </c>
       <c r="F47">
         <v>48.387099999999997</v>
@@ -3398,7 +3398,7 @@
         <v>720.57492538286499</v>
       </c>
       <c r="E48">
-        <v>45.011220000000002</v>
+        <v>32.940685499613338</v>
       </c>
       <c r="F48">
         <v>48.476100000000002</v>
@@ -3421,7 +3421,7 @@
         <v>733.95087814111696</v>
       </c>
       <c r="E49">
-        <v>45.374969999999998</v>
+        <v>33.20688966716277</v>
       </c>
       <c r="F49">
         <v>48.562899999999999</v>
@@ -3444,7 +3444,7 @@
         <v>731.836027914179</v>
       </c>
       <c r="E50">
-        <v>45.28913</v>
+        <v>33.144069142784922</v>
       </c>
       <c r="F50">
         <v>47.848100000000002</v>
@@ -3467,7 +3467,7 @@
         <v>733.37515946753501</v>
       </c>
       <c r="E51">
-        <v>45.133670000000002</v>
+        <v>33.030298421445444</v>
       </c>
       <c r="F51">
         <v>48.104399999999998</v>
@@ -3490,7 +3490,7 @@
         <v>744.03776681546697</v>
       </c>
       <c r="E52">
-        <v>45.484670000000001</v>
+        <v>33.28717172126634</v>
       </c>
       <c r="F52">
         <v>49.026499999999999</v>
@@ -3513,7 +3513,7 @@
         <v>741.31380211176395</v>
       </c>
       <c r="E53">
-        <v>46.526989999999998</v>
+        <v>34.049975646819945</v>
       </c>
       <c r="F53">
         <v>50.020600000000002</v>
@@ -3536,7 +3536,7 @@
         <v>721.32592294738595</v>
       </c>
       <c r="E54">
-        <v>46.19706</v>
+        <v>33.808522063315934</v>
       </c>
       <c r="F54">
         <v>50.253999999999998</v>
@@ -3559,7 +3559,7 @@
         <v>745.80881560666899</v>
       </c>
       <c r="E55">
-        <v>46.451059999999998</v>
+        <v>33.994407585123646</v>
       </c>
       <c r="F55">
         <v>50.580100000000002</v>
@@ -3582,7 +3582,7 @@
         <v>763.49391043891899</v>
       </c>
       <c r="E56">
-        <v>46.605260000000001</v>
+        <v>34.107256197181712</v>
       </c>
       <c r="F56">
         <v>50.538400000000003</v>
@@ -3605,7 +3605,7 @@
         <v>749.47773283597803</v>
       </c>
       <c r="E57">
-        <v>46.900239999999997</v>
+        <v>34.323132225618089</v>
       </c>
       <c r="F57">
         <v>50.745800000000003</v>
@@ -3628,7 +3628,7 @@
         <v>775.70547139848804</v>
       </c>
       <c r="E58">
-        <v>47.256210000000003</v>
+        <v>34.583642734271208</v>
       </c>
       <c r="F58">
         <v>50.874400000000001</v>
@@ -3651,7 +3651,7 @@
         <v>778.08321488622698</v>
       </c>
       <c r="E59">
-        <v>47.410089999999997</v>
+        <v>34.696257159845104</v>
       </c>
       <c r="F59">
         <v>51.255899999999997</v>
@@ -3674,7 +3674,7 @@
         <v>785.48869106963195</v>
       </c>
       <c r="E60">
-        <v>47.709699999999998</v>
+        <v>34.915521573974274</v>
       </c>
       <c r="F60">
         <v>51.651400000000002</v>
@@ -3697,7 +3697,7 @@
         <v>794.37679952483302</v>
       </c>
       <c r="E61">
-        <v>48.442590000000003</v>
+        <v>35.451874487665833</v>
       </c>
       <c r="F61">
         <v>51.908999999999999</v>
@@ -3720,7 +3720,7 @@
         <v>777.91299138162196</v>
       </c>
       <c r="E62">
-        <v>47.553100000000001</v>
+        <v>34.800916563284957</v>
       </c>
       <c r="F62">
         <v>51.627800000000001</v>
@@ -3743,7 +3743,7 @@
         <v>794.43109528699301</v>
       </c>
       <c r="E63">
-        <v>48.014449999999997</v>
+        <v>35.138547608505377</v>
       </c>
       <c r="F63">
         <v>51.8752</v>
@@ -3766,7 +3766,7 @@
         <v>817.97624949451301</v>
       </c>
       <c r="E64">
-        <v>48.24409</v>
+        <v>35.30660568420587</v>
       </c>
       <c r="F64">
         <v>52.044600000000003</v>
@@ -3789,7 +3789,7 @@
         <v>819.44740803750506</v>
       </c>
       <c r="E65">
-        <v>48.3018</v>
+        <v>35.348839752959897</v>
       </c>
       <c r="F65">
         <v>51.4193</v>
@@ -3812,7 +3812,7 @@
         <v>821.75450441937096</v>
       </c>
       <c r="E66">
-        <v>48.656480000000002</v>
+        <v>35.608406197348714</v>
       </c>
       <c r="F66">
         <v>51.885599999999997</v>
@@ -3835,7 +3835,7 @@
         <v>852.525571417999</v>
       </c>
       <c r="E67">
-        <v>48.856630000000003</v>
+        <v>35.754882524867668</v>
       </c>
       <c r="F67">
         <v>51.896500000000003</v>
@@ -3858,7 +3858,7 @@
         <v>835.72127187808201</v>
       </c>
       <c r="E68">
-        <v>48.969990000000003</v>
+        <v>35.8378430868839</v>
       </c>
       <c r="F68">
         <v>51.809699999999999</v>
@@ -3881,7 +3881,7 @@
         <v>858.44526124868105</v>
       </c>
       <c r="E69">
-        <v>49.126100000000001</v>
+        <v>35.952089499519346</v>
       </c>
       <c r="F69">
         <v>51.468400000000003</v>
@@ -3904,7 +3904,7 @@
         <v>874.66837765318201</v>
       </c>
       <c r="E70">
-        <v>49.020589999999999</v>
+        <v>35.874873824692841</v>
       </c>
       <c r="F70">
         <v>51.459699999999998</v>
@@ -3927,7 +3927,7 @@
         <v>898.81076870370498</v>
       </c>
       <c r="E71">
-        <v>49.241840000000003</v>
+        <v>36.036791823511571</v>
       </c>
       <c r="F71">
         <v>51.833399999999997</v>
@@ -3950,7 +3950,7 @@
         <v>904.37665485236403</v>
       </c>
       <c r="E72">
-        <v>49.47119</v>
+        <v>36.204637667710777</v>
       </c>
       <c r="F72">
         <v>51.753100000000003</v>
@@ -3973,7 +3973,7 @@
         <v>906.86517244816196</v>
       </c>
       <c r="E73">
-        <v>49.640689999999999</v>
+        <v>36.328683321043087</v>
       </c>
       <c r="F73">
         <v>51.787799999999997</v>
@@ -3996,7 +3996,7 @@
         <v>928.59672839348798</v>
       </c>
       <c r="E74">
-        <v>49.815550000000002</v>
+        <v>36.4566515979852</v>
       </c>
       <c r="F74">
         <v>52.067900000000002</v>
@@ -4019,7 +4019,7 @@
         <v>949.56640812030798</v>
       </c>
       <c r="E75">
-        <v>49.991300000000003</v>
+        <v>36.585271206086404</v>
       </c>
       <c r="F75">
         <v>52.082000000000001</v>
@@ -4042,7 +4042,7 @@
         <v>942.34000084946399</v>
       </c>
       <c r="E76">
-        <v>50.015659999999997</v>
+        <v>36.60309865219363</v>
       </c>
       <c r="F76">
         <v>51.87</v>
@@ -4065,7 +4065,7 @@
         <v>960.58001604824597</v>
       </c>
       <c r="E77">
-        <v>49.377110000000002</v>
+        <v>36.135786841365622</v>
       </c>
       <c r="F77">
         <v>50.839700000000001</v>
@@ -4088,7 +4088,7 @@
         <v>970.28001591620102</v>
       </c>
       <c r="E78">
-        <v>48.744500000000002</v>
+        <v>35.672822117149963</v>
       </c>
       <c r="F78">
         <v>49.588999999999999</v>
@@ -4111,7 +4111,7 @@
         <v>974.24321173982696</v>
       </c>
       <c r="E79">
-        <v>48.589689999999997</v>
+        <v>35.559527087106453</v>
       </c>
       <c r="F79">
         <v>48.9482</v>
@@ -4134,7 +4134,7 @@
         <v>974.68324608858495</v>
       </c>
       <c r="E80">
-        <v>48.331539999999997</v>
+        <v>35.370604459332192</v>
       </c>
       <c r="F80">
         <v>48.603900000000003</v>
@@ -4157,7 +4157,7 @@
         <v>992.79146483173997</v>
       </c>
       <c r="E81">
-        <v>48.287430000000001</v>
+        <v>35.338323316155275</v>
       </c>
       <c r="F81">
         <v>48.756300000000003</v>
@@ -4180,7 +4180,7 @@
         <v>988.43306588325902</v>
       </c>
       <c r="E82">
-        <v>48.242899999999999</v>
+        <v>35.305734803217881</v>
       </c>
       <c r="F82">
         <v>49.5608</v>
@@ -4203,7 +4203,7 @@
         <v>980.51849101421703</v>
       </c>
       <c r="E83">
-        <v>48.521850000000001</v>
+        <v>35.509879552463005</v>
       </c>
       <c r="F83">
         <v>50.190800000000003</v>
@@ -4226,7 +4226,7 @@
         <v>981.92573101306198</v>
       </c>
       <c r="E84">
-        <v>48.96902</v>
+        <v>35.837133209103776</v>
       </c>
       <c r="F84">
         <v>51.031100000000002</v>
@@ -4249,7 +4249,7 @@
         <v>979.35215202592099</v>
       </c>
       <c r="E85">
-        <v>48.983820000000001</v>
+        <v>35.847964333996508</v>
       </c>
       <c r="F85">
         <v>51.370800000000003</v>
@@ -4272,7 +4272,7 @@
         <v>1004.1966349504</v>
       </c>
       <c r="E86">
-        <v>48.845440000000004</v>
+        <v>35.746693316249456</v>
       </c>
       <c r="F86">
         <v>51.041499999999999</v>
@@ -4295,7 +4295,7 @@
         <v>1021.96067174505</v>
       </c>
       <c r="E87">
-        <v>49.082419999999999</v>
+        <v>35.920123044430525</v>
       </c>
       <c r="F87">
         <v>50.823999999999998</v>
@@ -4318,7 +4318,7 @@
         <v>1060.0149607641899</v>
       </c>
       <c r="E88">
-        <v>48.90804</v>
+        <v>35.792506047214665</v>
       </c>
       <c r="F88">
         <v>51.082599999999999</v>
@@ -4341,7 +4341,7 @@
         <v>1087.86252807389</v>
       </c>
       <c r="E89">
-        <v>48.848390000000002</v>
+        <v>35.748852222900375</v>
       </c>
       <c r="F89">
         <v>50.857999999999997</v>
@@ -4364,7 +4364,7 @@
         <v>1114.00329424439</v>
       </c>
       <c r="E90">
-        <v>48.889569999999999</v>
+        <v>35.778989096081645</v>
       </c>
       <c r="F90">
         <v>51.149500000000003</v>
@@ -4387,7 +4387,7 @@
         <v>1131.0618039568201</v>
       </c>
       <c r="E91">
-        <v>49.105690000000003</v>
+        <v>35.937152792826069</v>
       </c>
       <c r="F91">
         <v>51.4101</v>
@@ -4410,7 +4410,7 @@
         <v>1158.5387186513301</v>
       </c>
       <c r="E92">
-        <v>49.410440000000001</v>
+        <v>36.160178827357178</v>
       </c>
       <c r="F92">
         <v>51.747100000000003</v>
@@ -4433,7 +4433,7 @@
         <v>1132.41154146337</v>
       </c>
       <c r="E93">
-        <v>49.127949999999998</v>
+        <v>35.953443390130957</v>
       </c>
       <c r="F93">
         <v>51.682600000000001</v>
@@ -4456,7 +4456,7 @@
         <v>1167.676328921</v>
       </c>
       <c r="E94">
-        <v>49.284840000000003</v>
+        <v>36.068260632321561</v>
       </c>
       <c r="F94">
         <v>51.433700000000002</v>
@@ -4479,7 +4479,7 @@
         <v>1195.60208086378</v>
       </c>
       <c r="E95">
-        <v>49.30048</v>
+        <v>36.079706496735234</v>
       </c>
       <c r="F95">
         <v>51.028100000000002</v>
@@ -4502,7 +4502,7 @@
         <v>1216.5988533672801</v>
       </c>
       <c r="E96">
-        <v>49.087879999999998</v>
+        <v>35.924118851316649</v>
       </c>
       <c r="F96">
         <v>50.435000000000002</v>
@@ -4525,7 +4525,7 @@
         <v>1241.37521930668</v>
       </c>
       <c r="E97">
-        <v>48.724229999999999</v>
+        <v>35.657987867043516</v>
       </c>
       <c r="F97">
         <v>49.898699999999998</v>
@@ -4548,7 +4548,7 @@
         <v>1249.7705340663699</v>
       </c>
       <c r="E98">
-        <v>48.50826</v>
+        <v>35.499933945213549</v>
       </c>
       <c r="F98">
         <v>48.868499999999997</v>
@@ -4571,7 +4571,7 @@
         <v>1265.33364926421</v>
       </c>
       <c r="E99">
-        <v>48.707389999999997</v>
+        <v>35.645663803314214</v>
       </c>
       <c r="F99">
         <v>49.863599999999998</v>
@@ -4594,7 +4594,7 @@
         <v>1261.5109014585601</v>
       </c>
       <c r="E100">
-        <v>48.738370000000003</v>
+        <v>35.668335982312655</v>
       </c>
       <c r="F100">
         <v>49.532299999999999</v>
@@ -4617,7 +4617,7 @@
         <v>1252.7864022625899</v>
       </c>
       <c r="E101">
-        <v>48.595739999999999</v>
+        <v>35.563954675322755</v>
       </c>
       <c r="F101">
         <v>49.075000000000003</v>
@@ -4640,7 +4640,7 @@
         <v>1250.4423484548399</v>
       </c>
       <c r="E102">
-        <v>48.335929999999998</v>
+        <v>35.373817205161878</v>
       </c>
       <c r="F102">
         <v>48.7483</v>
@@ -4663,7 +4663,7 @@
         <v>1255.71193353885</v>
       </c>
       <c r="E103">
-        <v>48.062019999999997</v>
+        <v>35.173360893042386</v>
       </c>
       <c r="F103">
         <v>48.621400000000001</v>
@@ -4686,7 +4686,7 @@
         <v>1268.8638395708499</v>
       </c>
       <c r="E104">
-        <v>47.847999999999999</v>
+        <v>35.016734045100314</v>
       </c>
       <c r="F104">
         <v>48.461599999999997</v>
@@ -4709,7 +4709,7 @@
         <v>1297.74650868759</v>
       </c>
       <c r="E105">
-        <v>47.622950000000003</v>
+        <v>34.852035081782105</v>
       </c>
       <c r="F105">
         <v>48.019199999999998</v>
@@ -4732,7 +4732,7 @@
         <v>1298.8928005458299</v>
       </c>
       <c r="E106">
-        <v>47.736429999999999</v>
+        <v>34.935083463729896</v>
       </c>
       <c r="F106">
         <v>47.900799999999997</v>
@@ -4755,7 +4755,7 @@
         <v>1314.6366257282</v>
       </c>
       <c r="E107">
-        <v>47.084099999999999</v>
+        <v>34.457686997427437</v>
       </c>
       <c r="F107">
         <v>47.437100000000001</v>
@@ -4778,7 +4778,7 @@
         <v>1339.55137265298</v>
       </c>
       <c r="E108">
-        <v>47.00177</v>
+        <v>34.397435206047795</v>
       </c>
       <c r="F108">
         <v>47.283000000000001</v>
@@ -4801,7 +4801,7 @@
         <v>1340.2283513811799</v>
       </c>
       <c r="E109">
-        <v>46.831600000000002</v>
+        <v>34.272899224764259</v>
       </c>
       <c r="F109">
         <v>46.948500000000003</v>
@@ -4824,7 +4824,7 @@
         <v>1359.9442264742199</v>
       </c>
       <c r="E110">
-        <v>47.397150000000003</v>
+        <v>34.686787243891629</v>
       </c>
       <c r="F110">
         <v>47.823399999999999</v>
@@ -4847,7 +4847,7 @@
         <v>1380.9743567667099</v>
       </c>
       <c r="E111">
-        <v>47.122320000000002</v>
+        <v>34.485657645630155</v>
       </c>
       <c r="F111">
         <v>47.523299999999999</v>
@@ -4870,7 +4870,7 @@
         <v>1382.93330679256</v>
       </c>
       <c r="E112">
-        <v>47.46125</v>
+        <v>34.733697724001367</v>
       </c>
       <c r="F112">
         <v>47.924399999999999</v>
@@ -4893,7 +4893,7 @@
         <v>1396.8031190655099</v>
       </c>
       <c r="E113">
-        <v>47.795279999999998</v>
+        <v>34.978151821833769</v>
       </c>
       <c r="F113">
         <v>48.531100000000002</v>
@@ -4916,7 +4916,7 @@
         <v>1396.39199577361</v>
       </c>
       <c r="E114">
-        <v>47.956159999999997</v>
+        <v>35.095889076748833</v>
       </c>
       <c r="F114">
         <v>48.823900000000002</v>
@@ -4939,7 +4939,7 @@
         <v>1410.27194226348</v>
       </c>
       <c r="E115">
-        <v>48.25271</v>
+        <v>35.312914082623159</v>
       </c>
       <c r="F115">
         <v>49.122999999999998</v>
@@ -4962,7 +4962,7 @@
         <v>1396.8222269642199</v>
       </c>
       <c r="E116">
-        <v>48.384399999999999</v>
+        <v>35.409289139185589</v>
       </c>
       <c r="F116">
         <v>49.854599999999998</v>
@@ -4985,7 +4985,7 @@
         <v>1452.8715502252501</v>
       </c>
       <c r="E117">
-        <v>48.852400000000003</v>
+        <v>35.751786872280114</v>
       </c>
       <c r="F117">
         <v>50.444299999999998</v>
@@ -5008,7 +5008,7 @@
         <v>1482.25854480575</v>
       </c>
       <c r="E118">
-        <v>49.355849999999997</v>
+        <v>36.120228076823786</v>
       </c>
       <c r="F118">
         <v>51.177999999999997</v>
@@ -5031,7 +5031,7 @@
         <v>1482.9464717204601</v>
       </c>
       <c r="E119">
-        <v>49.540480000000002</v>
+        <v>36.255346359860631</v>
       </c>
       <c r="F119">
         <v>51.569299999999998</v>
@@ -5054,7 +5054,7 @@
         <v>1474.7106179073</v>
       </c>
       <c r="E120">
-        <v>49.890920000000001</v>
+        <v>36.511809833334233</v>
       </c>
       <c r="F120">
         <v>51.799300000000002</v>
@@ -5077,7 +5077,7 @@
         <v>1501.7189958608801</v>
       </c>
       <c r="E121">
-        <v>50.2986</v>
+        <v>36.810163414163242</v>
       </c>
       <c r="F121">
         <v>52.059399999999997</v>
@@ -5100,7 +5100,7 @@
         <v>1509.6212803404001</v>
       </c>
       <c r="E122">
-        <v>50.739400000000003</v>
+        <v>37.132755296103561</v>
       </c>
       <c r="F122">
         <v>53.098500000000001</v>
@@ -5123,7 +5123,7 @@
         <v>1500.9736953531201</v>
       </c>
       <c r="E123">
-        <v>51.004759999999997</v>
+        <v>37.326954438099207</v>
       </c>
       <c r="F123">
         <v>53.331800000000001</v>
@@ -5146,7 +5146,7 @@
         <v>1509.3283716557701</v>
       </c>
       <c r="E124">
-        <v>50.919649999999997</v>
+        <v>37.264668151638361</v>
       </c>
       <c r="F124">
         <v>53.5929</v>
@@ -5169,7 +5169,7 @@
         <v>1529.1330706697099</v>
       </c>
       <c r="E125">
-        <v>50.998869999999997</v>
+        <v>37.322643943125001</v>
       </c>
       <c r="F125">
         <v>53.91</v>
@@ -5192,7 +5192,7 @@
         <v>1572.35316004693</v>
       </c>
       <c r="E126">
-        <v>51.621510000000001</v>
+        <v>37.778312294693329</v>
       </c>
       <c r="F126">
         <v>54.202599999999997</v>
@@ -5215,7 +5215,7 @@
         <v>1582.2126393542801</v>
       </c>
       <c r="E127">
-        <v>51.330829999999999</v>
+        <v>37.56558314713795</v>
       </c>
       <c r="F127">
         <v>54.401400000000002</v>
@@ -5238,7 +5238,7 @@
         <v>1594.6658944276201</v>
       </c>
       <c r="E128">
-        <v>51.912140000000001</v>
+        <v>37.991004850610558</v>
       </c>
       <c r="F128">
         <v>54.552100000000003</v>
@@ -5261,7 +5261,7 @@
         <v>1587.2090256481599</v>
       </c>
       <c r="E129">
-        <v>52.300179999999997</v>
+        <v>38.274985235973801</v>
       </c>
       <c r="F129">
         <v>54.6083</v>
@@ -5284,7 +5284,7 @@
         <v>1580.7773999240901</v>
       </c>
       <c r="E130">
-        <v>52.22195</v>
+        <v>38.217733958922551</v>
       </c>
       <c r="F130">
         <v>54.446599999999997</v>
@@ -5307,7 +5307,7 @@
         <v>1615.85564500703</v>
       </c>
       <c r="E131">
-        <v>52.347999999999999</v>
+        <v>38.309981478701538</v>
       </c>
       <c r="F131">
         <v>54.440600000000003</v>
@@ -5330,7 +5330,7 @@
         <v>1630.14677633721</v>
       </c>
       <c r="E132">
-        <v>52.42436</v>
+        <v>38.36586422848594</v>
       </c>
       <c r="F132">
         <v>54.624000000000002</v>
@@ -5353,7 +5353,7 @@
         <v>1651.4975371809501</v>
       </c>
       <c r="E133">
-        <v>52.719349999999999</v>
+        <v>38.581747575249949</v>
       </c>
       <c r="F133">
         <v>54.641599999999997</v>
@@ -5376,7 +5376,7 @@
         <v>1634.30681337995</v>
       </c>
       <c r="E134">
-        <v>52.844009999999997</v>
+        <v>38.672977847488333</v>
       </c>
       <c r="F134">
         <v>54.632199999999997</v>
@@ -5399,7 +5399,7 @@
         <v>1613.1268899991701</v>
       </c>
       <c r="E135">
-        <v>53.0092</v>
+        <v>38.793869301612027</v>
       </c>
       <c r="F135">
         <v>54.782499999999999</v>
@@ -5422,7 +5422,7 @@
         <v>1636.49059490584</v>
       </c>
       <c r="E136">
-        <v>53.283329999999999</v>
+        <v>38.994486616939383</v>
       </c>
       <c r="F136">
         <v>54.865299999999998</v>
@@ -5445,7 +5445,7 @@
         <v>1662.3604126267101</v>
       </c>
       <c r="E137">
-        <v>53.098439999999997</v>
+        <v>38.859178057384149</v>
       </c>
       <c r="F137">
         <v>54.745899999999999</v>
@@ -5468,7 +5468,7 @@
         <v>1708.0904958270501</v>
       </c>
       <c r="E138">
-        <v>53.583889999999997</v>
+        <v>39.21444627219342</v>
       </c>
       <c r="F138">
         <v>54.825499999999998</v>
@@ -5491,7 +5491,7 @@
         <v>1693.47935636549</v>
       </c>
       <c r="E139">
-        <v>53.542560000000002</v>
+        <v>39.184199624097701</v>
       </c>
       <c r="F139">
         <v>54.798900000000003</v>
@@ -5514,7 +5514,7 @@
         <v>1673.5777450266201</v>
       </c>
       <c r="E140">
-        <v>53.595880000000001</v>
+        <v>39.223220947022057</v>
       </c>
       <c r="F140">
         <v>54.5396</v>
@@ -5537,7 +5537,7 @@
         <v>1675.6370986654799</v>
       </c>
       <c r="E141">
-        <v>53.683480000000003</v>
+        <v>39.287329497062828</v>
       </c>
       <c r="F141">
         <v>54.705500000000001</v>
@@ -5560,7 +5560,7 @@
         <v>1684.91039113587</v>
       </c>
       <c r="E142">
-        <v>53.77346</v>
+        <v>39.353179809079592</v>
       </c>
       <c r="F142">
         <v>54.890599999999999</v>
@@ -5583,7 +5583,7 @@
         <v>1665.08269077614</v>
       </c>
       <c r="E143">
-        <v>53.881509999999999</v>
+        <v>39.432254339124171</v>
       </c>
       <c r="F143">
         <v>54.719900000000003</v>
@@ -5606,7 +5606,7 @@
         <v>1684.98595103302</v>
       </c>
       <c r="E144">
-        <v>54.198779999999999</v>
+        <v>39.664442919848319</v>
       </c>
       <c r="F144">
         <v>54.912399999999998</v>
@@ -5629,7 +5629,7 @@
         <v>1690.9385518353099</v>
       </c>
       <c r="E145">
-        <v>54.096069999999997</v>
+        <v>39.589276376758278</v>
       </c>
       <c r="F145">
         <v>55.441200000000002</v>
@@ -5652,7 +5652,7 @@
         <v>1702.54328523714</v>
       </c>
       <c r="E146">
-        <v>54.409689999999998</v>
+        <v>39.818793767897397</v>
       </c>
       <c r="F146">
         <v>55.748100000000001</v>
@@ -5675,7 +5675,7 @@
         <v>1706.6395637309699</v>
       </c>
       <c r="E147">
-        <v>54.23668</v>
+        <v>39.692179381566874</v>
       </c>
       <c r="F147">
         <v>55.3568</v>
@@ -5698,7 +5698,7 @@
         <v>1728.7617107926999</v>
       </c>
       <c r="E148">
-        <v>54.149360000000001</v>
+        <v>39.628275744699749</v>
       </c>
       <c r="F148">
         <v>54.962499999999999</v>
@@ -5721,7 +5721,7 @@
         <v>1721.97212495489</v>
       </c>
       <c r="E149">
-        <v>54.473750000000003</v>
+        <v>39.865674974696617</v>
       </c>
       <c r="F149">
         <v>55.0413</v>
@@ -5744,7 +5744,7 @@
         <v>1706.9520387513901</v>
       </c>
       <c r="E150">
-        <v>54.132719999999999</v>
+        <v>39.616098047523053</v>
       </c>
       <c r="F150">
         <v>55.122599999999998</v>
@@ -5767,7 +5767,7 @@
         <v>1709.12105969185</v>
       </c>
       <c r="E151">
-        <v>54.4163</v>
+        <v>39.823631182460971</v>
       </c>
       <c r="F151">
         <v>54.900500000000001</v>
@@ -5790,7 +5790,7 @@
         <v>1746.3120083287299</v>
       </c>
       <c r="E152">
-        <v>54.712130000000002</v>
+        <v>40.040129268745915</v>
       </c>
       <c r="F152">
         <v>55.2592</v>
@@ -5813,7 +5813,7 @@
         <v>1742.49174803399</v>
       </c>
       <c r="E153">
-        <v>54.431100000000001</v>
+        <v>39.834462307353704</v>
       </c>
       <c r="F153">
         <v>55.156700000000001</v>
@@ -5836,7 +5836,7 @@
         <v>1763.8859684578199</v>
       </c>
       <c r="E154">
-        <v>54.88353</v>
+        <v>40.165565404327971</v>
       </c>
       <c r="F154">
         <v>55.297499999999999</v>
@@ -5859,7 +5859,7 @@
         <v>1764.4848625541099</v>
       </c>
       <c r="E155">
-        <v>55.022260000000003</v>
+        <v>40.267092563542086</v>
       </c>
       <c r="F155">
         <v>55.533200000000001</v>
@@ -5882,7 +5882,7 @@
         <v>1762.27128438878</v>
       </c>
       <c r="E156">
-        <v>54.996259999999999</v>
+        <v>40.248064911703494</v>
       </c>
       <c r="F156">
         <v>55.755699999999997</v>
@@ -5905,7 +5905,7 @@
         <v>1752.6787797264401</v>
       </c>
       <c r="E157">
-        <v>55.36692</v>
+        <v>40.519326043645414</v>
       </c>
       <c r="F157">
         <v>56.284500000000001</v>
@@ -5928,7 +5928,7 @@
         <v>1750.03603931672</v>
       </c>
       <c r="E158">
-        <v>54.7378</v>
+        <v>40.058915415772702</v>
       </c>
       <c r="F158">
         <v>56.088200000000001</v>
@@ -5951,7 +5951,7 @@
         <v>1750.09874833665</v>
       </c>
       <c r="E159">
-        <v>55.975000000000001</v>
+        <v>40.964338910184132</v>
       </c>
       <c r="F159">
         <v>56.827500000000001</v>
@@ -5974,7 +5974,7 @@
         <v>1754.01281009434</v>
       </c>
       <c r="E160">
-        <v>55.844900000000003</v>
+        <v>40.869127467714911</v>
       </c>
       <c r="F160">
         <v>56.909799999999997</v>
@@ -5997,7 +5997,7 @@
         <v>1749.15907323653</v>
       </c>
       <c r="E161">
-        <v>56.161839999999998</v>
+        <v>41.101074543627256</v>
       </c>
       <c r="F161">
         <v>57.270099999999999</v>
@@ -6020,7 +6020,7 @@
         <v>1748.33812038581</v>
       </c>
       <c r="E162">
-        <v>56.404899999999998</v>
+        <v>41.278953815007505</v>
       </c>
       <c r="F162">
         <v>57.632199999999997</v>
@@ -6043,7 +6043,7 @@
         <v>1764.5841992865301</v>
       </c>
       <c r="E163">
-        <v>56.569569999999999</v>
+        <v>41.399464716094421</v>
       </c>
       <c r="F163">
         <v>57.930700000000002</v>
@@ -6066,7 +6066,7 @@
         <v>1764.6241384816899</v>
       </c>
       <c r="E164">
-        <v>56.704039999999999</v>
+        <v>41.497874267738055</v>
       </c>
       <c r="F164">
         <v>58.325800000000001</v>
@@ -6089,7 +6089,7 @@
         <v>1796.3881956114701</v>
       </c>
       <c r="E165">
-        <v>56.920569999999998</v>
+        <v>41.656338015915317</v>
       </c>
       <c r="F165">
         <v>58.763599999999997</v>
@@ -6112,7 +6112,7 @@
         <v>1823.45656963786</v>
       </c>
       <c r="E166">
-        <v>57.321739999999998</v>
+        <v>41.94992736545705</v>
       </c>
       <c r="F166">
         <v>58.995100000000001</v>
@@ -6135,7 +6135,7 @@
         <v>1846.6163981857001</v>
       </c>
       <c r="E167">
-        <v>58.016030000000001</v>
+        <v>42.458031534495944</v>
       </c>
       <c r="F167">
         <v>59.780999999999999</v>
@@ -6158,7 +6158,7 @@
         <v>1874.98203435358</v>
       </c>
       <c r="E168">
-        <v>58.333440000000003</v>
+        <v>42.690322571806917</v>
       </c>
       <c r="F168">
         <v>60.072600000000001</v>
@@ -6181,7 +6181,7 @@
         <v>1853.2996196425099</v>
       </c>
       <c r="E169">
-        <v>58.501609999999999</v>
+        <v>42.813394887564407</v>
       </c>
       <c r="F169">
         <v>60.409500000000001</v>
@@ -6204,7 +6204,7 @@
         <v>2023.9073933641801</v>
       </c>
       <c r="E170">
-        <v>58.993429999999996</v>
+        <v>43.173324877074123</v>
       </c>
       <c r="F170">
         <v>60.397599999999997</v>
@@ -6227,7 +6227,7 @@
         <v>2016.63847671851</v>
       </c>
       <c r="E171">
-        <v>59.251939999999998</v>
+        <v>43.362510964643072</v>
       </c>
       <c r="F171">
         <v>60.700299999999999</v>
@@ -6250,7 +6250,7 @@
         <v>2004.96288346137</v>
       </c>
       <c r="E172">
-        <v>59.396830000000001</v>
+        <v>43.468546213677406</v>
       </c>
       <c r="F172">
         <v>60.850099999999998</v>
@@ -6273,7 +6273,7 @@
         <v>2004.91086615584</v>
       </c>
       <c r="E173">
-        <v>59.494579999999999</v>
+        <v>43.540082866262857</v>
       </c>
       <c r="F173">
         <v>61.203099999999999</v>
@@ -6296,7 +6296,7 @@
         <v>2015.3271945936899</v>
       </c>
       <c r="E174">
-        <v>59.54889</v>
+        <v>43.57982870362261</v>
       </c>
       <c r="F174">
         <v>61.079700000000003</v>
@@ -6319,7 +6319,7 @@
         <v>2033.61441207186</v>
       </c>
       <c r="E175">
-        <v>59.885019999999997</v>
+        <v>43.825819650257358</v>
       </c>
       <c r="F175">
         <v>61.256900000000002</v>
@@ -6342,7 +6342,7 @@
         <v>2042.6897333617801</v>
       </c>
       <c r="E176">
-        <v>59.770510000000002</v>
+        <v>43.742017480563653</v>
       </c>
       <c r="F176">
         <v>61.265900000000002</v>
@@ -6365,7 +6365,7 @@
         <v>2020.0848113941099</v>
       </c>
       <c r="E177">
-        <v>60.24456</v>
+        <v>44.088942801874467</v>
       </c>
       <c r="F177">
         <v>61.573099999999997</v>
@@ -6388,7 +6388,7 @@
         <v>2022.35672736161</v>
       </c>
       <c r="E178">
-        <v>60.490200000000002</v>
+        <v>44.268710201783314</v>
       </c>
       <c r="F178">
         <v>61.380699999999997</v>
@@ -6411,7 +6411,7 @@
         <v>2031.06497640115</v>
       </c>
       <c r="E179">
-        <v>60.498629999999999</v>
+        <v>44.274879551975594</v>
       </c>
       <c r="F179">
         <v>61.645299999999999</v>
@@ -6434,7 +6434,7 @@
         <v>2020.0295914513099</v>
       </c>
       <c r="E180">
-        <v>60.89434</v>
+        <v>44.564473094631225</v>
       </c>
       <c r="F180">
         <v>61.794400000000003</v>
@@ -6457,7 +6457,7 @@
         <v>2016.6124508375501</v>
       </c>
       <c r="E181">
-        <v>61.43759</v>
+        <v>44.962041243143197</v>
       </c>
       <c r="F181">
         <v>62.074300000000001</v>
@@ -6480,7 +6480,7 @@
         <v>2019.0776873085699</v>
       </c>
       <c r="E182">
-        <v>61.430070000000001</v>
+        <v>44.956537860765266</v>
       </c>
       <c r="F182">
         <v>62.257399999999997</v>
@@ -6503,7 +6503,7 @@
         <v>2006.8453015699499</v>
       </c>
       <c r="E183">
-        <v>61.16666</v>
+        <v>44.763765792657509</v>
       </c>
       <c r="F183">
         <v>61.981900000000003</v>
@@ -6526,7 +6526,7 @@
         <v>2001.8300759139399</v>
       </c>
       <c r="E184">
-        <v>61.666080000000001</v>
+        <v>45.129257711166204</v>
       </c>
       <c r="F184">
         <v>62.136899999999997</v>
@@ -6549,7 +6549,7 @@
         <v>2018.9668310028301</v>
       </c>
       <c r="E185">
-        <v>62.058599999999998</v>
+        <v>45.416516707307792</v>
       </c>
       <c r="F185">
         <v>62.127600000000001</v>
@@ -6572,7 +6572,7 @@
         <v>2030.4719350370799</v>
       </c>
       <c r="E186">
-        <v>61.599159999999998</v>
+        <v>45.080283462664738</v>
       </c>
       <c r="F186">
         <v>61.7744</v>
@@ -6595,7 +6595,7 @@
         <v>2022.8809796237399</v>
       </c>
       <c r="E187">
-        <v>62.248100000000001</v>
+        <v>45.555199015900556</v>
       </c>
       <c r="F187">
         <v>61.7697</v>
@@ -6618,7 +6618,7 @@
         <v>2028.6667267841599</v>
       </c>
       <c r="E188">
-        <v>61.864139999999999</v>
+        <v>45.274204508210438</v>
       </c>
       <c r="F188">
         <v>61.1738</v>
@@ -6641,7 +6641,7 @@
         <v>2063.7428594550101</v>
       </c>
       <c r="E189">
-        <v>62.127679999999998</v>
+        <v>45.467071714577386</v>
       </c>
       <c r="F189">
         <v>61.773200000000003</v>
@@ -6664,7 +6664,7 @@
         <v>2065.78823302418</v>
       </c>
       <c r="E190">
-        <v>62.092080000000003</v>
+        <v>45.441018468213791</v>
       </c>
       <c r="F190">
         <v>61.579599999999999</v>
@@ -6687,7 +6687,7 @@
         <v>2047.4003758466299</v>
       </c>
       <c r="E191">
-        <v>62.005710000000001</v>
+        <v>45.377810072471533</v>
       </c>
       <c r="F191">
         <v>61.496600000000001</v>
@@ -6710,7 +6710,7 @@
         <v>2098.3960554108999</v>
       </c>
       <c r="E192">
-        <v>62.286499999999997</v>
+        <v>45.583301394000621</v>
       </c>
       <c r="F192">
         <v>61.7044</v>
@@ -6733,7 +6733,7 @@
         <v>2136.11003086338</v>
       </c>
       <c r="E193">
-        <v>62.767719999999997</v>
+        <v>45.935473956222303</v>
       </c>
       <c r="F193">
         <v>62.0428</v>
@@ -6756,7 +6756,7 @@
         <v>2098.6607787483299</v>
       </c>
       <c r="E194">
-        <v>62.518689999999999</v>
+        <v>45.753225643246815</v>
       </c>
       <c r="F194">
         <v>61.728999999999999</v>
@@ -6779,7 +6779,7 @@
         <v>2067.07422543959</v>
       </c>
       <c r="E195">
-        <v>62.772950000000002</v>
+        <v>45.939301441572916</v>
       </c>
       <c r="F195">
         <v>62.2896</v>
@@ -6802,7 +6802,7 @@
         <v>2143.7467707833298</v>
       </c>
       <c r="E196">
-        <v>63.038029999999999</v>
+        <v>46.133295670394915</v>
       </c>
       <c r="F196">
         <v>62.599899999999998</v>
@@ -6825,7 +6825,7 @@
         <v>2159.90877471056</v>
       </c>
       <c r="E197">
-        <v>62.392319999999998</v>
+        <v>45.660743936983657</v>
       </c>
       <c r="F197">
         <v>62.435899999999997</v>
@@ -6848,7 +6848,7 @@
         <v>2196.0816857139298</v>
       </c>
       <c r="E198">
-        <v>63.092370000000003</v>
+        <v>46.173063462737559</v>
       </c>
       <c r="F198">
         <v>62.625799999999998</v>
@@ -6871,7 +6871,7 @@
         <v>2203.67175783117</v>
       </c>
       <c r="E199">
-        <v>63.31662</v>
+        <v>46.337176959845351</v>
       </c>
       <c r="F199">
         <v>62.838200000000001</v>
@@ -6894,7 +6894,7 @@
         <v>2165.6398492779899</v>
       </c>
       <c r="E200">
-        <v>63.307160000000003</v>
+        <v>46.330253821907164</v>
       </c>
       <c r="F200">
         <v>62.728400000000001</v>
@@ -6917,7 +6917,7 @@
         <v>2151.9420418507798</v>
       </c>
       <c r="E201">
-        <v>63.65352</v>
+        <v>46.583731417707632</v>
       </c>
       <c r="F201">
         <v>62.947499999999998</v>
@@ -6940,7 +6940,7 @@
         <v>2119.7231131488502</v>
       </c>
       <c r="E202">
-        <v>63.781280000000002</v>
+        <v>46.677230371511385</v>
       </c>
       <c r="F202">
         <v>62.952300000000001</v>
@@ -6963,7 +6963,7 @@
         <v>2129.5347940791798</v>
       </c>
       <c r="E203">
-        <v>63.738419999999998</v>
+        <v>46.64586401928824</v>
       </c>
       <c r="F203">
         <v>62.584499999999998</v>
@@ -6986,7 +6986,7 @@
         <v>2118.7162370866199</v>
       </c>
       <c r="E204">
-        <v>63.43197</v>
+        <v>46.421593869059997</v>
       </c>
       <c r="F204">
         <v>61.788699999999999</v>
@@ -7009,7 +7009,7 @@
         <v>2116.3398882164602</v>
       </c>
       <c r="E205">
-        <v>63.300690000000003</v>
+        <v>46.325518863930405</v>
       </c>
       <c r="F205">
         <v>61.3352</v>
@@ -7032,7 +7032,7 @@
         <v>2105.6710718805002</v>
       </c>
       <c r="E206">
-        <v>63.428980000000003</v>
+        <v>46.419405689098561</v>
       </c>
       <c r="F206">
         <v>61.1355</v>
@@ -7055,7 +7055,7 @@
         <v>2110.0964576206402</v>
       </c>
       <c r="E207">
-        <v>62.983730000000001</v>
+        <v>46.340114135967305</v>
       </c>
       <c r="F207">
         <v>60.683799999999998</v>
@@ -7078,7 +7078,7 @@
         <v>2133.21989380271</v>
       </c>
       <c r="E208">
-        <v>62.733409999999999</v>
+        <v>46.056073036145968</v>
       </c>
       <c r="F208">
         <v>60.334600000000002</v>
@@ -7101,7 +7101,7 @@
         <v>2089.0596246443201</v>
       </c>
       <c r="E209">
-        <v>63.189390000000003</v>
+        <v>46.057498612310333</v>
       </c>
       <c r="F209">
         <v>60.4938</v>
@@ -7124,7 +7124,7 @@
         <v>2081.7497460497402</v>
       </c>
       <c r="E210">
-        <v>63.47475</v>
+        <v>46.319782539882183</v>
       </c>
       <c r="F210">
         <v>61.063299999999998</v>
@@ -7147,7 +7147,7 @@
         <v>2083.7379150278698</v>
       </c>
       <c r="E211">
-        <v>63.57452</v>
+        <v>46.363333071127755</v>
       </c>
       <c r="F211">
         <v>61.558100000000003</v>
@@ -7170,7 +7170,7 @@
         <v>2096.1317664871899</v>
       </c>
       <c r="E212">
-        <v>63.656730000000003</v>
+        <v>46.511117589656422</v>
       </c>
       <c r="F212">
         <v>61.730499999999999</v>
@@ -7193,7 +7193,7 @@
         <v>2103.74327767469</v>
       </c>
       <c r="E213">
-        <v>63.62811</v>
+        <v>46.446696067975452</v>
       </c>
       <c r="F213">
         <v>61.729799999999997</v>
@@ -7216,7 +7216,7 @@
         <v>2124.6486224273699</v>
       </c>
       <c r="E214">
-        <v>63.817039999999999</v>
+        <v>46.426071091401035</v>
       </c>
       <c r="F214">
         <v>62.219499999999996</v>
@@ -7239,7 +7239,7 @@
         <v>2111.21818240837</v>
       </c>
       <c r="E215">
-        <v>63.996630000000003</v>
+        <v>46.591802779168304</v>
       </c>
       <c r="F215">
         <v>62.185499999999998</v>
@@ -7262,7 +7262,7 @@
         <v>2117.12366619062</v>
       </c>
       <c r="E216">
-        <v>64.01737</v>
+        <v>46.573989479785041</v>
       </c>
       <c r="F216">
         <v>62.0871</v>
@@ -7285,7 +7285,7 @@
         <v>2087.4294362266401</v>
       </c>
       <c r="E217">
-        <v>63.506169999999997</v>
+        <v>46.223360213357999</v>
       </c>
       <c r="F217">
         <v>61.785200000000003</v>
@@ -7308,7 +7308,7 @@
         <v>2110.4332130594898</v>
       </c>
       <c r="E218">
-        <v>63.777470000000001</v>
+        <v>46.599578748748662</v>
       </c>
       <c r="F218">
         <v>61.461599999999997</v>
@@ -7331,7 +7331,7 @@
         <v>2130.1898400232699</v>
       </c>
       <c r="E219">
-        <v>64.219200000000001</v>
+        <v>46.781846164540184</v>
       </c>
       <c r="F219">
         <v>61.895499999999998</v>
@@ -7354,7 +7354,7 @@
         <v>2106.3740993977599</v>
       </c>
       <c r="E220">
-        <v>64.160769999999999</v>
+        <v>46.692780877493512</v>
       </c>
       <c r="F220">
         <v>62.423200000000001</v>
@@ -7377,7 +7377,7 @@
         <v>2111.9216914859499</v>
       </c>
       <c r="E221">
-        <v>64.293139999999994</v>
+        <v>46.720044926721357</v>
       </c>
       <c r="F221">
         <v>62.896999999999998</v>
@@ -7400,7 +7400,7 @@
         <v>2106.8945855012698</v>
       </c>
       <c r="E222">
-        <v>64.102890000000002</v>
+        <v>46.44479523226687</v>
       </c>
       <c r="F222">
         <v>63.103999999999999</v>
@@ -7423,7 +7423,7 @@
         <v>2092.3889842240701</v>
       </c>
       <c r="E223">
-        <v>64.191689999999994</v>
+        <v>46.540181420314646</v>
       </c>
       <c r="F223">
         <v>63.136299999999999</v>
@@ -7446,7 +7446,7 @@
         <v>2094.9232001533901</v>
       </c>
       <c r="E224">
-        <v>64.492429999999999</v>
+        <v>46.624394098508148</v>
       </c>
       <c r="F224">
         <v>63.717599999999997</v>
@@ -7469,7 +7469,7 @@
         <v>2108.61065299966</v>
       </c>
       <c r="E225">
-        <v>64.070449999999994</v>
+        <v>46.354421541190376</v>
       </c>
       <c r="F225">
         <v>63.3613</v>
@@ -7492,7 +7492,7 @@
         <v>2106.6100380104899</v>
       </c>
       <c r="E226">
-        <v>64.415989999999994</v>
+        <v>46.750814007529804</v>
       </c>
       <c r="F226">
         <v>63.570300000000003</v>
@@ -7515,7 +7515,7 @@
         <v>2112.8911482399199</v>
       </c>
       <c r="E227">
-        <v>64.52534</v>
+        <v>46.837151908251549</v>
       </c>
       <c r="F227">
         <v>63.999499999999998</v>
@@ -7538,7 +7538,7 @@
         <v>2102.35392232309</v>
       </c>
       <c r="E228">
-        <v>64.485429999999994</v>
+        <v>46.659013876244522</v>
       </c>
       <c r="F228">
         <v>64.242199999999997</v>
@@ -7561,7 +7561,7 @@
         <v>2124.0695062324398</v>
       </c>
       <c r="E229">
-        <v>64.116140000000001</v>
+        <v>46.396802055828651</v>
       </c>
       <c r="F229">
         <v>64.350700000000003</v>
@@ -7584,7 +7584,7 @@
         <v>2135.6921582171299</v>
       </c>
       <c r="E230">
-        <v>64.612930000000006</v>
+        <v>46.81391995458398</v>
       </c>
       <c r="F230">
         <v>64.597800000000007</v>
@@ -7607,7 +7607,7 @@
         <v>2125.9488640939899</v>
       </c>
       <c r="E231">
-        <v>65.0715</v>
+        <v>47.15360983694007</v>
       </c>
       <c r="F231">
         <v>64.908900000000003</v>
@@ -7630,7 +7630,7 @@
         <v>2136.9655347548201</v>
       </c>
       <c r="E232">
-        <v>65.014880000000005</v>
+        <v>46.98237058753913</v>
       </c>
       <c r="F232">
         <v>64.852199999999996</v>
@@ -7653,7 +7653,7 @@
         <v>2140.4765479984299</v>
       </c>
       <c r="E233">
-        <v>65.199529999999996</v>
+        <v>47.077141282705739</v>
       </c>
       <c r="F233">
         <v>65.030100000000004</v>
@@ -7676,7 +7676,7 @@
         <v>2148.0863389958399</v>
       </c>
       <c r="E234">
-        <v>65.387119999999996</v>
+        <v>47.226878016302976</v>
       </c>
       <c r="F234">
         <v>64.784000000000006</v>
@@ -7699,7 +7699,7 @@
         <v>2157.1972617640999</v>
       </c>
       <c r="E235">
-        <v>65.157420000000002</v>
+        <v>47.137433504112607</v>
       </c>
       <c r="F235">
         <v>64.930099999999996</v>
@@ -7722,7 +7722,7 @@
         <v>2159.5974605925098</v>
       </c>
       <c r="E236">
-        <v>65.166439999999994</v>
+        <v>47.118387239764196</v>
       </c>
       <c r="F236">
         <v>65.105199999999996</v>
@@ -7745,7 +7745,7 @@
         <v>2159.6020368393802</v>
       </c>
       <c r="E237">
-        <v>65.088549999999998</v>
+        <v>47.018396095683585</v>
       </c>
       <c r="F237">
         <v>65.026700000000005</v>
@@ -7768,7 +7768,7 @@
         <v>2154.73903184343</v>
       </c>
       <c r="E238">
-        <v>65.330889999999997</v>
+        <v>47.332645098009124</v>
       </c>
       <c r="F238">
         <v>65.371700000000004</v>
@@ -7791,7 +7791,7 @@
         <v>2142.6334684928502</v>
       </c>
       <c r="E239">
-        <v>65.333449999999999</v>
+        <v>47.302745066351051</v>
       </c>
       <c r="F239">
         <v>65.850899999999996</v>
@@ -7814,7 +7814,7 @@
         <v>2155.97608279938</v>
       </c>
       <c r="E240">
-        <v>65.527630000000002</v>
+        <v>47.361738219027544</v>
       </c>
       <c r="F240">
         <v>66.151799999999994</v>
@@ -7837,7 +7837,7 @@
         <v>2162.5231513117001</v>
       </c>
       <c r="E241">
-        <v>65.910409999999999</v>
+        <v>47.578204111594246</v>
       </c>
       <c r="F241">
         <v>66.543599999999998</v>
@@ -7860,7 +7860,7 @@
         <v>2188.0766968972698</v>
       </c>
       <c r="E242">
-        <v>65.884119999999996</v>
+        <v>47.576282032929917</v>
       </c>
       <c r="F242">
         <v>66.735100000000003</v>
@@ -7883,7 +7883,7 @@
         <v>2165.57918915043</v>
       </c>
       <c r="E243">
-        <v>66.101510000000005</v>
+        <v>47.815510603443556</v>
       </c>
       <c r="F243">
         <v>66.774000000000001</v>
@@ -7906,7 +7906,7 @@
         <v>2169.5148136216299</v>
       </c>
       <c r="E244">
-        <v>66.620170000000002</v>
+        <v>48.127188223284335</v>
       </c>
       <c r="F244">
         <v>67.455200000000005</v>
@@ -7929,7 +7929,7 @@
         <v>2168.1344509219398</v>
       </c>
       <c r="E245">
-        <v>67.051519999999996</v>
+        <v>48.47492504289665</v>
       </c>
       <c r="F245">
         <v>67.854100000000003</v>
@@ -7952,7 +7952,7 @@
         <v>2170.39187569969</v>
       </c>
       <c r="E246">
-        <v>67.399140000000003</v>
+        <v>48.623911633025664</v>
       </c>
       <c r="F246">
         <v>68.166300000000007</v>
@@ -7975,7 +7975,7 @@
         <v>2176.9234719584401</v>
       </c>
       <c r="E247">
-        <v>67.903859999999995</v>
+        <v>49.041807145410417</v>
       </c>
       <c r="F247">
         <v>68.626499999999993</v>
@@ -7998,7 +7998,7 @@
         <v>2177.1793987452502</v>
       </c>
       <c r="E248">
-        <v>68.061660000000003</v>
+        <v>49.025757921712319</v>
       </c>
       <c r="F248">
         <v>68.717799999999997</v>
@@ -8021,7 +8021,7 @@
         <v>2176.16063546034</v>
       </c>
       <c r="E249">
-        <v>68.771000000000001</v>
+        <v>49.662399866763934</v>
       </c>
       <c r="F249">
         <v>69.1785</v>
@@ -8044,7 +8044,7 @@
         <v>2195.06855661691</v>
       </c>
       <c r="E250">
-        <v>69.021960000000007</v>
+        <v>49.788564740485342</v>
       </c>
       <c r="F250">
         <v>69.396100000000004</v>
@@ -8067,7 +8067,7 @@
         <v>2205.2355617887301</v>
       </c>
       <c r="E251">
-        <v>69.534499999999994</v>
+        <v>50.117460120178464</v>
       </c>
       <c r="F251">
         <v>69.954400000000007</v>
@@ -8090,7 +8090,7 @@
         <v>2206.7306615792099</v>
       </c>
       <c r="E252">
-        <v>70.139189999999999</v>
+        <v>50.513384680692546</v>
       </c>
       <c r="F252">
         <v>70.432599999999994</v>
@@ -8113,7 +8113,7 @@
         <v>2216.3080799419299</v>
       </c>
       <c r="E253">
-        <v>70.929060000000007</v>
+        <v>50.941401893518211</v>
       </c>
       <c r="F253">
         <v>71.152299999999997</v>
@@ -8136,7 +8136,7 @@
         <v>2191.4773800555699</v>
       </c>
       <c r="E254">
-        <v>70.683120000000002</v>
+        <v>50.788436745669678</v>
       </c>
       <c r="F254">
         <v>71.273399999999995</v>
@@ -8159,7 +8159,7 @@
         <v>2195.0642422380301</v>
       </c>
       <c r="E255">
-        <v>70.823220000000006</v>
+        <v>50.899522897345086</v>
       </c>
       <c r="F255">
         <v>71.192999999999998</v>
@@ -8182,7 +8182,7 @@
         <v>2187.9416684797902</v>
       </c>
       <c r="E256">
-        <v>70.779039999999995</v>
+        <v>50.979783737157668</v>
       </c>
       <c r="F256">
         <v>71.311300000000003</v>
@@ -8205,7 +8205,7 @@
         <v>2195.3305301547898</v>
       </c>
       <c r="E257">
-        <v>71.098240000000004</v>
+        <v>51.225069712211969</v>
       </c>
       <c r="F257">
         <v>71.188199999999995</v>
@@ -8228,7 +8228,7 @@
         <v>2190.1425380672499</v>
       </c>
       <c r="E258">
-        <v>70.819339999999997</v>
+        <v>51.159921101142679</v>
       </c>
       <c r="F258">
         <v>71.537800000000004</v>
@@ -8251,7 +8251,7 @@
         <v>2225.0772373479799</v>
       </c>
       <c r="E259">
-        <v>71.170810000000003</v>
+        <v>51.260769289809112</v>
       </c>
       <c r="F259">
         <v>71.774900000000002</v>
@@ -8274,7 +8274,7 @@
         <v>2207.80890718508</v>
       </c>
       <c r="E260">
-        <v>71.090500000000006</v>
+        <v>51.166575177138576</v>
       </c>
       <c r="F260">
         <v>71.474800000000002</v>
@@ -8297,7 +8297,7 @@
         <v>2183.77369871265</v>
       </c>
       <c r="E261">
-        <v>71.538480000000007</v>
+        <v>51.637919337936673</v>
       </c>
       <c r="F261">
         <v>72.422300000000007</v>
@@ -8320,7 +8320,7 @@
         <v>2203.29861116658</v>
       </c>
       <c r="E262">
-        <v>71.54795</v>
+        <v>51.488728320505821</v>
       </c>
       <c r="F262">
         <v>72.714399999999998</v>
@@ -8343,7 +8343,7 @@
         <v>2198.9346029286498</v>
       </c>
       <c r="E263">
-        <v>71.546220000000005</v>
+        <v>51.507317627615876</v>
       </c>
       <c r="F263">
         <v>72.586600000000004</v>
@@ -8366,7 +8366,7 @@
         <v>2217.4219325348199</v>
       </c>
       <c r="E264">
-        <v>71.914919999999995</v>
+        <v>51.763975880095821</v>
       </c>
       <c r="F264">
         <v>72.777900000000002</v>
@@ -8389,7 +8389,7 @@
         <v>2192.6310058735198</v>
       </c>
       <c r="E265">
-        <v>72.477369999999993</v>
+        <v>52.065280693999277</v>
       </c>
       <c r="F265">
         <v>73.030500000000004</v>
@@ -8412,7 +8412,7 @@
         <v>2176.5865139367502</v>
       </c>
       <c r="E266">
-        <v>72.337040000000002</v>
+        <v>52.01438111143527</v>
       </c>
       <c r="F266">
         <v>72.612499999999997</v>
@@ -8435,7 +8435,7 @@
         <v>2193.3980455681199</v>
       </c>
       <c r="E267">
-        <v>72.316019999999995</v>
+        <v>52.195268698803886</v>
       </c>
       <c r="F267">
         <v>73.675200000000004</v>
@@ -8458,7 +8458,7 @@
         <v>2177.7714951064399</v>
       </c>
       <c r="E268">
-        <v>72.677149999999997</v>
+        <v>52.157724703039165</v>
       </c>
       <c r="F268">
         <v>73.584999999999994</v>
@@ -8481,7 +8481,7 @@
         <v>2171.1338756660002</v>
       </c>
       <c r="E269">
-        <v>72.969549999999998</v>
+        <v>52.365480858644105</v>
       </c>
       <c r="F269">
         <v>74.3172</v>
@@ -8504,7 +8504,7 @@
         <v>2178.0000910419099</v>
       </c>
       <c r="E270">
-        <v>73.454689999999999</v>
+        <v>52.73683011710775</v>
       </c>
       <c r="F270">
         <v>74.872600000000006</v>
@@ -8527,7 +8527,7 @@
         <v>2190.4727440129</v>
       </c>
       <c r="E271">
-        <v>73.561549999999997</v>
+        <v>52.785678312706217</v>
       </c>
       <c r="F271">
         <v>75.443299999999994</v>
@@ -8550,7 +8550,7 @@
         <v>2181.3377052220098</v>
       </c>
       <c r="E272">
-        <v>73.791219999999996</v>
+        <v>52.995614260506656</v>
       </c>
       <c r="F272">
         <v>75.454899999999995</v>
@@ -8573,7 +8573,7 @@
         <v>2199.2029605473499</v>
       </c>
       <c r="E273">
-        <v>74.097949999999997</v>
+        <v>53.202237011457527</v>
       </c>
       <c r="F273">
         <v>75.841099999999997</v>
@@ -8596,7 +8596,7 @@
         <v>2179.9152605921299</v>
       </c>
       <c r="E274">
-        <v>74.469319999999996</v>
+        <v>53.405690998839233</v>
       </c>
       <c r="F274">
         <v>76.315799999999996</v>
@@ -8619,7 +8619,7 @@
         <v>2182.3459743026501</v>
       </c>
       <c r="E275">
-        <v>74.681929999999994</v>
+        <v>53.52542996973142</v>
       </c>
       <c r="F275">
         <v>76.338399999999993</v>
@@ -8642,7 +8642,7 @@
         <v>2174.9009798050201</v>
       </c>
       <c r="E276">
-        <v>75.021540000000002</v>
+        <v>53.825542873361819</v>
       </c>
       <c r="F276">
         <v>77.039699999999996</v>
@@ -8665,7 +8665,7 @@
         <v>2161.0044260019799</v>
       </c>
       <c r="E277">
-        <v>75.424189999999996</v>
+        <v>53.97794199328883</v>
       </c>
       <c r="F277">
         <v>77.533299999999997</v>
@@ -8688,7 +8688,7 @@
         <v>2187.5259894860301</v>
       </c>
       <c r="E278">
-        <v>75.668899999999994</v>
+        <v>54.394010700076223</v>
       </c>
       <c r="F278">
         <v>77.656199999999998</v>
@@ -8711,7 +8711,7 @@
         <v>2178.5476760756601</v>
       </c>
       <c r="E279">
-        <v>76.092799999999997</v>
+        <v>54.686229376236824</v>
       </c>
       <c r="F279">
         <v>78.583299999999994</v>
@@ -8734,7 +8734,7 @@
         <v>2198.6877492643798</v>
       </c>
       <c r="E280">
-        <v>76.708240000000004</v>
+        <v>54.892620517025684</v>
       </c>
       <c r="F280">
         <v>79.081999999999994</v>
@@ -8757,7 +8757,7 @@
         <v>2195.6443868747501</v>
       </c>
       <c r="E281">
-        <v>77.120630000000006</v>
+        <v>55.375861574157</v>
       </c>
       <c r="F281">
         <v>79.174700000000001</v>
@@ -8780,7 +8780,7 @@
         <v>2190.0997548006999</v>
       </c>
       <c r="E282">
-        <v>77.291240000000002</v>
+        <v>55.431315149067885</v>
       </c>
       <c r="F282">
         <v>79.613299999999995</v>
@@ -8803,7 +8803,7 @@
         <v>2166.6806399888501</v>
       </c>
       <c r="E283">
-        <v>77.985669999999999</v>
+        <v>55.721999641205464</v>
       </c>
       <c r="F283">
         <v>79.979200000000006</v>
@@ -8826,7 +8826,7 @@
         <v>2160.84805471562</v>
       </c>
       <c r="E284">
-        <v>78.268320000000003</v>
+        <v>56.022133048001656</v>
       </c>
       <c r="F284">
         <v>80.662400000000005</v>
@@ -8849,7 +8849,7 @@
         <v>2148.2703787260698</v>
       </c>
       <c r="E285">
-        <v>78.614369999999994</v>
+        <v>56.230038040997378</v>
       </c>
       <c r="F285">
         <v>81.469399999999993</v>
@@ -8872,7 +8872,7 @@
         <v>2159.63985244386</v>
       </c>
       <c r="E286">
-        <v>79.010069999999999</v>
+        <v>56.427317621200523</v>
       </c>
       <c r="F286">
         <v>82.215599999999995</v>
@@ -8895,7 +8895,7 @@
         <v>2164.3210325459299</v>
       </c>
       <c r="E287">
-        <v>79.543869999999998</v>
+        <v>56.781111131970171</v>
       </c>
       <c r="F287">
         <v>82.944599999999994</v>
@@ -8918,7 +8918,7 @@
         <v>2205.2112418352499</v>
       </c>
       <c r="E288">
-        <v>79.424589999999995</v>
+        <v>56.603495871936751</v>
       </c>
       <c r="F288">
         <v>83.597800000000007</v>
@@ -8941,7 +8941,7 @@
         <v>2200.5905745054201</v>
       </c>
       <c r="E289">
-        <v>79.373779999999996</v>
+        <v>56.46516523775783</v>
       </c>
       <c r="F289">
         <v>83.953800000000001</v>
@@ -8964,7 +8964,7 @@
         <v>2200.5914444854702</v>
       </c>
       <c r="E290">
-        <v>79.205039999999997</v>
+        <v>56.690420745208243</v>
       </c>
       <c r="F290">
         <v>84.321799999999996</v>
@@ -8987,7 +8987,7 @@
         <v>2192.6113260557599</v>
       </c>
       <c r="E291">
-        <v>79.827640000000002</v>
+        <v>56.691056611553655</v>
       </c>
       <c r="F291">
         <v>84.458299999999994</v>
@@ -9010,7 +9010,7 @@
         <v>2179.89371701448</v>
       </c>
       <c r="E292">
-        <v>79.579729999999998</v>
+        <v>56.619742127711184</v>
       </c>
       <c r="F292">
         <v>84.488</v>
@@ -9033,7 +9033,7 @@
         <v>2210.81895718445</v>
       </c>
       <c r="E293">
-        <v>79.520430000000005</v>
+        <v>56.688698423933367</v>
       </c>
       <c r="F293">
         <v>84.777900000000002</v>
@@ -9056,7 +9056,7 @@
         <v>2238.4985034684901</v>
       </c>
       <c r="E294">
-        <v>79.713909999999998</v>
+        <v>56.676601464596146</v>
       </c>
       <c r="F294">
         <v>85.336699999999993</v>
@@ -9079,7 +9079,7 @@
         <v>2203.5178644779198</v>
       </c>
       <c r="E295">
-        <v>79.553420000000003</v>
+        <v>56.617076525473934</v>
       </c>
       <c r="F295">
         <v>84.824799999999996</v>
@@ -9102,7 +9102,7 @@
         <v>2207.4636441743801</v>
       </c>
       <c r="E296">
-        <v>79.470759999999999</v>
+        <v>56.605643605474363</v>
       </c>
       <c r="F296">
         <v>84.498599999999996</v>
@@ -9125,7 +9125,7 @@
         <v>2210.1546783849599</v>
       </c>
       <c r="E297">
-        <v>79.742620000000002</v>
+        <v>56.435061173531551</v>
       </c>
       <c r="F297">
         <v>86.248000000000005</v>
@@ -9148,7 +9148,7 @@
         <v>2196.4450583478001</v>
       </c>
       <c r="E298">
-        <v>79.930279999999996</v>
+        <v>56.73863341727801</v>
       </c>
       <c r="F298">
         <v>86.202100000000002</v>
@@ -9171,7 +9171,7 @@
         <v>2229.3770957472102</v>
       </c>
       <c r="E299">
-        <v>80.166780000000003</v>
+        <v>56.846789888413539</v>
       </c>
       <c r="F299">
         <v>86.791399999999996</v>
@@ -9194,7 +9194,7 @@
         <v>2227.4221090548399</v>
       </c>
       <c r="E300">
-        <v>80.297160000000005</v>
+        <v>56.801597180763601</v>
       </c>
       <c r="F300">
         <v>86.7256</v>
@@ -9217,7 +9217,7 @@
         <v>2223.0546583208102</v>
       </c>
       <c r="E301">
-        <v>80.201239999999999</v>
+        <v>56.843432769615788</v>
       </c>
       <c r="F301">
         <v>87.118499999999997</v>
@@ -9240,7 +9240,7 @@
         <v>2248.8612603091701</v>
       </c>
       <c r="E302">
-        <v>80.96566</v>
+        <v>57.195853513495209</v>
       </c>
       <c r="F302">
         <v>87.494900000000001</v>
@@ -9263,7 +9263,7 @@
         <v>2219.0419221800298</v>
       </c>
       <c r="E303">
-        <v>80.499979999999994</v>
+        <v>57.249799847201004</v>
       </c>
       <c r="F303">
         <v>88.027000000000001</v>
@@ -9286,7 +9286,7 @@
         <v>2220.9802384823101</v>
       </c>
       <c r="E304">
-        <v>81.148219999999995</v>
+        <v>57.488104969393156</v>
       </c>
       <c r="F304">
         <v>88.226699999999994</v>
@@ -9309,7 +9309,7 @@
         <v>2211.29806813605</v>
       </c>
       <c r="E305">
-        <v>81.197329999999994</v>
+        <v>57.438058997911092</v>
       </c>
       <c r="F305">
         <v>88.429500000000004</v>
@@ -9332,7 +9332,7 @@
         <v>2220.3606778078602</v>
       </c>
       <c r="E306">
-        <v>81.951719999999995</v>
+        <v>57.787851068640173</v>
       </c>
       <c r="F306">
         <v>88.988600000000005</v>
@@ -9355,7 +9355,7 @@
         <v>2219.36637399451</v>
       </c>
       <c r="E307">
-        <v>82.002560000000003</v>
+        <v>57.926167518173465</v>
       </c>
       <c r="F307">
         <v>88.918800000000005</v>
@@ -9378,7 +9378,7 @@
         <v>2231.4566428736698</v>
       </c>
       <c r="E308">
-        <v>82.572010000000006</v>
+        <v>58.326806371738591</v>
       </c>
       <c r="F308">
         <v>89.433300000000003</v>
@@ -9401,7 +9401,7 @@
         <v>2217.3170949144501</v>
       </c>
       <c r="E309">
-        <v>82.928759999999997</v>
+        <v>58.499570956228624</v>
       </c>
       <c r="F309">
         <v>89.792400000000001</v>
@@ -9424,7 +9424,7 @@
         <v>2203.5689150128801</v>
       </c>
       <c r="E310">
-        <v>83.467060000000004</v>
+        <v>58.925260391984004</v>
       </c>
       <c r="F310">
         <v>89.429900000000004</v>
@@ -9447,7 +9447,7 @@
         <v>2195.9609182145</v>
       </c>
       <c r="E311">
-        <v>83.950220000000002</v>
+        <v>59.196527940764263</v>
       </c>
       <c r="F311">
         <v>90.522999999999996</v>
@@ -9470,7 +9470,7 @@
         <v>2183.2736513332902</v>
       </c>
       <c r="E312">
-        <v>84.743189999999998</v>
+        <v>59.776831909339265</v>
       </c>
       <c r="F312">
         <v>90.961799999999997</v>
@@ -9493,7 +9493,7 @@
         <v>2178.7993225514501</v>
       </c>
       <c r="E313">
-        <v>85.532560000000004</v>
+        <v>60.081113769978217</v>
       </c>
       <c r="F313">
         <v>91.663399999999996</v>
@@ -9516,7 +9516,7 @@
         <v>2170.8562407787399</v>
       </c>
       <c r="E314">
-        <v>85.323189999999997</v>
+        <v>60.085637296745098</v>
       </c>
       <c r="F314">
         <v>91.537999999999997</v>
@@ -9539,7 +9539,7 @@
         <v>2175.6147332298801</v>
       </c>
       <c r="E315">
-        <v>85.634529999999998</v>
+        <v>60.628344832162497</v>
       </c>
       <c r="F315">
         <v>91.823899999999995</v>
@@ -9562,7 +9562,7 @@
         <v>2156.6293973933698</v>
       </c>
       <c r="E316">
-        <v>86.065070000000006</v>
+        <v>60.977107535555199</v>
       </c>
       <c r="F316">
         <v>92.150400000000005</v>
@@ -9585,7 +9585,7 @@
         <v>2154.8446319217401</v>
       </c>
       <c r="E317">
-        <v>86.918080000000003</v>
+        <v>61.439571407023202</v>
       </c>
       <c r="F317">
         <v>92.698899999999995</v>
@@ -9608,7 +9608,7 @@
         <v>2142.4075486001502</v>
       </c>
       <c r="E318">
-        <v>87.355999999999995</v>
+        <v>61.940660732590601</v>
       </c>
       <c r="F318">
         <v>92.9499</v>
@@ -9631,7 +9631,7 @@
         <v>2153.0586370187002</v>
       </c>
       <c r="E319">
-        <v>87.443349999999995</v>
+        <v>61.993848197007701</v>
       </c>
       <c r="F319">
         <v>92.986199999999997</v>
@@ -9654,7 +9654,7 @@
         <v>2157.1370711303398</v>
       </c>
       <c r="E320">
-        <v>87.759680000000003</v>
+        <v>62.213566214833499</v>
       </c>
       <c r="F320">
         <v>92.8048</v>
@@ -9677,7 +9677,7 @@
         <v>2163.1070358050401</v>
       </c>
       <c r="E321">
-        <v>88.185360000000003</v>
+        <v>62.513454454148402</v>
       </c>
       <c r="F321">
         <v>92.552099999999996</v>
@@ -9700,7 +9700,7 @@
         <v>2165.6827358274199</v>
       </c>
       <c r="E322">
-        <v>87.989270000000005</v>
+        <v>62.438279251471997</v>
       </c>
       <c r="F322">
         <v>92.979200000000006</v>
@@ -9723,7 +9723,7 @@
         <v>2152.34612675574</v>
       </c>
       <c r="E323">
-        <v>88.280940000000001</v>
+        <v>62.689950006007102</v>
       </c>
       <c r="F323">
         <v>92.617900000000006</v>
@@ -9746,7 +9746,7 @@
         <v>2159.4386929238399</v>
       </c>
       <c r="E324">
-        <v>88.602180000000004</v>
+        <v>62.991155484238902</v>
       </c>
       <c r="F324">
         <v>92.643799999999999</v>
@@ -9769,7 +9769,7 @@
         <v>2180.6370177005301</v>
       </c>
       <c r="E325">
-        <v>88.918909999999997</v>
+        <v>62.863893260192</v>
       </c>
       <c r="F325">
         <v>92.341499999999996</v>
@@ -9792,7 +9792,7 @@
         <v>2149.3658438392499</v>
       </c>
       <c r="E326">
-        <v>87.723500000000001</v>
+        <v>62.446684009723398</v>
       </c>
       <c r="F326">
         <v>91.902000000000001</v>
@@ -9815,7 +9815,7 @@
         <v>2113.8078804081301</v>
       </c>
       <c r="E327">
-        <v>88.453180000000003</v>
+        <v>62.375893366530903</v>
       </c>
       <c r="F327">
         <v>91.303399999999996</v>
@@ -9838,7 +9838,7 @@
         <v>2154.6656920932301</v>
       </c>
       <c r="E328">
-        <v>87.630679999999998</v>
+        <v>62.1350803732633</v>
       </c>
       <c r="F328">
         <v>91.116200000000006</v>
@@ -9861,7 +9861,7 @@
         <v>2178.8741320292102</v>
       </c>
       <c r="E329">
-        <v>87.244709999999998</v>
+        <v>61.684853835451101</v>
       </c>
       <c r="F329">
         <v>90.789100000000005</v>
@@ -9884,7 +9884,7 @@
         <v>2162.8974506794598</v>
       </c>
       <c r="E330">
-        <v>87.226910000000004</v>
+        <v>61.5184945758296</v>
       </c>
       <c r="F330">
         <v>90.355500000000006</v>
@@ -9907,7 +9907,7 @@
         <v>2117.3437188552598</v>
       </c>
       <c r="E331">
-        <v>87.014679999999998</v>
+        <v>61.222404030692999</v>
       </c>
       <c r="F331">
         <v>89.878399999999999</v>
@@ -9930,7 +9930,7 @@
         <v>2139.7228614330602</v>
       </c>
       <c r="E332">
-        <v>86.409419999999997</v>
+        <v>60.8502058381317</v>
       </c>
       <c r="F332">
         <v>89.302800000000005</v>
@@ -9953,7 +9953,7 @@
         <v>2152.4458184642799</v>
       </c>
       <c r="E333">
-        <v>86.883610000000004</v>
+        <v>61.257155828536398</v>
       </c>
       <c r="F333">
         <v>89.200299999999999</v>
@@ -9976,7 +9976,7 @@
         <v>2158.6244137918802</v>
       </c>
       <c r="E334">
-        <v>86.290890000000005</v>
+        <v>60.703501331649001</v>
       </c>
       <c r="F334">
         <v>88.748500000000007</v>
@@ -9999,7 +9999,7 @@
         <v>2161.0858804304999</v>
       </c>
       <c r="E335">
-        <v>86.007919999999999</v>
+        <v>60.416934782422899</v>
       </c>
       <c r="F335">
         <v>88.505200000000002</v>
@@ -10022,7 +10022,7 @@
         <v>2160.5675622494</v>
       </c>
       <c r="E336">
-        <v>85.776430000000005</v>
+        <v>60.185635408937799</v>
       </c>
       <c r="F336">
         <v>87.97</v>
@@ -10045,7 +10045,7 @@
         <v>2172.6545006773299</v>
       </c>
       <c r="E337">
-        <v>85.842770000000002</v>
+        <v>60.034883833470801</v>
       </c>
       <c r="F337">
         <v>87.932400000000001</v>
@@ -10068,7 +10068,7 @@
         <v>2186.7422872437501</v>
       </c>
       <c r="E338">
-        <v>86.752880000000005</v>
+        <v>60.526296387477799</v>
       </c>
       <c r="F338">
         <v>88.517600000000002</v>
@@ -10091,7 +10091,7 @@
         <v>2214.7571554569599</v>
       </c>
       <c r="E339">
-        <v>86.518349999999998</v>
+        <v>60.586237776467897</v>
       </c>
       <c r="F339">
         <v>88.527799999999999</v>
@@ -10114,7 +10114,7 @@
         <v>2200.4284296148699</v>
       </c>
       <c r="E340">
-        <v>87.361170000000001</v>
+        <v>60.8930094523839</v>
       </c>
       <c r="F340">
         <v>89.168599999999998</v>
@@ -10137,7 +10137,7 @@
         <v>2170.5424615449201</v>
       </c>
       <c r="E341">
-        <v>87.974559999999997</v>
+        <v>61.177350522188398</v>
       </c>
       <c r="F341">
         <v>89.603999999999999</v>
@@ -10160,7 +10160,7 @@
         <v>2193.6417587266101</v>
       </c>
       <c r="E342">
-        <v>88.308300000000003</v>
+        <v>61.646507144028398</v>
       </c>
       <c r="F342">
         <v>89.963999999999999</v>
@@ -10183,7 +10183,7 @@
         <v>2203.3106102951201</v>
       </c>
       <c r="E343">
-        <v>88.481049999999996</v>
+        <v>61.665499178217999</v>
       </c>
       <c r="F343">
         <v>90.706100000000006</v>
@@ -10206,7 +10206,7 @@
         <v>2189.7930890934399</v>
       </c>
       <c r="E344">
-        <v>88.838800000000006</v>
+        <v>62.098521274906503</v>
       </c>
       <c r="F344">
         <v>90.676900000000003</v>
@@ -10229,7 +10229,7 @@
         <v>2195.2773078457299</v>
       </c>
       <c r="E345">
-        <v>89.144130000000004</v>
+        <v>62.228694422252097</v>
       </c>
       <c r="F345">
         <v>90.5762</v>
@@ -10252,7 +10252,7 @@
         <v>2157.28631922155</v>
       </c>
       <c r="E346">
-        <v>89.408810000000003</v>
+        <v>62.3842943631509</v>
       </c>
       <c r="F346">
         <v>90.653099999999995</v>
@@ -10275,7 +10275,7 @@
         <v>2203.7725483568202</v>
       </c>
       <c r="E347">
-        <v>89.506450000000001</v>
+        <v>62.597744732476002</v>
       </c>
       <c r="F347">
         <v>90.464299999999994</v>
@@ -10298,7 +10298,7 @@
         <v>2207.63788825552</v>
       </c>
       <c r="E348">
-        <v>89.820520000000002</v>
+        <v>62.865060731244903</v>
       </c>
       <c r="F348">
         <v>90.971100000000007</v>
@@ -10321,7 +10321,7 @@
         <v>2207.4986779843898</v>
       </c>
       <c r="E349">
-        <v>89.514849999999996</v>
+        <v>62.084083677543099</v>
       </c>
       <c r="F349">
         <v>90.465199999999996</v>
@@ -10344,7 +10344,7 @@
         <v>2220.5258507312701</v>
       </c>
       <c r="E350">
-        <v>90.516170000000002</v>
+        <v>63.305130654930302</v>
       </c>
       <c r="F350">
         <v>91.236099999999993</v>
@@ -10367,7 +10367,7 @@
         <v>2216.0744713572299</v>
       </c>
       <c r="E351">
-        <v>90.493579999999994</v>
+        <v>63.601986823306902</v>
       </c>
       <c r="F351">
         <v>91.344499999999996</v>
@@ -10390,7 +10390,7 @@
         <v>2240.9053091176202</v>
       </c>
       <c r="E352">
-        <v>90.541089999999997</v>
+        <v>63.832252285787</v>
       </c>
       <c r="F352">
         <v>91.104399999999998</v>
@@ -10413,7 +10413,7 @@
         <v>2242.2133344307499</v>
       </c>
       <c r="E353">
-        <v>90.274919999999995</v>
+        <v>63.6192767796109</v>
       </c>
       <c r="F353">
         <v>90.561700000000002</v>
@@ -10436,7 +10436,7 @@
         <v>2229.72490001297</v>
       </c>
       <c r="E354">
-        <v>90.132419999999996</v>
+        <v>63.526777986336697</v>
       </c>
       <c r="F354">
         <v>90.537000000000006</v>
@@ -10459,7 +10459,7 @@
         <v>2247.8630530001201</v>
       </c>
       <c r="E355">
-        <v>90.549040000000005</v>
+        <v>63.686115395015598</v>
       </c>
       <c r="F355">
         <v>90.652699999999996</v>
@@ -10482,7 +10482,7 @@
         <v>2273.6396867681001</v>
       </c>
       <c r="E356">
-        <v>91.219329999999999</v>
+        <v>64.096592979543402</v>
       </c>
       <c r="F356">
         <v>91.118499999999997</v>
@@ -10505,7 +10505,7 @@
         <v>2281.5909954422</v>
       </c>
       <c r="E357">
-        <v>91.101550000000003</v>
+        <v>64.113445301756997</v>
       </c>
       <c r="F357">
         <v>90.919700000000006</v>
@@ -10528,7 +10528,7 @@
         <v>2303.9354548092001</v>
       </c>
       <c r="E358">
-        <v>91.965869999999995</v>
+        <v>64.502241107290502</v>
       </c>
       <c r="F358">
         <v>91.505899999999997</v>
@@ -10551,7 +10551,7 @@
         <v>2302.4539815002599</v>
       </c>
       <c r="E359">
-        <v>92.80256</v>
+        <v>65.401473190605998</v>
       </c>
       <c r="F359">
         <v>91.618600000000001</v>
@@ -10574,7 +10574,7 @@
         <v>2308.3930929426901</v>
       </c>
       <c r="E360">
-        <v>93.109260000000006</v>
+        <v>65.390161240492901</v>
       </c>
       <c r="F360">
         <v>92.232900000000001</v>
@@ -10597,7 +10597,7 @@
         <v>2315.3839751594101</v>
       </c>
       <c r="E361">
-        <v>93.794749999999993</v>
+        <v>66.058331194205195</v>
       </c>
       <c r="F361">
         <v>92.260199999999998</v>
@@ -10620,7 +10620,7 @@
         <v>2319.32594417682</v>
       </c>
       <c r="E362">
-        <v>93.643230000000003</v>
+        <v>66.164129547625393</v>
       </c>
       <c r="F362">
         <v>92.400599999999997</v>
@@ -10643,7 +10643,7 @@
         <v>2334.85873076599</v>
       </c>
       <c r="E363">
-        <v>94.864930000000001</v>
+        <v>66.607441952306203</v>
       </c>
       <c r="F363">
         <v>92.957999999999998</v>
@@ -10666,7 +10666,7 @@
         <v>2326.57908435737</v>
       </c>
       <c r="E364">
-        <v>94.842579999999998</v>
+        <v>66.688156334301794</v>
       </c>
       <c r="F364">
         <v>92.586100000000002</v>
@@ -10689,7 +10689,7 @@
         <v>2343.8832265390602</v>
       </c>
       <c r="E365">
-        <v>95.461780000000005</v>
+        <v>67.060617736036505</v>
       </c>
       <c r="F365">
         <v>92.93</v>
@@ -10712,7 +10712,7 @@
         <v>2353.5361131027198</v>
       </c>
       <c r="E366">
-        <v>95.780320000000003</v>
+        <v>67.388419743750404</v>
       </c>
       <c r="F366">
         <v>93.601299999999995</v>
@@ -10735,7 +10735,7 @@
         <v>2359.3582335709302</v>
       </c>
       <c r="E367">
-        <v>95.707149999999999</v>
+        <v>67.626056188494204</v>
       </c>
       <c r="F367">
         <v>92.870999999999995</v>
@@ -10758,7 +10758,7 @@
         <v>2349.9752558068099</v>
       </c>
       <c r="E368">
-        <v>96.365390000000005</v>
+        <v>67.901606110743302</v>
       </c>
       <c r="F368">
         <v>93.564899999999994</v>
@@ -10781,7 +10781,7 @@
         <v>2322.16729310646</v>
       </c>
       <c r="E369">
-        <v>96.41619</v>
+        <v>67.663400081664705</v>
       </c>
       <c r="F369">
         <v>93.627700000000004</v>
@@ -10804,7 +10804,7 @@
         <v>2338.9698542686201</v>
       </c>
       <c r="E370">
-        <v>96.805130000000005</v>
+        <v>68.1839927516274</v>
       </c>
       <c r="F370">
         <v>93.746700000000004</v>
@@ -10827,7 +10827,7 @@
         <v>2359.4495494002499</v>
       </c>
       <c r="E371">
-        <v>97.240899999999996</v>
+        <v>68.525738371692597</v>
       </c>
       <c r="F371">
         <v>94.546499999999995</v>
@@ -10850,7 +10850,7 @@
         <v>2395.6512599327798</v>
       </c>
       <c r="E372">
-        <v>97.384119999999996</v>
+        <v>68.334086358848793</v>
       </c>
       <c r="F372">
         <v>94.781300000000002</v>
@@ -10873,7 +10873,7 @@
         <v>2377.5271348431102</v>
       </c>
       <c r="E373">
-        <v>97.728980000000007</v>
+        <v>68.733716014104999</v>
       </c>
       <c r="F373">
         <v>95.536500000000004</v>
@@ -10896,7 +10896,7 @@
         <v>2374.0061100610201</v>
       </c>
       <c r="E374">
-        <v>98.488140000000001</v>
+        <v>69.299118088304695</v>
       </c>
       <c r="F374">
         <v>95.880099999999999</v>
@@ -10919,7 +10919,7 @@
         <v>2367.6335719599401</v>
       </c>
       <c r="E375">
-        <v>98.547129999999996</v>
+        <v>69.468645553066594</v>
       </c>
       <c r="F375">
         <v>96.576099999999997</v>
@@ -10942,7 +10942,7 @@
         <v>2398.83387603551</v>
       </c>
       <c r="E376">
-        <v>98.779730000000001</v>
+        <v>69.567219779854099</v>
       </c>
       <c r="F376">
         <v>96.445599999999999</v>
@@ -10965,7 +10965,7 @@
         <v>2405.0889320256701</v>
       </c>
       <c r="E377">
-        <v>99.500789999999995</v>
+        <v>70.158865809106302</v>
       </c>
       <c r="F377">
         <v>96.653199999999998</v>
@@ -10988,7 +10988,7 @@
         <v>2430.9917871614798</v>
       </c>
       <c r="E378">
-        <v>99.127110000000002</v>
+        <v>70.013956828424298</v>
       </c>
       <c r="F378">
         <v>96.740200000000002</v>
@@ -11011,7 +11011,7 @@
         <v>2412.3787455378201</v>
       </c>
       <c r="E379">
-        <v>99.791139999999999</v>
+        <v>70.135450086424598</v>
       </c>
       <c r="F379">
         <v>97.175299999999993</v>
@@ -11034,7 +11034,7 @@
         <v>2429.4725827791599</v>
       </c>
       <c r="E380">
-        <v>99.880129999999994</v>
+        <v>70.242722947283994</v>
       </c>
       <c r="F380">
         <v>96.867599999999996</v>
@@ -11057,7 +11057,7 @@
         <v>2439.5060412606299</v>
       </c>
       <c r="E381">
-        <v>100.1999</v>
+        <v>70.563498169035398</v>
       </c>
       <c r="F381">
         <v>97.183300000000003</v>
@@ -11080,7 +11080,7 @@
         <v>2448.18663474287</v>
       </c>
       <c r="E382">
-        <v>100.28400000000001</v>
+        <v>70.553180077957407</v>
       </c>
       <c r="F382">
         <v>95.3005</v>
@@ -11103,7 +11103,7 @@
         <v>2452.59046426536</v>
       </c>
       <c r="E383">
-        <v>100.8638</v>
+        <v>70.952316468936999</v>
       </c>
       <c r="F383">
         <v>96.4572</v>
@@ -11126,7 +11126,7 @@
         <v>2446.6012322953502</v>
       </c>
       <c r="E384">
-        <v>101.93819999999999</v>
+        <v>71.654367770825601</v>
       </c>
       <c r="F384">
         <v>97.541399999999996</v>
@@ -11149,7 +11149,7 @@
         <v>2455.2766162655698</v>
       </c>
       <c r="E385">
-        <v>102.6133</v>
+        <v>72.001816484506193</v>
       </c>
       <c r="F385">
         <v>98.045199999999994</v>
@@ -11172,7 +11172,7 @@
         <v>2429.6622814482698</v>
       </c>
       <c r="E386">
-        <v>102.4846</v>
+        <v>72.291982186702</v>
       </c>
       <c r="F386">
         <v>98.1999</v>
@@ -11195,7 +11195,7 @@
         <v>2451.50344605694</v>
       </c>
       <c r="E387">
-        <v>103.3763</v>
+        <v>72.431577096132102</v>
       </c>
       <c r="F387">
         <v>98.241299999999995</v>
@@ -11218,7 +11218,7 @@
         <v>2450.9999360153602</v>
       </c>
       <c r="E388">
-        <v>103.7015</v>
+        <v>72.813048944618501</v>
       </c>
       <c r="F388">
         <v>98.462800000000001</v>
@@ -11241,7 +11241,7 @@
         <v>2456.2342274091202</v>
       </c>
       <c r="E389">
-        <v>104.1263</v>
+        <v>72.8566714134612</v>
       </c>
       <c r="F389">
         <v>98.761799999999994</v>
@@ -11264,7 +11264,7 @@
         <v>2450.4826880318901</v>
       </c>
       <c r="E390">
-        <v>104.83110000000001</v>
+        <v>73.251420586531097</v>
       </c>
       <c r="F390">
         <v>98.786900000000003</v>
@@ -11287,7 +11287,7 @@
         <v>2449.5539408999298</v>
       </c>
       <c r="E391">
-        <v>105.1742</v>
+        <v>73.546263134128395</v>
       </c>
       <c r="F391">
         <v>99.099699999999999</v>
@@ -11310,7 +11310,7 @@
         <v>2460.0100358405598</v>
       </c>
       <c r="E392">
-        <v>105.5162</v>
+        <v>73.691919403971497</v>
       </c>
       <c r="F392">
         <v>99.048900000000003</v>
@@ -11333,7 +11333,7 @@
         <v>2461.9437661604402</v>
       </c>
       <c r="E393">
-        <v>105.93040000000001</v>
+        <v>73.960333822904005</v>
       </c>
       <c r="F393">
         <v>99.483599999999996</v>
@@ -11356,7 +11356,7 @@
         <v>2464.4744165145498</v>
       </c>
       <c r="E394">
-        <v>106.3349</v>
+        <v>74.171316821853296</v>
       </c>
       <c r="F394">
         <v>99.318299999999994</v>
@@ -11379,7 +11379,7 @@
         <v>2478.5099645486098</v>
       </c>
       <c r="E395">
-        <v>106.608</v>
+        <v>74.210685996498</v>
       </c>
       <c r="F395">
         <v>99.204400000000007</v>
@@ -11402,7 +11402,7 @@
         <v>2496.5263997421298</v>
       </c>
       <c r="E396">
-        <v>107.87860000000001</v>
+        <v>74.843019773926798</v>
       </c>
       <c r="F396">
         <v>99.162700000000001</v>
@@ -11425,7 +11425,7 @@
         <v>2461.23379547594</v>
       </c>
       <c r="E397">
-        <v>108.57129999999999</v>
+        <v>75.327168887619095</v>
       </c>
       <c r="F397">
         <v>100.1735</v>
@@ -11448,7 +11448,7 @@
         <v>2462.0737481338901</v>
       </c>
       <c r="E398">
-        <v>109.2043</v>
+        <v>75.570711379389294</v>
       </c>
       <c r="F398">
         <v>99.834599999999995</v>
@@ -11471,7 +11471,7 @@
         <v>2475.1729695165</v>
       </c>
       <c r="E399">
-        <v>109.4357</v>
+        <v>75.877403068157903</v>
       </c>
       <c r="F399">
         <v>100.7753</v>
@@ -11494,7 +11494,7 @@
         <v>2458.1419686204499</v>
       </c>
       <c r="E400">
-        <v>110.15179999999999</v>
+        <v>76.255217184458203</v>
       </c>
       <c r="F400">
         <v>100.9547</v>
@@ -11517,7 +11517,7 @@
         <v>2465.3750181661699</v>
       </c>
       <c r="E401">
-        <v>110.30110000000001</v>
+        <v>76.304364034564301</v>
       </c>
       <c r="F401">
         <v>101.63339999999999</v>
@@ -11540,7 +11540,7 @@
         <v>2493.47837597436</v>
       </c>
       <c r="E402">
-        <v>111.31270000000001</v>
+        <v>76.878593229321396</v>
       </c>
       <c r="F402">
         <v>101.7306</v>
@@ -11563,7 +11563,7 @@
         <v>2499.8042190176702</v>
       </c>
       <c r="E403">
-        <v>111.4787</v>
+        <v>76.968857080055201</v>
       </c>
       <c r="F403">
         <v>101.7893</v>
@@ -11586,7 +11586,7 @@
         <v>2484.8246372942399</v>
       </c>
       <c r="E404">
-        <v>111.97799999999999</v>
+        <v>77.3264953985326</v>
       </c>
       <c r="F404">
         <v>101.66719999999999</v>
@@ -11609,7 +11609,7 @@
         <v>2467.4589474690601</v>
       </c>
       <c r="E405">
-        <v>112.4597</v>
+        <v>77.815726516273699</v>
       </c>
       <c r="F405">
         <v>101.863</v>
@@ -11632,7 +11632,7 @@
         <v>2461.8478611237601</v>
       </c>
       <c r="E406">
-        <v>112.5314</v>
+        <v>77.860779069356894</v>
       </c>
       <c r="F406">
         <v>102.0894</v>
@@ -11655,7 +11655,7 @@
         <v>2439.0808406302199</v>
       </c>
       <c r="E407">
-        <v>113.2724</v>
+        <v>78.543378155361395</v>
       </c>
       <c r="F407">
         <v>101.8015</v>
@@ -11678,7 +11678,7 @@
         <v>2430.2708286769398</v>
       </c>
       <c r="E408">
-        <v>113.74290000000001</v>
+        <v>78.645748140826996</v>
       </c>
       <c r="F408">
         <v>102.3446</v>
@@ -11701,7 +11701,7 @@
         <v>2446.9521726503499</v>
       </c>
       <c r="E409">
-        <v>113.9851</v>
+        <v>79.099013662542603</v>
       </c>
       <c r="F409">
         <v>102.38030000000001</v>
@@ -11724,7 +11724,7 @@
         <v>2449.6875876582699</v>
       </c>
       <c r="E410">
-        <v>115.6785</v>
+        <v>79.549663715232398</v>
       </c>
       <c r="F410">
         <v>102.2448</v>
@@ -11747,7 +11747,7 @@
         <v>2433.8796380693898</v>
       </c>
       <c r="E411">
-        <v>115.05029999999999</v>
+        <v>79.626783133485404</v>
       </c>
       <c r="F411">
         <v>101.8438</v>
@@ -11770,7 +11770,7 @@
         <v>2471.8948166566402</v>
       </c>
       <c r="E412">
-        <v>114.6896</v>
+        <v>79.316304330726794</v>
       </c>
       <c r="F412">
         <v>101.53360000000001</v>
@@ -11793,7 +11793,7 @@
         <v>2450.0974405260399</v>
       </c>
       <c r="E413">
-        <v>115.1825</v>
+        <v>79.561505385404203</v>
       </c>
       <c r="F413">
         <v>100.8785</v>
@@ -11816,7 +11816,7 @@
         <v>2435.4743408917702</v>
       </c>
       <c r="E414">
-        <v>114.1686</v>
+        <v>79.015975329084299</v>
       </c>
       <c r="F414">
         <v>100.26739999999999</v>
@@ -11839,7 +11839,7 @@
         <v>2432.2538318546999</v>
       </c>
       <c r="E415">
-        <v>114.4692</v>
+        <v>78.915733710166194</v>
       </c>
       <c r="F415">
         <v>100.0335</v>
@@ -11862,7 +11862,7 @@
         <v>2464.8929037032499</v>
       </c>
       <c r="E416">
-        <v>113.70659999999999</v>
+        <v>78.660842254414007</v>
       </c>
       <c r="F416">
         <v>99.676000000000002</v>
@@ -11885,7 +11885,7 @@
         <v>2479.3648170033898</v>
       </c>
       <c r="E417">
-        <v>112.6833</v>
+        <v>77.985948171417803</v>
       </c>
       <c r="F417">
         <v>98.111099999999993</v>
@@ -11908,7 +11908,7 @@
         <v>2489.9626028247799</v>
       </c>
       <c r="E418">
-        <v>111.54130000000001</v>
+        <v>77.128655980757003</v>
       </c>
       <c r="F418">
         <v>93.789500000000004</v>
@@ -11931,7 +11931,7 @@
         <v>2498.4204337624501</v>
       </c>
       <c r="E419">
-        <v>109.8184</v>
+        <v>76.252398335500203</v>
       </c>
       <c r="F419">
         <v>94.721900000000005</v>
@@ -11954,7 +11954,7 @@
         <v>2505.1183624312798</v>
       </c>
       <c r="E420">
-        <v>106.8489</v>
+        <v>73.968431446946497</v>
       </c>
       <c r="F420">
         <v>93.471500000000006</v>
@@ -11977,7 +11977,7 @@
         <v>2523.6458284939899</v>
       </c>
       <c r="E421">
-        <v>103.4164</v>
+        <v>71.706714797044398</v>
       </c>
       <c r="F421">
         <v>90.835700000000003</v>
@@ -12000,7 +12000,7 @@
         <v>2535.4603304556099</v>
       </c>
       <c r="E422">
-        <v>100.49039999999999</v>
+        <v>69.669664539877004</v>
       </c>
       <c r="F422">
         <v>88.57</v>
@@ -12023,7 +12023,7 @@
         <v>2531.9339284892999</v>
       </c>
       <c r="E423">
-        <v>101.3404</v>
+        <v>69.423809179835104</v>
       </c>
       <c r="F423">
         <v>88.031000000000006</v>
@@ -12046,7 +12046,7 @@
         <v>2525.6764987443298</v>
       </c>
       <c r="E424">
-        <v>100.8404</v>
+        <v>69.401310410870394</v>
       </c>
       <c r="F424">
         <v>86.652799999999999</v>
@@ -12069,7 +12069,7 @@
         <v>2518.4947360469901</v>
       </c>
       <c r="E425">
-        <v>101.0283</v>
+        <v>69.831470033112097</v>
       </c>
       <c r="F425">
         <v>85.934399999999997</v>
@@ -12092,7 +12092,7 @@
         <v>2503.9483545476101</v>
       </c>
       <c r="E426">
-        <v>101.6028</v>
+        <v>70.336550042894601</v>
       </c>
       <c r="F426">
         <v>85.066500000000005</v>
@@ -12115,7 +12115,7 @@
         <v>2488.77330359706</v>
       </c>
       <c r="E427">
-        <v>102.5956</v>
+        <v>70.925762957459597</v>
       </c>
       <c r="F427">
         <v>84.745900000000006</v>
@@ -12138,7 +12138,7 @@
         <v>2504.1713645762402</v>
       </c>
       <c r="E428">
-        <v>103.5034</v>
+        <v>71.592409081088704</v>
       </c>
       <c r="F428">
         <v>85.702699999999993</v>
@@ -12161,7 +12161,7 @@
         <v>2513.5729187462098</v>
       </c>
       <c r="E429">
-        <v>104.3562</v>
+        <v>72.164952775937394</v>
       </c>
       <c r="F429">
         <v>86.642600000000002</v>
@@ -12184,7 +12184,7 @@
         <v>2516.1088831289899</v>
       </c>
       <c r="E430">
-        <v>105.5352</v>
+        <v>73.160738698015294</v>
       </c>
       <c r="F430">
         <v>87.406300000000002</v>
@@ -12207,7 +12207,7 @@
         <v>2505.8786106646698</v>
       </c>
       <c r="E431">
-        <v>106.04770000000001</v>
+        <v>73.642182626806701</v>
       </c>
       <c r="F431">
         <v>87.641900000000007</v>
@@ -12230,7 +12230,7 @@
         <v>2535.6831487220802</v>
       </c>
       <c r="E432">
-        <v>107.0355</v>
+        <v>74.322389395742704</v>
       </c>
       <c r="F432">
         <v>88.022099999999995</v>
@@ -12253,7 +12253,7 @@
         <v>2530.3457239131699</v>
       </c>
       <c r="E433">
-        <v>107.667</v>
+        <v>74.748825853834404</v>
       </c>
       <c r="F433">
         <v>88.379300000000001</v>
@@ -12276,7 +12276,7 @@
         <v>2538.1596676716799</v>
       </c>
       <c r="E434">
-        <v>109.66849999999999</v>
+        <v>75.578996463220506</v>
       </c>
       <c r="F434">
         <v>89.342600000000004</v>
@@ -12299,7 +12299,7 @@
         <v>2528.4589114055002</v>
       </c>
       <c r="E435">
-        <v>109.52509999999999</v>
+        <v>75.878727756713999</v>
       </c>
       <c r="F435">
         <v>89.677899999999994</v>
@@ -12322,7 +12322,7 @@
         <v>2531.5178021340998</v>
       </c>
       <c r="E436">
-        <v>111.12949999999999</v>
+        <v>76.660987780072603</v>
       </c>
       <c r="F436">
         <v>90.2928</v>
@@ -12345,7 +12345,7 @@
         <v>2520.9392746233002</v>
       </c>
       <c r="E437">
-        <v>111.63500000000001</v>
+        <v>77.136602133787207</v>
       </c>
       <c r="F437">
         <v>90.599100000000007</v>
@@ -12368,7 +12368,7 @@
         <v>2526.9743982549098</v>
       </c>
       <c r="E438">
-        <v>112.58069999999999</v>
+        <v>77.620479744289398</v>
       </c>
       <c r="F438">
         <v>91.822999999999993</v>
@@ -12391,7 +12391,7 @@
         <v>2539.9696014074698</v>
       </c>
       <c r="E439">
-        <v>112.3613</v>
+        <v>77.569379031180603</v>
       </c>
       <c r="F439">
         <v>91.992800000000003</v>
@@ -12414,7 +12414,7 @@
         <v>2531.54459989616</v>
       </c>
       <c r="E440">
-        <v>112.8854</v>
+        <v>77.799847375788005</v>
       </c>
       <c r="F440">
         <v>92.342100000000002</v>
@@ -12437,7 +12437,7 @@
         <v>2547.6328391881302</v>
       </c>
       <c r="E441">
-        <v>113.30880000000001</v>
+        <v>78.140921846753699</v>
       </c>
       <c r="F441">
         <v>92.680499999999995</v>
@@ -12460,7 +12460,7 @@
         <v>2538.97705644092</v>
       </c>
       <c r="E442">
-        <v>113.5702</v>
+        <v>78.421419292514599</v>
       </c>
       <c r="F442">
         <v>92.953699999999998</v>
@@ -12483,7 +12483,7 @@
         <v>2570.63679950193</v>
       </c>
       <c r="E443">
-        <v>114.1142</v>
+        <v>78.928103466330697</v>
       </c>
       <c r="F443">
         <v>92.690299999999993</v>
@@ -12506,7 +12506,7 @@
         <v>2543.54426834573</v>
       </c>
       <c r="E444">
-        <v>114.7718</v>
+        <v>79.4282840743153</v>
       </c>
       <c r="F444">
         <v>92.770899999999997</v>
@@ -12529,7 +12529,7 @@
         <v>2532.1526665532801</v>
       </c>
       <c r="E445">
-        <v>116.1199</v>
+        <v>80.017114084724099</v>
       </c>
       <c r="F445">
         <v>93.678700000000006</v>
@@ -12552,7 +12552,7 @@
         <v>2535.1333467141899</v>
       </c>
       <c r="E446">
-        <v>117.7303</v>
+        <v>80.679234999728394</v>
       </c>
       <c r="F446">
         <v>93.481399999999994</v>
@@ -12575,7 +12575,7 @@
         <v>2527.7989571551898</v>
       </c>
       <c r="E447">
-        <v>117.5355</v>
+        <v>80.621205843482201</v>
       </c>
       <c r="F447">
         <v>93.110200000000006</v>
@@ -12598,7 +12598,7 @@
         <v>2527.1075486259101</v>
       </c>
       <c r="E448">
-        <v>117.1961</v>
+        <v>80.191257593376704</v>
       </c>
       <c r="F448">
         <v>94.078800000000001</v>
@@ -12621,7 +12621,7 @@
         <v>2534.80656517236</v>
       </c>
       <c r="E449">
-        <v>116.61060000000001</v>
+        <v>80.100532098061294</v>
       </c>
       <c r="F449">
         <v>93.774900000000002</v>
@@ -12644,7 +12644,7 @@
         <v>2531.0966973529498</v>
       </c>
       <c r="E450">
-        <v>117.684</v>
+        <v>80.663877269277606</v>
       </c>
       <c r="F450">
         <v>93.888000000000005</v>
@@ -12667,7 +12667,7 @@
         <v>2516.7819850849</v>
       </c>
       <c r="E451">
-        <v>117.9905</v>
+        <v>81.212609216603497</v>
       </c>
       <c r="F451">
         <v>94.171999999999997</v>
@@ -12690,7 +12690,7 @@
         <v>2493.8152045883298</v>
       </c>
       <c r="E452">
-        <v>118.34990000000001</v>
+        <v>81.598331766782493</v>
       </c>
       <c r="F452">
         <v>94.635999999999996</v>
@@ -12713,7 +12713,7 @@
         <v>2465.0733650439802</v>
       </c>
       <c r="E453">
-        <v>118.6061</v>
+        <v>82.003899231685807</v>
       </c>
       <c r="F453">
         <v>95.274900000000002</v>
@@ -12736,7 +12736,7 @@
         <v>2439.04148411811</v>
       </c>
       <c r="E454">
-        <v>118.533</v>
+        <v>82.011821140828502</v>
       </c>
       <c r="F454">
         <v>95.196100000000001</v>
@@ -12759,7 +12759,7 @@
         <v>2443.6808366294599</v>
       </c>
       <c r="E455">
-        <v>118.5491</v>
+        <v>81.870490522485696</v>
       </c>
       <c r="F455">
         <v>95.856800000000007</v>
@@ -12782,7 +12782,7 @@
         <v>2448.9736733670302</v>
       </c>
       <c r="E456">
-        <v>118.14075730506754</v>
+        <v>82.067041873643007</v>
       </c>
       <c r="F456">
         <v>95.848500000000001</v>
@@ -12805,7 +12805,7 @@
         <v>2455.58485076335</v>
       </c>
       <c r="E457">
-        <v>118.41470415791355</v>
+        <v>82.523420470115497</v>
       </c>
       <c r="F457">
         <v>96.357100000000003</v>
@@ -12828,7 +12828,7 @@
         <v>2440.85189403817</v>
       </c>
       <c r="E458">
-        <v>119.33437715532203</v>
+        <v>82.807829647970806</v>
       </c>
       <c r="F458">
         <v>96.931799999999996</v>
@@ -12851,7 +12851,7 @@
         <v>2430.3894433054202</v>
       </c>
       <c r="E459">
-        <v>119.58573725959694</v>
+        <v>83.5442591074397</v>
       </c>
       <c r="F459">
         <v>97.243499999999997</v>
@@ -12874,7 +12874,7 @@
         <v>2452.1061064332998</v>
       </c>
       <c r="E460">
-        <v>118.99054109179259</v>
+        <v>83.415050631545995</v>
       </c>
       <c r="F460">
         <v>96.74</v>
@@ -12897,7 +12897,7 @@
         <v>2477.4557643661501</v>
       </c>
       <c r="E461">
-        <v>118.15970701999298</v>
+        <v>83.307392245879598</v>
       </c>
       <c r="F461">
         <v>97.435900000000004</v>
@@ -12920,7 +12920,7 @@
         <v>2494.3588957591701</v>
       </c>
       <c r="E462">
-        <v>118.86664944643007</v>
+        <v>83.651205561546902</v>
       </c>
       <c r="F462">
         <v>97.660899999999998</v>
@@ -12943,7 +12943,7 @@
         <v>2504.86511587519</v>
       </c>
       <c r="E463">
-        <v>118.3926607642689</v>
+        <v>83.468145959388394</v>
       </c>
       <c r="F463">
         <v>97.666300000000007</v>
@@ -12966,7 +12966,7 @@
         <v>2511.61533246917</v>
       </c>
       <c r="E464">
-        <v>118.52036283139523</v>
+        <v>83.648743533143104</v>
       </c>
       <c r="F464">
         <v>97.871300000000005</v>
@@ -12989,7 +12989,7 @@
         <v>2515.5184086997301</v>
       </c>
       <c r="E465">
-        <v>118.16673072549602</v>
+        <v>83.539355402706306</v>
       </c>
       <c r="F465">
         <v>97.452500000000001</v>
@@ -13012,7 +13012,7 @@
         <v>2522.20498781059</v>
       </c>
       <c r="E466">
-        <v>117.75755242288895</v>
+        <v>83.246837067614194</v>
       </c>
       <c r="F466">
         <v>97.381</v>
@@ -13035,7 +13035,7 @@
         <v>2509.60468244096</v>
       </c>
       <c r="E467">
-        <v>118.35596815169392</v>
+        <v>83.503468499415902</v>
       </c>
       <c r="F467">
         <v>97.719300000000004</v>
@@ -13058,7 +13058,7 @@
         <v>2517.41459779977</v>
       </c>
       <c r="E468">
-        <v>118.19566799799401</v>
+        <v>83.5593683533194</v>
       </c>
       <c r="F468">
         <v>98.077699999999993</v>
@@ -13081,7 +13081,7 @@
         <v>2500.5429887425898</v>
       </c>
       <c r="E469">
-        <v>118.57286011270736</v>
+        <v>83.888377273886505</v>
       </c>
       <c r="F469">
         <v>98.310100000000006</v>
@@ -13104,7 +13104,7 @@
         <v>2504.1810923264602</v>
       </c>
       <c r="E470">
-        <v>119.04896745594699</v>
+        <v>84.068316958983502</v>
       </c>
       <c r="F470">
         <v>98.334199999999996</v>
@@ -13127,7 +13127,7 @@
         <v>2507.26629865823</v>
       </c>
       <c r="E471">
-        <v>119.02866143345256</v>
+        <v>84.116956568271206</v>
       </c>
       <c r="F471">
         <v>98.7941</v>
@@ -13150,7 +13150,7 @@
         <v>2511.0954690497301</v>
       </c>
       <c r="E472">
-        <v>119.35038495946846</v>
+        <v>84.689478025041296</v>
       </c>
       <c r="F472">
         <v>99.192099999999996</v>
@@ -13173,7 +13173,7 @@
         <v>2497.1062753995502</v>
       </c>
       <c r="E473">
-        <v>119.80717869674264</v>
+        <v>84.937236923951701</v>
       </c>
       <c r="F473">
         <v>99.106499999999997</v>
@@ -13196,7 +13196,7 @@
         <v>2475.7788022517002</v>
       </c>
       <c r="E474">
-        <v>119.89250139482283</v>
+        <v>85.144160091621899</v>
       </c>
       <c r="F474">
         <v>99.183899999999994</v>
@@ -13219,7 +13219,7 @@
         <v>2473.4296399662599</v>
       </c>
       <c r="E475">
-        <v>119.38053640623478</v>
+        <v>85.014966380019004</v>
       </c>
       <c r="F475">
         <v>99.389700000000005</v>
@@ -13242,7 +13242,7 @@
         <v>2487.0511198716299</v>
       </c>
       <c r="E476">
-        <v>120.06179493641287</v>
+        <v>85.389386621087795</v>
       </c>
       <c r="F476">
         <v>99.081400000000002</v>
@@ -13265,7 +13265,7 @@
         <v>2487.1518459654199</v>
       </c>
       <c r="E477">
-        <v>120.62158187704878</v>
+        <v>85.827088799295396</v>
       </c>
       <c r="F477">
         <v>99.654300000000006</v>
@@ -13288,7 +13288,7 @@
         <v>2515.5975488243098</v>
       </c>
       <c r="E478">
-        <v>120.99892306608187</v>
+        <v>86.130328333313997</v>
       </c>
       <c r="F478">
         <v>100.161</v>
@@ -13311,7 +13311,7 @@
         <v>2521.5234977718501</v>
       </c>
       <c r="E479">
-        <v>120.81653939296628</v>
+        <v>86.231032045948297</v>
       </c>
       <c r="F479">
         <v>100.08199999999999</v>
@@ -13334,7 +13334,7 @@
         <v>2516.7565046681798</v>
       </c>
       <c r="E480">
-        <v>121.39299775045774</v>
+        <v>86.664038886914994</v>
       </c>
       <c r="F480">
         <v>100.3158</v>
@@ -13357,7 +13357,7 @@
         <v>2513.1548951551599</v>
       </c>
       <c r="E481">
-        <v>121.2350712992764</v>
+        <v>86.902715934804604</v>
       </c>
       <c r="F481">
         <v>100.5175</v>
@@ -13380,7 +13380,7 @@
         <v>2515.6948508032001</v>
       </c>
       <c r="E482">
-        <v>122.29477842314841</v>
+        <v>87.145491894909796</v>
       </c>
       <c r="F482">
         <v>100.15989999999999</v>
@@ -13403,7 +13403,7 @@
         <v>2505.3410138282502</v>
       </c>
       <c r="E483">
-        <v>122.99393056930916</v>
+        <v>87.531553399305096</v>
       </c>
       <c r="F483">
         <v>100.91679999999999</v>
@@ -13426,7 +13426,7 @@
         <v>2502.0569118840499</v>
       </c>
       <c r="E484">
-        <v>122.80862122821897</v>
+        <v>87.694171210091298</v>
       </c>
       <c r="F484">
         <v>101.8942</v>
@@ -13449,7 +13449,7 @@
         <v>2483.5565282910402</v>
       </c>
       <c r="E485">
-        <v>123.28358667038096</v>
+        <v>87.940555457845903</v>
       </c>
       <c r="F485">
         <v>101.9928</v>
@@ -13472,7 +13472,7 @@
         <v>2490.9273788485998</v>
       </c>
       <c r="E486">
-        <v>122.99587285905162</v>
+        <v>88.034192069244796</v>
       </c>
       <c r="F486">
         <v>102.3836</v>
@@ -13495,7 +13495,7 @@
         <v>2486.4018912576398</v>
       </c>
       <c r="E487">
-        <v>123.2257264918003</v>
+        <v>88.071295459930099</v>
       </c>
       <c r="F487">
         <v>102.735</v>
@@ -13518,7 +13518,7 @@
         <v>2477.19528640931</v>
       </c>
       <c r="E488">
-        <v>123.45360970387436</v>
+        <v>88.403512054694204</v>
       </c>
       <c r="F488">
         <v>102.9632</v>
@@ -13541,7 +13541,7 @@
         <v>2493.2375696792401</v>
       </c>
       <c r="E489">
-        <v>122.25831169856602</v>
+        <v>87.998497507001304</v>
       </c>
       <c r="F489">
         <v>102.7688</v>
@@ -13564,7 +13564,7 @@
         <v>2493.0531848116698</v>
       </c>
       <c r="E490">
-        <v>123.48572963177847</v>
+        <v>88.844741212185795</v>
       </c>
       <c r="F490">
         <v>103.0641</v>
@@ -13587,7 +13587,7 @@
         <v>2505.9305361810498</v>
       </c>
       <c r="E491">
-        <v>122.65342657538569</v>
+        <v>88.852665558749194</v>
       </c>
       <c r="F491">
         <v>103.07640000000001</v>
@@ -13610,7 +13610,7 @@
         <v>2492.0968079374002</v>
       </c>
       <c r="E492">
-        <v>123.5449340741413</v>
+        <v>89.066744740939995</v>
       </c>
       <c r="F492">
         <v>103.71259999999999</v>
@@ -13633,7 +13633,7 @@
         <v>2502.8193622475001</v>
       </c>
       <c r="E493">
-        <v>123.82562279424961</v>
+        <v>89.576396987926501</v>
       </c>
       <c r="F493">
         <v>103.70440000000001</v>
@@ -13656,7 +13656,7 @@
         <v>2510.17930661941</v>
       </c>
       <c r="E494">
-        <v>124.51339629768127</v>
+        <v>89.303849291929296</v>
       </c>
       <c r="F494">
         <v>102.8905</v>
@@ -13679,7 +13679,7 @@
         <v>2534.3801913165698</v>
       </c>
       <c r="E495">
-        <v>124.17704048680501</v>
+        <v>89.375426431347705</v>
       </c>
       <c r="F495">
         <v>102.23350000000001</v>
@@ -13702,7 +13702,7 @@
         <v>2571.8828599016301</v>
       </c>
       <c r="E496">
-        <v>124.13239125563145</v>
+        <v>89.350358678531407</v>
       </c>
       <c r="F496">
         <v>101.8914</v>
@@ -13725,7 +13725,7 @@
         <v>2572.3045627950901</v>
       </c>
       <c r="E497">
-        <v>124.06245844535665</v>
+        <v>89.448355494300102</v>
       </c>
       <c r="F497">
         <v>101.3355</v>
@@ -13748,7 +13748,7 @@
         <v>2586.7429430899101</v>
       </c>
       <c r="E498">
-        <v>123.74836754574204</v>
+        <v>89.399506759849103</v>
       </c>
       <c r="F498">
         <v>100.8883</v>
@@ -13771,7 +13771,7 @@
         <v>2586.5667089093399</v>
       </c>
       <c r="E499">
-        <v>124.33509119711461</v>
+        <v>89.722512597503496</v>
       </c>
       <c r="F499">
         <v>100.571</v>
@@ -13794,7 +13794,7 @@
         <v>2582.9460709750001</v>
       </c>
       <c r="E500">
-        <v>124.07425868463432</v>
+        <v>89.9446500249297</v>
       </c>
       <c r="F500">
         <v>101.22280000000001</v>
@@ -13817,7 +13817,7 @@
         <v>2610.5583441157901</v>
       </c>
       <c r="E501">
-        <v>124.49109553380849</v>
+        <v>89.909237841305995</v>
       </c>
       <c r="F501">
         <v>101.0367</v>
@@ -13840,7 +13840,7 @@
         <v>2622.9852929798299</v>
       </c>
       <c r="E502">
-        <v>124.37144851537983</v>
+        <v>90.281125277103101</v>
       </c>
       <c r="F502">
         <v>100.7547</v>
@@ -13863,7 +13863,7 @@
         <v>2642.3586915317001</v>
       </c>
       <c r="E503">
-        <v>124.77885124480906</v>
+        <v>90.264075578860002</v>
       </c>
       <c r="F503">
         <v>100.2675</v>
@@ -13886,7 +13886,7 @@
         <v>2650.2511718617002</v>
       </c>
       <c r="E504">
-        <v>124.31098861255964</v>
+        <v>90.146923783133801</v>
       </c>
       <c r="F504">
         <v>99.529799999999994</v>
@@ -13909,7 +13909,7 @@
         <v>2675.5639957119201</v>
       </c>
       <c r="E505">
-        <v>124.01275898947097</v>
+        <v>90.047354095585504</v>
       </c>
       <c r="F505">
         <v>99.041700000000006</v>
@@ -13932,7 +13932,7 @@
         <v>2676.9830076767498</v>
       </c>
       <c r="E506">
-        <v>125.35768452359675</v>
+        <v>90.6793123075729</v>
       </c>
       <c r="F506">
         <v>99.560699999999997</v>
@@ -13955,7 +13955,7 @@
         <v>2685.9051147370501</v>
       </c>
       <c r="E507">
-        <v>125.02797942597637</v>
+        <v>90.496018749172904</v>
       </c>
       <c r="F507">
         <v>99.044499999999999</v>
@@ -13978,7 +13978,7 @@
         <v>2686.59492505559</v>
       </c>
       <c r="E508">
-        <v>125.28072428385592</v>
+        <v>90.412936259425095</v>
       </c>
       <c r="F508">
         <v>98.309600000000003</v>
@@ -14001,7 +14001,7 @@
         <v>2680.6727594434401</v>
       </c>
       <c r="E509">
-        <v>125.51082522869189</v>
+        <v>90.8106621551931</v>
       </c>
       <c r="F509">
         <v>98.642099999999999</v>
@@ -14024,7 +14024,7 @@
         <v>2693.5809952422901</v>
       </c>
       <c r="E510">
-        <v>125.44819974466931</v>
+        <v>90.606021877283098</v>
       </c>
       <c r="F510">
         <v>98.418400000000005</v>
@@ -14047,7 +14047,7 @@
         <v>2705.5449003898502</v>
       </c>
       <c r="E511">
-        <v>126.31682558927686</v>
+        <v>91.068881636954899</v>
       </c>
       <c r="F511">
         <v>98.883300000000006</v>
@@ -14070,7 +14070,7 @@
         <v>2715.7194472967199</v>
       </c>
       <c r="E512">
-        <v>125.70197635861378</v>
+        <v>91.133681179055699</v>
       </c>
       <c r="F512">
         <v>98.999200000000002</v>
@@ -14093,7 +14093,7 @@
         <v>2709.59508099614</v>
       </c>
       <c r="E513">
-        <v>126.07324989916349</v>
+        <v>91.379423800377396</v>
       </c>
       <c r="F513">
         <v>98.85</v>
@@ -14116,7 +14116,7 @@
         <v>2697.3614612359802</v>
       </c>
       <c r="E514">
-        <v>125.96148503155078</v>
+        <v>91.463245326784204</v>
       </c>
       <c r="F514">
         <v>98.745699999999999</v>
@@ -14139,7 +14139,7 @@
         <v>2698.6320847182101</v>
       </c>
       <c r="E515">
-        <v>126.83403785871297</v>
+        <v>91.848373148160206</v>
       </c>
       <c r="F515">
         <v>98.761099999999999</v>
@@ -14162,7 +14162,7 @@
         <v>2695.6992901113399</v>
       </c>
       <c r="E516">
-        <v>126.92318194808253</v>
+        <v>92.495339760513602</v>
       </c>
       <c r="F516">
         <v>98.349100000000007</v>
@@ -14185,7 +14185,7 @@
         <v>2707.0125298018102</v>
       </c>
       <c r="E517">
-        <v>126.88902479694869</v>
+        <v>92.630109600789496</v>
       </c>
       <c r="F517">
         <v>99.0214</v>
@@ -14208,7 +14208,7 @@
         <v>2730.3526369413298</v>
       </c>
       <c r="E518">
-        <v>127.85577746216126</v>
+        <v>92.481196338989605</v>
       </c>
       <c r="F518">
         <v>98.761099999999999</v>
@@ -14231,7 +14231,7 @@
         <v>2735.7342897383801</v>
       </c>
       <c r="E519">
-        <v>128.33369493686936</v>
+        <v>92.756683069838601</v>
       </c>
       <c r="F519">
         <v>98.364599999999996</v>
@@ -14254,7 +14254,7 @@
         <v>2749.4876489220001</v>
       </c>
       <c r="E520">
-        <v>129.01558161615276</v>
+        <v>93.104312689534098</v>
       </c>
       <c r="F520">
         <v>99.0137</v>
@@ -14277,7 +14277,7 @@
         <v>2713.5888757610101</v>
       </c>
       <c r="E521">
-        <v>129.27656943628483</v>
+        <v>93.500320565898704</v>
       </c>
       <c r="F521">
         <v>100.0224</v>
@@ -14300,7 +14300,7 @@
         <v>2691.3025363196898</v>
       </c>
       <c r="E522">
-        <v>129.50706446858402</v>
+        <v>93.860393447382194</v>
       </c>
       <c r="F522">
         <v>100.1408</v>
@@ -14323,7 +14323,7 @@
         <v>2687.3763876419998</v>
       </c>
       <c r="E523">
-        <v>129.47927127320767</v>
+        <v>94.152229790694804</v>
       </c>
       <c r="F523">
         <v>100.3471</v>
@@ -14346,7 +14346,7 @@
         <v>2678.3840965890499</v>
       </c>
       <c r="E524">
-        <v>129.33671267722045</v>
+        <v>94.282248959429097</v>
       </c>
       <c r="F524">
         <v>100.10680000000001</v>
@@ -14369,7 +14369,7 @@
         <v>2645.5822588013498</v>
       </c>
       <c r="E525">
-        <v>130.17848438081424</v>
+        <v>94.769348105404305</v>
       </c>
       <c r="F525">
         <v>99.692499999999995</v>
@@ -14392,7 +14392,7 @@
         <v>2666.7195882997999</v>
       </c>
       <c r="E526">
-        <v>130.46378519162477</v>
+        <v>94.819850465167605</v>
       </c>
       <c r="F526">
         <v>99.795400000000001</v>
@@ -14415,7 +14415,7 @@
         <v>2620.6928805780399</v>
       </c>
       <c r="E527">
-        <v>130.55413121856733</v>
+        <v>94.9501173328471</v>
       </c>
       <c r="F527">
         <v>101.0247</v>
@@ -14438,7 +14438,7 @@
         <v>2599.6951869702598</v>
       </c>
       <c r="E528">
-        <v>131.77102810417074</v>
+        <v>95.813553433020701</v>
       </c>
       <c r="F528">
         <v>101.2664</v>
@@ -14461,7 +14461,7 @@
         <v>2563.6879177312098</v>
       </c>
       <c r="E529">
-        <v>131.96378721102226</v>
+        <v>96.154994032045195</v>
       </c>
       <c r="F529">
         <v>101.4644</v>
@@ -14484,7 +14484,7 @@
         <v>2560.4027568052602</v>
       </c>
       <c r="E530">
-        <v>132.47125094422424</v>
+        <v>96.112719163658596</v>
       </c>
       <c r="F530">
         <v>101.46250000000001</v>
@@ -14507,7 +14507,7 @@
         <v>2527.15409101266</v>
       </c>
       <c r="E531">
-        <v>132.93298644421094</v>
+        <v>96.319095399027105</v>
       </c>
       <c r="F531">
         <v>101.7085</v>
@@ -14530,7 +14530,7 @@
         <v>2513.1125381390598</v>
       </c>
       <c r="E532">
-        <v>132.44750488403352</v>
+        <v>96.376997983512197</v>
       </c>
       <c r="F532">
         <v>102.2067</v>
@@ -14553,7 +14553,7 @@
         <v>2518.9301776244401</v>
       </c>
       <c r="E533">
-        <v>133.15785976208238</v>
+        <v>96.835625056610795</v>
       </c>
       <c r="F533">
         <v>103.3329</v>
@@ -14576,7 +14576,7 @@
         <v>2511.4218101169899</v>
       </c>
       <c r="E534">
-        <v>132.90321082650064</v>
+        <v>96.815165670400404</v>
       </c>
       <c r="F534">
         <v>102.4024</v>
@@ -14599,7 +14599,7 @@
         <v>2500.3222517612999</v>
       </c>
       <c r="E535">
-        <v>132.70481133397854</v>
+        <v>96.7707241014961</v>
       </c>
       <c r="F535">
         <v>103.19799999999999</v>
@@ -14622,7 +14622,7 @@
         <v>2511.0237465700402</v>
       </c>
       <c r="E536">
-        <v>133.07972091568664</v>
+        <v>96.9722522369986</v>
       </c>
       <c r="F536">
         <v>103.3646</v>
@@ -14645,7 +14645,7 @@
         <v>2514.3538294405698</v>
       </c>
       <c r="E537">
-        <v>133.65067677033733</v>
+        <v>97.391604016758507</v>
       </c>
       <c r="F537">
         <v>104.03270000000001</v>
@@ -14668,7 +14668,7 @@
         <v>2509.6973736965001</v>
       </c>
       <c r="E538">
-        <v>133.159422977715</v>
+        <v>97.095381916782301</v>
       </c>
       <c r="F538">
         <v>104.10039999999999</v>
@@ -14691,7 +14691,7 @@
         <v>2520.9949441613398</v>
       </c>
       <c r="E539">
-        <v>134.08243461507712</v>
+        <v>97.6836096997162</v>
       </c>
       <c r="F539">
         <v>103.98560000000001</v>
@@ -14714,7 +14714,7 @@
         <v>2545.40152890031</v>
       </c>
       <c r="E540">
-        <v>133.49864356080025</v>
+        <v>97.286502584965504</v>
       </c>
       <c r="F540">
         <v>104.0681</v>
@@ -14737,7 +14737,7 @@
         <v>2557.38410609017</v>
       </c>
       <c r="E541">
-        <v>133.6238541456282</v>
+        <v>97.420037195968405</v>
       </c>
       <c r="F541">
         <v>104.0936</v>
@@ -14760,7 +14760,7 @@
         <v>2542.4084704851798</v>
       </c>
       <c r="E542">
-        <v>133.56866403399539</v>
+        <v>97.358753422140296</v>
       </c>
       <c r="F542">
         <v>103.4021</v>
@@ -14783,7 +14783,7 @@
         <v>2528.7506035004499</v>
       </c>
       <c r="E543">
-        <v>133.4937783333651</v>
+        <v>97.246836461850606</v>
       </c>
       <c r="F543">
         <v>102.83710000000001</v>
@@ -14806,7 +14806,7 @@
         <v>2534.9435178513299</v>
       </c>
       <c r="E544">
-        <v>134.26612326684631</v>
+        <v>97.876612370062105</v>
       </c>
       <c r="F544">
         <v>102.87569999999999</v>
@@ -14829,7 +14829,7 @@
         <v>2518.6259217316201</v>
       </c>
       <c r="E545">
-        <v>134.17591478155919</v>
+        <v>97.777474923404597</v>
       </c>
       <c r="F545">
         <v>102.274</v>
@@ -14852,7 +14852,7 @@
         <v>2520.0307032939299</v>
       </c>
       <c r="E546">
-        <v>134.25153176848161</v>
+        <v>97.869105169729394</v>
       </c>
       <c r="F546">
         <v>102.392</v>
@@ -14875,7 +14875,7 @@
         <v>2523.7129935090402</v>
       </c>
       <c r="E547">
-        <v>133.45443223898036</v>
+        <v>97.234223329052298</v>
       </c>
       <c r="F547">
         <v>102.4375</v>
@@ -14898,7 +14898,7 @@
         <v>2493.88303602616</v>
       </c>
       <c r="E548">
-        <v>133.61623976098895</v>
+        <v>97.351656160277798</v>
       </c>
       <c r="F548">
         <v>101.9408</v>
@@ -14921,7 +14921,7 @@
         <v>2511.34629801149</v>
       </c>
       <c r="E549">
-        <v>133.64469860722178</v>
+        <v>97.358991953115705</v>
       </c>
       <c r="F549">
         <v>102.639</v>
@@ -14944,7 +14944,7 @@
         <v>2505.83602086171</v>
       </c>
       <c r="E550">
-        <v>133.46851801539395</v>
+        <v>97.275424823361007</v>
       </c>
       <c r="F550">
         <v>102.29170000000001</v>
@@ -14967,7 +14967,7 @@
         <v>2504.6372635123098</v>
       </c>
       <c r="E551">
-        <v>133.66177641528549</v>
+        <v>97.309066418854002</v>
       </c>
       <c r="F551">
         <v>101.4281</v>
@@ -14990,7 +14990,7 @@
         <v>2501.18696193917</v>
       </c>
       <c r="E552">
-        <v>133.94468599478679</v>
+        <v>97.543263590920404</v>
       </c>
       <c r="F552">
         <v>101.9372</v>
@@ -15013,7 +15013,7 @@
         <v>2488.5340843451399</v>
       </c>
       <c r="E553">
-        <v>134.16612882337895</v>
+        <v>97.721365192452296</v>
       </c>
       <c r="F553">
         <v>101.7003</v>
@@ -15036,7 +15036,7 @@
         <v>2483.26605328403</v>
       </c>
       <c r="E554">
-        <v>127.66912971222796</v>
+        <v>92.958782779011997</v>
       </c>
       <c r="F554">
         <v>101.0338</v>
@@ -15059,7 +15059,7 @@
         <v>2469.0190190308199</v>
       </c>
       <c r="E555">
-        <v>128.06744133285179</v>
+        <v>93.157070828095101</v>
       </c>
       <c r="F555">
         <v>101.37350000000001</v>
@@ -15082,7 +15082,7 @@
         <v>2520.4470066464301</v>
       </c>
       <c r="E556">
-        <v>127.7271957964585</v>
+        <v>93.009665746446998</v>
       </c>
       <c r="F556">
         <v>97.407799999999995</v>
@@ -15105,7 +15105,7 @@
         <v>2595.9488178127799</v>
       </c>
       <c r="E557">
-        <v>116.9094593718261</v>
+        <v>85.124649690455698</v>
       </c>
       <c r="F557">
         <v>84.561899999999994</v>
@@ -15128,7 +15128,7 @@
         <v>2622.5404202851901</v>
       </c>
       <c r="E558">
-        <v>117.85233344680985</v>
+        <v>85.869022427731196</v>
       </c>
       <c r="F558">
         <v>85.960400000000007</v>
@@ -15151,7 +15151,7 @@
         <v>2666.1271918146899</v>
       </c>
       <c r="E559">
-        <v>123.35193015827606</v>
+        <v>89.787915547212805</v>
       </c>
       <c r="F559">
         <v>91.593400000000003</v>
@@ -15174,7 +15174,7 @@
         <v>2666.1825716124999</v>
       </c>
       <c r="E560">
-        <v>127.33643926328182</v>
+        <v>92.730134673182704</v>
       </c>
       <c r="F560">
         <v>95.025599999999997</v>
@@ -15197,7 +15197,7 @@
         <v>2653.1726518291298</v>
       </c>
       <c r="E561">
-        <v>129.04118020316363</v>
+        <v>93.958643334788107</v>
       </c>
       <c r="F561">
         <v>95.954899999999995</v>
@@ -15220,7 +15220,7 @@
         <v>2648.3966001787999</v>
       </c>
       <c r="E562">
-        <v>131.12876809185218</v>
+        <v>95.531928337251998</v>
       </c>
       <c r="F562">
         <v>95.966899999999995</v>
@@ -15243,7 +15243,7 @@
         <v>2626.5034539885701</v>
       </c>
       <c r="E563">
-        <v>132.6055269121259</v>
+        <v>96.608202182205204</v>
       </c>
       <c r="F563">
         <v>96.739400000000003</v>
@@ -15266,7 +15266,7 @@
         <v>2617.8544875023799</v>
       </c>
       <c r="E564">
-        <v>134.03304133938576</v>
+        <v>97.623066895294698</v>
       </c>
       <c r="F564">
         <v>97.081599999999995</v>
@@ -15289,7 +15289,7 @@
         <v>2619.0167782380699</v>
       </c>
       <c r="E565">
-        <v>135.18145979699403</v>
+        <v>98.411733492786496</v>
       </c>
       <c r="F565">
         <v>98.363</v>
@@ -15312,7 +15312,7 @@
         <v>2593.5412622465801</v>
       </c>
       <c r="E566">
-        <v>135.98689105914522</v>
+        <v>99.049502696569604</v>
       </c>
       <c r="F566">
         <v>98.882199999999997</v>
@@ -15335,7 +15335,7 @@
         <v>2588.1386918196999</v>
       </c>
       <c r="E567">
-        <v>135.1392194227671</v>
+        <v>98.432127863793895</v>
       </c>
       <c r="F567">
         <v>95.614900000000006</v>
@@ -15358,7 +15358,7 @@
         <v>2558.3961019178</v>
       </c>
       <c r="E568">
-        <v>136.22571270832398</v>
+        <v>99.232685949395204</v>
       </c>
       <c r="F568">
         <v>98.385599999999997</v>
@@ -15381,7 +15381,7 @@
         <v>2513.4557498447102</v>
       </c>
       <c r="E569">
-        <v>137.64564942626836</v>
+        <v>100.30878852382899</v>
       </c>
       <c r="F569">
         <v>98.558700000000002</v>
@@ -15404,7 +15404,7 @@
         <v>2498.9985361147301</v>
       </c>
       <c r="E570">
-        <v>136.05389989753658</v>
+        <v>99.221716124212307</v>
       </c>
       <c r="F570">
         <v>99.433300000000003</v>
@@ -15427,7 +15427,7 @@
         <v>2457.1845742417599</v>
       </c>
       <c r="E571">
-        <v>137.16216009258682</v>
+        <v>100.013011386221</v>
       </c>
       <c r="F571">
         <v>99.798699999999997</v>
@@ -15450,7 +15450,7 @@
         <v>2439.8379281799398</v>
       </c>
       <c r="E572">
-        <v>137.53122656301971</v>
+        <v>100.263051128995</v>
       </c>
       <c r="F572">
         <v>100.25190000000001</v>
@@ -15473,7 +15473,7 @@
         <v>2435.7672276643202</v>
       </c>
       <c r="E573">
-        <v>136.99512698838896</v>
+        <v>99.822789129563205</v>
       </c>
       <c r="F573">
         <v>100.0437</v>
@@ -15496,7 +15496,7 @@
         <v>2416.2762991456102</v>
       </c>
       <c r="E574">
-        <v>136.31922406989943</v>
+        <v>99.3518217307264</v>
       </c>
       <c r="F574">
         <v>98.857900000000001</v>
@@ -15519,7 +15519,7 @@
         <v>2412.5375182978701</v>
       </c>
       <c r="E575">
-        <v>137.74665055013264</v>
+        <v>100.285486249128</v>
       </c>
       <c r="F575">
         <v>100.1861</v>
@@ -15542,7 +15542,7 @@
         <v>2391.79900422729</v>
       </c>
       <c r="E576">
-        <v>139.44267258599598</v>
+        <v>101.566534757049</v>
       </c>
       <c r="F576">
         <v>100.86539999999999</v>
@@ -15565,7 +15565,7 @@
         <v>2364.5694835723202</v>
       </c>
       <c r="E577">
-        <v>140.81205214436932</v>
+        <v>102.452484460517</v>
       </c>
       <c r="F577">
         <v>100.57259999999999</v>
@@ -15588,7 +15588,7 @@
         <v>2330.7938082947699</v>
       </c>
       <c r="E578">
-        <v>141.11520203055548</v>
+        <v>102.69030748270799</v>
       </c>
       <c r="F578">
         <v>100.18559999999999</v>
@@ -15611,7 +15611,7 @@
         <v>2263.58552786072</v>
       </c>
       <c r="E579">
-        <v>141.89557206449706</v>
+        <v>103.331349755178</v>
       </c>
       <c r="F579">
         <v>100.8064</v>
@@ -15634,7 +15634,7 @@
         <v>2252.0828825763301</v>
       </c>
       <c r="E580">
-        <v>141.29459428789141</v>
+        <v>102.823899363679</v>
       </c>
       <c r="F580">
         <v>101.3907</v>
@@ -15657,7 +15657,7 @@
         <v>2235.7275641401602</v>
       </c>
       <c r="E581">
-        <v>139.63250258409872</v>
+        <v>101.629311522558</v>
       </c>
       <c r="F581">
         <v>101.44</v>
@@ -15680,7 +15680,7 @@
         <v>2190.35679238791</v>
       </c>
       <c r="E582">
-        <v>140.35543238866498</v>
+        <v>102.15625222586399</v>
       </c>
       <c r="F582">
         <v>101.3335</v>
@@ -15703,7 +15703,7 @@
         <v>2167.5525395701802</v>
       </c>
       <c r="E583">
-        <v>141.60750151547671</v>
+        <v>102.986113772358</v>
       </c>
       <c r="F583">
         <v>101.018</v>
@@ -15726,7 +15726,7 @@
         <v>2143.3778313460898</v>
       </c>
       <c r="E584">
-        <v>141.33029180276199</v>
+        <v>102.75562754024</v>
       </c>
       <c r="F584">
         <v>101.223</v>
@@ -15749,7 +15749,7 @@
         <v>2117.96608194485</v>
       </c>
       <c r="E585">
-        <v>141.96568860854504</v>
+        <v>103.219075332342</v>
       </c>
       <c r="F585">
         <v>101.0963</v>
@@ -15772,7 +15772,7 @@
         <v>2112.2785716127501</v>
       </c>
       <c r="E586">
-        <v>142.55112807576546</v>
+        <v>103.639385494115</v>
       </c>
       <c r="F586">
         <v>101.29179999999999</v>
@@ -15795,7 +15795,7 @@
         <v>2076.1785042356501</v>
       </c>
       <c r="E587">
-        <v>141.80588567412346</v>
+        <v>103.095184315249</v>
       </c>
       <c r="F587">
         <v>101.2529</v>
@@ -15818,7 +15818,7 @@
         <v>2010.9412406163201</v>
       </c>
       <c r="E588">
-        <v>141.61984042213524</v>
+        <v>102.973409037468</v>
       </c>
       <c r="F588">
         <v>100.9552</v>
@@ -15841,7 +15841,7 @@
         <v>2034.1256771262399</v>
       </c>
       <c r="E589">
-        <v>140.93961230073265</v>
+        <v>102.46154997413301</v>
       </c>
       <c r="F589">
         <v>99.766400000000004</v>
@@ -15864,7 +15864,7 @@
         <v>2067.1462221632901</v>
       </c>
       <c r="E590">
-        <v>141.45516232434346</v>
+        <v>102.846422667467</v>
       </c>
       <c r="F590">
         <v>100.505</v>
@@ -15887,7 +15887,7 @@
         <v>2021.8132338079399</v>
       </c>
       <c r="E591">
-        <v>142.24732815523618</v>
+        <v>103.442890165807</v>
       </c>
       <c r="F591">
         <v>100.6416</v>
@@ -15910,7 +15910,7 @@
         <v>2017.5955506360201</v>
       </c>
       <c r="E592">
-        <v>142.50489486501837</v>
+        <v>103.613958441074</v>
       </c>
       <c r="F592">
         <v>101.0205</v>
@@ -15933,7 +15933,7 @@
         <v>1985.97384727553</v>
       </c>
       <c r="E593">
-        <v>141.50964977288419</v>
+        <v>102.87456259747501</v>
       </c>
       <c r="F593">
         <v>101.253</v>
@@ -15956,7 +15956,7 @@
         <v>1979.3665705262199</v>
       </c>
       <c r="E594">
-        <v>142.3039535870723</v>
+        <v>103.585115297329</v>
       </c>
       <c r="F594">
         <v>100.9286</v>
@@ -15979,7 +15979,7 @@
         <v>1980.1193524471</v>
       </c>
       <c r="E595">
-        <v>142.90640034148012</v>
+        <v>103.852941814613</v>
       </c>
       <c r="F595">
         <v>100.11960000000001</v>
@@ -16002,7 +16002,7 @@
         <v>1964.73899156887</v>
       </c>
       <c r="E596">
-        <v>142.40442573493118</v>
+        <v>103.48614438363199</v>
       </c>
       <c r="F596">
         <v>100.9067</v>
@@ -16025,7 +16025,7 @@
         <v>1953.83062718582</v>
       </c>
       <c r="E597">
-        <v>143.01127915189505</v>
+        <v>103.98752113575701</v>
       </c>
       <c r="F597">
         <v>100.83929999999999</v>
@@ -16048,7 +16048,7 @@
         <v>1946.02322556232</v>
       </c>
       <c r="E598">
-        <v>143.35150642794963</v>
+        <v>104.178577444778</v>
       </c>
       <c r="F598">
         <v>101.0211</v>
@@ -16071,7 +16071,7 @@
         <v>1945.5176154021301</v>
       </c>
       <c r="E599">
-        <v>143.52873551435749</v>
+        <v>104.35772758935499</v>
       </c>
       <c r="F599">
         <v>100.4689</v>
@@ -16094,7 +16094,7 @@
         <v>1970.9590953454499</v>
       </c>
       <c r="E600">
-        <v>144.01491438554649</v>
+        <v>104.70695908836301</v>
       </c>
       <c r="F600">
         <v>100.8639</v>
@@ -16117,7 +16117,7 @@
         <v>1962.2337548333501</v>
       </c>
       <c r="E601">
-        <v>144.06551042465961</v>
+        <v>104.767910948912</v>
       </c>
       <c r="F601">
         <v>100.6031</v>
@@ -16140,7 +16140,7 @@
         <v>1963.5157417365899</v>
       </c>
       <c r="E602">
-        <v>143.47766767134777</v>
+        <v>104.361107060376</v>
       </c>
       <c r="F602">
         <v>99.222300000000004</v>
@@ -16163,7 +16163,7 @@
         <v>1978.3592108456901</v>
       </c>
       <c r="E603">
-        <v>144.22185649110688</v>
+        <v>104.837183305222</v>
       </c>
       <c r="F603">
         <v>100.285</v>
@@ -16186,7 +16186,7 @@
         <v>1967.7881871773</v>
       </c>
       <c r="E604">
-        <v>143.90923674577942</v>
+        <v>104.516513574307</v>
       </c>
       <c r="F604">
         <v>100.4575</v>
@@ -16209,7 +16209,7 @@
         <v>1995.1211427619201</v>
       </c>
       <c r="E605">
-        <v>144.50524604530958</v>
+        <v>105.03922765142499</v>
       </c>
       <c r="F605">
         <v>100.24339999999999</v>
@@ -16232,7 +16232,7 @@
         <v>1991.10903594964</v>
       </c>
       <c r="E606">
-        <v>144.97598475286594</v>
+        <v>105.366762050172</v>
       </c>
       <c r="F606">
         <v>100.863</v>
@@ -16255,7 +16255,7 @@
         <v>1993.10966513932</v>
       </c>
       <c r="E607">
-        <v>144.98852611627615</v>
+        <v>105.41484297943801</v>
       </c>
       <c r="F607">
         <v>100.89400000000001</v>
@@ -16278,7 +16278,7 @@
         <v>1967.69407090138</v>
       </c>
       <c r="E608">
-        <v>145.34415303977144</v>
+        <v>105.604275623574</v>
       </c>
       <c r="F608">
         <v>99.975700000000003</v>
@@ -16301,7 +16301,7 @@
         <v>1991.63125800957</v>
       </c>
       <c r="E609">
-        <v>145.60409123922608</v>
+        <v>105.95592996778799</v>
       </c>
       <c r="F609">
         <v>100.43089999999999</v>
@@ -16324,7 +16324,7 @@
         <v>2000.7953105434899</v>
       </c>
       <c r="E610">
-        <v>145.61711612476154</v>
+        <v>105.76761233795</v>
       </c>
       <c r="F610">
         <v>99.808400000000006</v>
@@ -16347,7 +16347,7 @@
         <v>2004.85323222442</v>
       </c>
       <c r="E611">
-        <v>146.38329320972682</v>
+        <v>106.39203598725</v>
       </c>
       <c r="F611">
         <v>99.469499999999996</v>
@@ -16370,7 +16370,7 @@
         <v>1995.1591679421199</v>
       </c>
       <c r="E612">
-        <v>146.43996866414332</v>
+        <v>106.457350613678</v>
       </c>
       <c r="F612">
         <v>99.292500000000004</v>
@@ -16393,7 +16393,7 @@
         <v>2004.7099317212801</v>
       </c>
       <c r="E613">
-        <v>147.55848999353427</v>
+        <v>107.159826847594</v>
       </c>
       <c r="F613">
         <v>100.32729999999999</v>
